--- a/docs/mascot-prompts.xlsx
+++ b/docs/mascot-prompts.xlsx
@@ -2,28 +2,28 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="วิธีใช้" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="สั่งทำหน้าลูกค้า" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ตัวละคร" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="คำสั่งทั้งหมด" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ส่งมอบแล้ว" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ตัวละคร" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="คำสั่งทั้งหมด" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ตัวละคร'!$A$1:$E$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'คำสั่งทั้งหมด'!$A$1:$H$511</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'ตัวละคร'!$A$1:$E$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'คำสั่งทั้งหมด'!$A$1:$H$511</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,24 +32,37 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00E0468E"/>
+      <color rgb="FFE0468E"/>
       <sz val="16"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFC0392B"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
-    <font>
-      <b val="1"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00C0392B"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -58,42 +71,53 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FF6FAA"/>
+        <fgColor rgb="FFFF6FAA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF0F6"/>
+        <fgColor rgb="FFFFF0F6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EEF2FF"/>
+        <fgColor rgb="FFEEF2FF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C8F2DC"/>
+        <fgColor rgb="FFC8F2DC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFE1E1"/>
+        <fgColor rgb="FFFFE1E1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF4C8"/>
+        <fgColor rgb="FFFFF4C8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0468E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE3F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E0468E"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE3F1"/>
       </patternFill>
     </fill>
   </fills>
@@ -107,23 +131,24 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00E6D6F0"/>
+        <color rgb="FFE6D6F0"/>
       </left>
       <right style="thin">
-        <color rgb="00E6D6F0"/>
+        <color rgb="FFE6D6F0"/>
       </right>
       <top style="thin">
-        <color rgb="00E6D6F0"/>
+        <color rgb="FFE6D6F0"/>
       </top>
       <bottom style="thin">
-        <color rgb="00E6D6F0"/>
+        <color rgb="FFE6D6F0"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -144,22 +169,31 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -525,10 +559,10 @@
   <dimension ref="A1:A29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="120" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" style="12" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="21" customHeight="1" s="12">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ตัวละครแทนวีเจ — คำสั่งสร้างรูปด้วย ChatGPT</t>
@@ -724,548 +758,548 @@
   <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="110" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" style="12" min="1" max="1"/>
+    <col width="26" customWidth="1" style="12" min="2" max="2"/>
+    <col width="34" customWidth="1" style="12" min="3" max="3"/>
+    <col width="16" customWidth="1" style="12" min="4" max="4"/>
+    <col width="110" customWidth="1" style="12" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>สั่งทำมาสคอตหน้าลูกค้า — คำสั่งสร้างรูปด้วย ChatGPT</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr"/>
+      <c r="A2" s="11" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>ก่อนเริ่ม: ใช้รูปที่ลูกค้าส่งมาเอง (หน้าของลูกค้าเอง) ผ่านแชทแจ้งปัญหาเท่านั้น — ห้ามใช้รูปคนอื่น/ดารา</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>1) ขอรูปหน้าตรงชัด ๆ 1–3 รูป (แสงพอ ไม่ใส่แมสก์ ไม่มีฟิลเตอร์หนัก ๆ) + สไตล์ชุดที่อยากได้</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>2) เปิดแชทใหม่ใน ChatGPT — 1 ลูกค้า = 1 แชท</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>3) แนบรูปลูกค้า (และแนบ G1-1.png จาก docs/mascots/G1 เป็นตัวอย่างสไตล์ ถ้าต้องการให้เข้าชุดกับตัวอื่น)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>4) คำสั่งที่ 1: แก้ [OUTFIT] เป็นชุดที่ลูกค้าอยากได้ เช่น "the same outfit as in the photo" หรือ "pastel pink hoodie with bunny ears"</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>5) ถ้าหน้าไม่ค่อยเหมือน ใช้คำสั่ง "แก้ให้เหมือนขึ้น" ด้านล่าง (ส่งซ้ำได้) จนลูกค้าพอใจ — ส่งรูปที่ 1 ให้ลูกค้าดูก่อนทำท่าอื่น</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>6) ได้รูปที่ 1 แล้ว วางคำสั่ง 2 → 17 ทีละช่องในแชทเดิม รอรูปเสร็จก่อนส่งคำสั่งถัดไป</t>
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>6) ได้รูปที่ 1 แล้ว วางคำสั่ง 2 → 17 ทีละช่องในแชทเดิม รอรูปเสร็จก่อนส่งคำสั่งถัดไป — ถ้ารูปไหนหัวใหญ่/เล็กกว่ารูปแรก หรือสีชุดเพี้ยน ให้ Gen ใหม่ (ระบบทาบให้ได้ แต่รูปตรงตั้งแต่แรกจะลื่นที่สุด)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>7) ดาวน์โหลดรูป (ไม่ใช่แคปจอ) ตั้งชื่อตามคอลัมน์ "ชื่อไฟล์" — แทน XX ด้วยชื่อย่อลูกค้า เช่น C-mimi-1.png แล้วส่งให้ทีมเว็บใส่ในวิดเจ็ต</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr"/>
+      <c r="A11" s="11" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>คำสั่ง "แก้ให้เหมือนขึ้น":</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="48" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+    <row r="13" ht="48" customHeight="1" s="12">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>Make the face look more like the person in the photo (hairstyle, eyes, face shape) while keeping the same chibi 3D style, outfit, pose, size and framing. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr"/>
+      <c r="A14" s="11" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>ลำดับ</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>ท่า</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>ใช้ตอน</t>
         </is>
       </c>
-      <c r="D15" s="11" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>ชื่อไฟล์</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t>คำสั่ง (คัดลอกไปวางได้เลย)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="110" customHeight="1">
-      <c r="A16" s="12" t="n">
+    <row r="16" ht="110.1" customHeight="1" s="12">
+      <c r="A16" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>ท่าปกติ (ท่าหลัก)</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>ยืนเฉย ๆ หายใจเด้ง</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>C-XX-1.png</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>Turn the person in the attached photo(s) into a cute chibi mascot character for a TikTok live streamer. Keep their recognizable features so they can tell it is them: face shape, hairstyle and hair color, eye shape, eyebrows, glasses or accessories, beauty marks. Outfit: [OUTFIT]. Full body, front view, standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Centered, 2.5 heads tall, big sparkly eyes open, soft blush cheeks, gentle smile with mouth closed. Soft 3D pastel style like a vinyl toy, smooth shading, clean outline, kawaii — same art style as the reference character image if one is attached. Transparent background, no shadow on ground, no text, single character only, 1024x1024.</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="70" customHeight="1">
-      <c r="A17" s="9" t="n">
+    <row r="17" ht="69.95" customHeight="1" s="12">
+      <c r="A17" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>หลับตา</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>กะพริบตา</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>C-XX-2.png</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
-        <is>
-          <t>Same character, same outfit, exact same pose, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: eyes gently closed as if blinking. Gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="70" customHeight="1">
-      <c r="A18" s="9" t="n">
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>Same character, same outfit, exact same pose, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: eyes gently closed as if blinking. Gentle smile with mouth closed. Transparent background, no text, 1024x1024. IMPORTANT for animation: keep the head exactly the same size and at the same height in the frame as the first image, do not zoom in or out, feet at the same ground line, and keep the outfit colors and lighting identical (same pink shade, same brightness).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="69.95" customHeight="1" s="12">
+      <c r="A18" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>อ้าปาก</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>ขยับปากตอนอ่านแชท</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>C-XX-3.png</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
-        <is>
-          <t>Same character, same outfit, exact same pose, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: mouth open happily as if talking "ah". Eyes open. Transparent background, no text, 1024x1024.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="70" customHeight="1">
-      <c r="A19" s="9" t="n">
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>Same character, same outfit, exact same pose, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: eyes gently closed as if blinking. Gentle smile with mouth closed. Transparent background, no text, 1024x1024. IMPORTANT for animation: keep the head exactly the same size and at the same height in the frame as the first image, do not zoom in or out, feet at the same ground line, and keep the outfit colors and lighting identical (same pink shade, same brightness).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="69.95" customHeight="1" s="12">
+      <c r="A19" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>ผมปลิวซ้าย</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>สลับกับ 5 ให้ผมพลิ้ว</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D19" s="11" t="inlineStr">
         <is>
           <t>C-XX-4.png</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr">
-        <is>
-          <t>Same character, same outfit, exact same pose, body, face, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: hair and hair accessories gently swaying to the LEFT as if blown by a soft breeze (only hair tips, strands and ribbons shift slightly left). Eyes open, gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="70" customHeight="1">
-      <c r="A20" s="9" t="n">
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>Same character, same outfit, exact same pose, body, face, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: hair and hair accessories gently swaying to the LEFT as if blown by a soft breeze (only hair tips, strands and ribbons shift slightly left). Eyes open, gentle smile with mouth closed. Transparent background, no text, 1024x1024. IMPORTANT for animation: keep the head exactly the same size and at the same height in the frame as the first image, do not zoom in or out, feet at the same ground line, and keep the outfit colors and lighting identical (same pink shade, same brightness).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="69.95" customHeight="1" s="12">
+      <c r="A20" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>ผมปลิวขวา</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>สลับกับ 4 ให้ผมพลิ้ว</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D20" s="11" t="inlineStr">
         <is>
           <t>C-XX-5.png</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>Same character, same outfit, exact same pose, body, face, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: hair and hair accessories gently swaying to the RIGHT as if blown by a soft breeze (only hair tips, strands and ribbons shift slightly right). Eyes open, gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="70" customHeight="1">
-      <c r="A21" s="9" t="n">
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>Same character, same outfit, exact same pose, body, face, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: hair and hair accessories gently swaying to the RIGHT as if blown by a soft breeze (only hair tips, strands and ribbons shift slightly right). Eyes open, gentle smile with mouth closed. Transparent background, no text, 1024x1024. IMPORTANT for animation: keep the head exactly the same size and at the same height in the frame as the first image, do not zoom in or out, feet at the same ground line, and keep the outfit colors and lighting identical (same pink shade, same brightness).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="69.95" customHeight="1" s="12">
+      <c r="A21" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>รับของขวัญ 🎁 (มือว่าง)</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C21" s="11" t="inlineStr">
         <is>
           <t>ได้กิฟต์ — ระบบวางรูปกิฟต์จริงในมือ</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="D21" s="11" t="inlineStr">
         <is>
           <t>C-XX-6.png</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>Same character, same outfit, same size, position and framing as the first image — new pose: happily ready to catch a gift, both hands cupped together in front of the chest with palms facing up, empty hands, not holding anything (no gift box, no props), clear empty space above the palms, eyes sparkling looking at the hands, big happy smile with mouth open, slight lean forward. Transparent background, no text, 1024x1024.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="70" customHeight="1">
-      <c r="A22" s="9" t="n">
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>Same character, same outfit, same size, position and framing as the first image — new pose: happily ready to catch a gift, both hands cupped together in front of the chest with palms facing up, empty hands, not holding anything (no gift box, no props), clear empty space above the palms, eyes sparkling looking at the hands, big happy smile with mouth open, slight lean forward. Transparent background, no text, 1024x1024. IMPORTANT for animation: keep the head exactly the same size and at the same height in the frame as the first image, do not zoom in or out, feet at the same ground line, and keep the outfit colors and lighting identical (same pink shade, same brightness).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="69.95" customHeight="1" s="12">
+      <c r="A22" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>ดีใจสุด ๆ 🎉</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>ได้กิฟต์ใหญ่</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D22" s="11" t="inlineStr">
         <is>
           <t>C-XX-7.png</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>Same character, same outfit, same size, position and framing as the first image — new pose: super excited jumping pose, both arms raised high in celebration, empty hands, not holding anything (no gift box, no props), eyes closed happily (^ ^), wide open smile, tiny hearts and sparkles around the head. Transparent background, no text, 1024x1024.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="70" customHeight="1">
-      <c r="A23" s="9" t="n">
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>Same character, same outfit, same size, position and framing as the first image — new pose: super excited jumping pose, both arms raised high in celebration, empty hands, not holding anything (no gift box, no props), eyes closed happily (^ ^), wide open smile, tiny hearts and sparkles around the head. Transparent background, no text, 1024x1024. IMPORTANT for animation: keep the head exactly the same size and at the same height in the frame as the first image, do not zoom in or out, feet at the same ground line, and keep the outfit colors and lighting identical (same pink shade, same brightness).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="69.95" customHeight="1" s="12">
+      <c r="A23" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>ส่งหัวใจ 😘</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>มีคนติดตาม / Finger Heart</t>
         </is>
       </c>
-      <c r="D23" s="9" t="inlineStr">
+      <c r="D23" s="11" t="inlineStr">
         <is>
           <t>C-XX-8.png</t>
         </is>
       </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>Same character, same outfit, same size, position and framing as the first image — new pose: making a finger heart toward the viewer with one hand near the cheek, other arm relaxed, not holding anything else (no gift box, no props), winking, cute blush, small smile. Transparent background, no text, 1024x1024.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="70" customHeight="1">
-      <c r="A24" s="9" t="n">
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>Same character, same outfit, same size, position and framing as the first image — new pose: making a finger heart toward the viewer with one hand near the cheek, other arm relaxed, not holding anything else (no gift box, no props), winking, cute blush, small smile. Transparent background, no text, 1024x1024. IMPORTANT for animation: keep the head exactly the same size and at the same height in the frame as the first image, do not zoom in or out, feet at the same ground line, and keep the outfit colors and lighting identical (same pink shade, same brightness).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="69.95" customHeight="1" s="12">
+      <c r="A24" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>เต้น ท่า A 💃</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C24" s="11" t="inlineStr">
         <is>
           <t>Action เต้น (สลับ 9→10→11)</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="D24" s="11" t="inlineStr">
         <is>
           <t>C-XX-9.png</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance move — body leaning to the LEFT, left arm raised up with index finger pointing to the sky, right hand on hip, right knee slightly bent, empty hands, not holding anything (no gift box, no props), cheerful open smile, small music notes around. Transparent background, no text, 1024x1024.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="70" customHeight="1">
-      <c r="A25" s="9" t="n">
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance move — body leaning to the LEFT, left arm raised up with index finger pointing to the sky, right hand on hip, right knee slightly bent, empty hands, not holding anything (no gift box, no props), cheerful open smile, small music notes around. Transparent background, no text, 1024x1024. IMPORTANT for animation: keep the head exactly the same size and at the same height in the frame as the first image, do not zoom in or out, feet at the same ground line, and keep the outfit colors and lighting identical (same pink shade, same brightness).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="69.95" customHeight="1" s="12">
+      <c r="A25" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="B25" s="9" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>เต้น ท่า B 💃</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="C25" s="11" t="inlineStr">
         <is>
           <t>Action เต้น (สลับ 9→10→11)</t>
         </is>
       </c>
-      <c r="D25" s="9" t="inlineStr">
+      <c r="D25" s="11" t="inlineStr">
         <is>
           <t>C-XX-10.png</t>
         </is>
       </c>
-      <c r="E25" s="9" t="inlineStr">
-        <is>
-          <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance move — body leaning to the RIGHT, right arm raised up with index finger pointing to the sky, left hand on hip, left knee slightly bent, empty hands, not holding anything (no gift box, no props), cheerful open smile, small music notes around. Transparent background, no text, 1024x1024.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="70" customHeight="1">
-      <c r="A26" s="9" t="n">
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance move — body leaning to the RIGHT, right arm raised up with index finger pointing to the sky, left hand on hip, left knee slightly bent, empty hands, not holding anything (no gift box, no props), cheerful open smile, small music notes around. Transparent background, no text, 1024x1024. IMPORTANT for animation: keep the head exactly the same size and at the same height in the frame as the first image, do not zoom in or out, feet at the same ground line, and keep the outfit colors and lighting identical (same pink shade, same brightness).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="69.95" customHeight="1" s="12">
+      <c r="A26" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>เต้น ท่า C 💃</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C26" s="11" t="inlineStr">
         <is>
           <t>Action เต้น (ท่าจบ)</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
+      <c r="D26" s="11" t="inlineStr">
         <is>
           <t>C-XX-11.png</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance finishing pose — both hands making peace signs (V) next to the face, one foot kicked up behind, empty hands, not holding anything (no gift box, no props), winking with a big smile, sparkles around. Transparent background, no text, 1024x1024.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="70" customHeight="1">
-      <c r="A27" s="9" t="n">
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance finishing pose — both hands making peace signs (V) next to the face, one foot kicked up behind, empty hands, not holding anything (no gift box, no props), winking with a big smile, sparkles around. Transparent background, no text, 1024x1024. IMPORTANT for animation: keep the head exactly the same size and at the same height in the frame as the first image, do not zoom in or out, feet at the same ground line, and keep the outfit colors and lighting identical (same pink shade, same brightness).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="69.95" customHeight="1" s="12">
+      <c r="A27" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>เดิน ก้าวซ้าย 🚶</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C27" s="11" t="inlineStr">
         <is>
           <t>Action เดินมาส่งจุ๊บ (สลับ 12↔13 ตอนเดินเข้า)</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="D27" s="11" t="inlineStr">
         <is>
           <t>C-XX-12.png</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t>Same character, same outfit, same size, position and framing as the first image — new pose: walking toward the viewer, front view, LEFT foot stepping forward, right arm swinging forward and left arm back, empty hands, not holding anything (no gift box, no props), happy smile, slight bounce. Transparent background, no text, 1024x1024.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="70" customHeight="1">
-      <c r="A28" s="9" t="n">
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>Same character, same outfit, same size, position and framing as the first image — new pose: walking toward the viewer, front view, LEFT foot stepping forward, right arm swinging forward and left arm back, empty hands, not holding anything (no gift box, no props), happy smile, slight bounce. Transparent background, no text, 1024x1024. IMPORTANT for animation: keep the head exactly the same size and at the same height in the frame as the first image, do not zoom in or out, feet at the same ground line, and keep the outfit colors and lighting identical (same pink shade, same brightness).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="69.95" customHeight="1" s="12">
+      <c r="A28" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="B28" s="9" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>เดิน ก้าวขวา 🚶</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="C28" s="11" t="inlineStr">
         <is>
           <t>Action เดินมาส่งจุ๊บ (สลับ 12↔13 ตอนเดินเข้า)</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr">
+      <c r="D28" s="11" t="inlineStr">
         <is>
           <t>C-XX-13.png</t>
         </is>
       </c>
-      <c r="E28" s="9" t="inlineStr">
-        <is>
-          <t>Same character, same outfit, same size, position and framing as the first image — new pose: walking toward the viewer, front view, RIGHT foot stepping forward, left arm swinging forward and right arm back, empty hands, not holding anything (no gift box, no props), happy smile, slight bounce. Transparent background, no text, 1024x1024.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="70" customHeight="1">
-      <c r="A29" s="9" t="n">
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>Same character, same outfit, same size, position and framing as the first image — new pose: walking toward the viewer, front view, RIGHT foot stepping forward, left arm swinging forward and right arm back, empty hands, not holding anything (no gift box, no props), happy smile, slight bounce. Transparent background, no text, 1024x1024. IMPORTANT for animation: keep the head exactly the same size and at the same height in the frame as the first image, do not zoom in or out, feet at the same ground line, and keep the outfit colors and lighting identical (same pink shade, same brightness).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="69.95" customHeight="1" s="12">
+      <c r="A29" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="B29" s="9" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>ส่งจุ๊บ 💋 (ท่าเตรียม)</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C29" s="11" t="inlineStr">
         <is>
           <t>Action เดินมาส่งจุ๊บ — มือแตะปาก</t>
         </is>
       </c>
-      <c r="D29" s="9" t="inlineStr">
+      <c r="D29" s="11" t="inlineStr">
         <is>
           <t>C-XX-14.png</t>
         </is>
       </c>
-      <c r="E29" s="9" t="inlineStr">
-        <is>
-          <t>Same character, same outfit, same size, position and framing as the first image — new pose: close to the viewer, front view, one hand touching the lips about to blow a kiss, eyes gently closed, cute blush, other arm relaxed, not holding anything else (no gift box, no props). Transparent background, no text, 1024x1024.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="70" customHeight="1">
-      <c r="A30" s="9" t="n">
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>Same character, same outfit, same size, position and framing as the first image — new pose: close to the viewer, front view, one hand touching the lips about to blow a kiss, eyes gently closed, cute blush, other arm relaxed, not holding anything else (no gift box, no props). Transparent background, no text, 1024x1024. IMPORTANT for animation: keep the head exactly the same size and at the same height in the frame as the first image, do not zoom in or out, feet at the same ground line, and keep the outfit colors and lighting identical (same pink shade, same brightness).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="69.95" customHeight="1" s="12">
+      <c r="A30" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>ส่งจุ๊บ 💋 (ปล่อยจุ๊บ)</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C30" s="11" t="inlineStr">
         <is>
           <t>Action เดินมาส่งจุ๊บ — ปล่อยหัวใจ</t>
         </is>
       </c>
-      <c r="D30" s="9" t="inlineStr">
+      <c r="D30" s="11" t="inlineStr">
         <is>
           <t>C-XX-15.png</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>Same character, same outfit, same size, position and framing as the first image — new pose: blowing a kiss toward the viewer, arm stretched forward with open palm from the lips, lips puckered, winking, cute blush, a small pink heart floating out from the hand, not holding anything else (no gift box, no props). Transparent background, no text, 1024x1024.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="70" customHeight="1">
-      <c r="A31" s="9" t="n">
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>Same character, same outfit, same size, position and framing as the first image — new pose: blowing a kiss toward the viewer, arm stretched forward with open palm from the lips, lips puckered, winking, cute blush, a small pink heart floating out from the hand, not holding anything else (no gift box, no props). Transparent background, no text, 1024x1024. IMPORTANT for animation: keep the head exactly the same size and at the same height in the frame as the first image, do not zoom in or out, feet at the same ground line, and keep the outfit colors and lighting identical (same pink shade, same brightness).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="69.95" customHeight="1" s="12">
+      <c r="A31" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="B31" s="9" t="inlineStr">
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t>เดินกลับ (หันหลัง) 🚶</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
+      <c r="C31" s="11" t="inlineStr">
         <is>
           <t>Action เดินมาส่งจุ๊บ (สลับ 16↔17 ตอนเดินกลับ)</t>
         </is>
       </c>
-      <c r="D31" s="9" t="inlineStr">
+      <c r="D31" s="11" t="inlineStr">
         <is>
           <t>C-XX-16.png</t>
         </is>
       </c>
-      <c r="E31" s="9" t="inlineStr">
-        <is>
-          <t>Same character, same outfit, same size, position and framing as the first image — new pose: back view, walking away from the viewer, LEFT foot stepping forward, arms swinging naturally, empty hands, not holding anything (no gift box, no props), showing the back of the outfit and hair. Transparent background, no text, 1024x1024.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="70" customHeight="1">
-      <c r="A32" s="9" t="n">
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>Same character, same outfit, same size, position and framing as the first image — new pose: back view, walking away from the viewer, LEFT foot stepping forward, arms swinging naturally, empty hands, not holding anything (no gift box, no props), showing the back of the outfit and hair. Transparent background, no text, 1024x1024. IMPORTANT for animation: keep the head exactly the same size and at the same height in the frame as the first image, do not zoom in or out, feet at the same ground line, and keep the outfit colors and lighting identical (same pink shade, same brightness).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="69.95" customHeight="1" s="12">
+      <c r="A32" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="B32" s="9" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>เดินกลับ (หันหลัง) ก้าวขวา 🚶</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
+      <c r="C32" s="11" t="inlineStr">
         <is>
           <t>Action เดินมาส่งจุ๊บ (สลับ 16↔17 ตอนเดินกลับ)</t>
         </is>
       </c>
-      <c r="D32" s="9" t="inlineStr">
+      <c r="D32" s="11" t="inlineStr">
         <is>
           <t>C-XX-17.png</t>
         </is>
       </c>
-      <c r="E32" s="9" t="inlineStr">
-        <is>
-          <t>Same character, same outfit, same size, position and framing as the first image — new pose: back view, walking away from the viewer, RIGHT foot stepping forward, arms swinging naturally, empty hands, not holding anything (no gift box, no props), showing the back of the outfit and hair. Transparent background, no text, 1024x1024.</t>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>Same character, same outfit, same size, position and framing as the first image — new pose: back view, walking away from the viewer, RIGHT foot stepping forward, arms swinging naturally, empty hands, not holding anything (no gift box, no props), showing the back of the outfit and hair. Transparent background, no text, 1024x1024. IMPORTANT for animation: keep the head exactly the same size and at the same height in the frame as the first image, do not zoom in or out, feet at the same ground line, and keep the outfit colors and lighting identical (same pink shade, same brightness).</t>
         </is>
       </c>
     </row>
@@ -1274,14 +1308,14 @@
     <mergeCell ref="A12:E12"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A14:E14"/>
     <mergeCell ref="A7:E7"/>
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A8:E8"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A14:E14"/>
     <mergeCell ref="A6:E6"/>
     <mergeCell ref="A9:E9"/>
     <mergeCell ref="A3:E3"/>
@@ -1296,775 +1330,89 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="90" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" style="12" min="1" max="1"/>
+    <col width="14" customWidth="1" style="12" min="2" max="2"/>
+    <col width="18" customWidth="1" style="12" min="3" max="3"/>
+    <col width="40" customWidth="1" style="12" min="4" max="4"/>
+    <col width="50" customWidth="1" style="12" min="5" max="5"/>
+    <col width="45" customWidth="1" style="12" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>รหัส</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>เพศ</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>ธีม</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>[CHARACTER] (คำที่ใส่ในคำสั่ง 1)</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>เสร็จแล้ว ✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>G1</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>ผู้หญิง</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>🐰 กระต่ายหวาน</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>girl with long pink twin-tails, white bunny-ear hoodie with pink bows, pastel pink skirt</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>✓ 17/17 ครบ</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>G2</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>ผู้หญิง</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>⭐ ไอดอลดาว</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>girl with lavender bob hair and star hairclips, sparkly idol stage dress with stars</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>✓ 17/17 ครบ</t>
+      <c r="B1" s="16" t="inlineStr">
+        <is>
+          <t>วันที่ส่งมอบ</t>
+        </is>
+      </c>
+      <c r="C1" s="16" t="inlineStr">
+        <is>
+          <t>ท่า</t>
+        </is>
+      </c>
+      <c r="D1" s="16" t="inlineStr">
+        <is>
+          <t>สถานะบนเว็บ</t>
+        </is>
+      </c>
+      <c r="E1" s="16" t="inlineStr">
+        <is>
+          <t>หมายเหตุ</t>
+        </is>
+      </c>
+      <c r="F1" s="16" t="inlineStr">
+        <is>
+          <t>ไฟล์</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="60" customHeight="1" s="12">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>Cplai</t>
+        </is>
+      </c>
+      <c r="B2" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="C2" s="11" t="inlineStr">
+        <is>
+          <t>17/17 (+ท่าเสริม 1)</t>
+        </is>
+      </c>
+      <c r="D2" s="11" t="inlineStr">
+        <is>
+          <t>✓ ขึ้นเว็บแล้ว — เห็นเฉพาะบัญชีเจ้าของ (แอดมินเห็นในแท็บ "มาสคอตสั่งทำ")</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>รูปที่ Gen มาซูมไม่เท่ากัน → ทาบทุกท่ายึดใบหน้า + ปรับความสว่างให้เท่ากัน</t>
+        </is>
+      </c>
+      <c r="F2" s="11" t="inlineStr">
+        <is>
+          <t>ต้นฉบับ docs/mascots/custom/Cplai · บนเว็บ overlay/public/mascot/Cplai</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>G3</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>ผู้หญิง</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>🐱 แมวนักเรียน</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>girl with brown wavy hair, cat-ear headband, cute sailor school uniform with pink ribbon</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>✓ 16/17 (ขาดท่า 14)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>G4</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>ผู้หญิง</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>🔮 แม่มดไพ่ทาโร่</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>girl with mint short hair, small purple witch hat with moon charm, starry cape, tarot theme</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>✓ 17/17 ครบ</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>G5</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>ผู้หญิง</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>🧁 เชฟขนม</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>girl with orange hair buns, white chef hat and frilly pastel apron with strawberry print</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>G6</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>ผู้หญิง</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>🎮 เกมเมอร์สาว</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>girl with blue ponytail, oversized gamer hoodie with pixel hearts, cat-ear headphones</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>✓ 17/17 ครบ</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>G7</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>ผู้หญิง</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>🎤 นักร้อง</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>girl with long golden wavy hair, sparkly pink singer dress, tiny microphone hair clip</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>G8</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>ผู้หญิง</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>🌸 ชุดไทยประยุกต์</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>girl with black hair in a neat bun with jasmine flowers, cute pastel modern Thai traditional dress</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>✓ 17/17 ครบ</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>G9</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>ผู้หญิง</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>🦄 ยูนิคอร์น</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>girl with rainbow pastel hair, unicorn horn headband, fluffy cloud-like pastel dress</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>G10</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>ผู้หญิง</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>🍓 สตรอว์เบอร์รี</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>girl with red bob hair, strawberry beret, red-and-white polka dot dress</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>B1</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>ผู้ชาย</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>🐻 หมีอบอุ่น</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>boy with fluffy brown hair, brown bear-ear hoodie, cream shorts</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>B2</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>ผู้ชาย</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>🎧 ไอดอลหนุ่ม</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>boy with silver hair, cool pastel idol jacket and lavender headphones</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>B3</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>ผู้ชาย</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>🎮 เกมเมอร์</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>boy with black messy hair, gamer hoodie with controller print, gaming headset</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>B4</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>ผู้ชาย</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>👑 เจ้าชาย</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>boy with blond hair, pastel prince outfit with tiny golden crown and short cape</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>✓ 17/17 ครบ</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>B5</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>ผู้ชาย</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>⚽ นักกีฬา</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>boy with red spiky hair, sporty pastel jersey with number 7, sneakers</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>B6</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>ผู้ชาย</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>🦊 จิ้งจอก</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>boy with orange hair, fox-ear hoodie with fluffy tail, cute mittens</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>B7</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>ผู้ชาย</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>🧙 นักเวทย์</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>boy with blue hair, small wizard hat with stars, mint robe</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>✓ 17/17 ครบ</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>B8</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>ผู้ชาย</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>🎸 ร็อกเกอร์น่ารัก</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>boy with purple undercut hair, pastel leather jacket with heart pins, star sunglasses on head</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>✓ 17/17 ครบ</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>B9</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>ผู้ชาย</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>🐶 หมาน้อย</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>boy with light brown curly hair, puppy-ear hoodie with paw print, red collar scarf</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>B10</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>ผู้ชาย</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>🍜 เชฟหนุ่ม</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>boy with dark green hair, white chef jacket and tall chef hat, pastel apron</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>✓ 17/17 ครบ</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>B11</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>ผู้ชาย</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>🐰 กระต่ายหนุ่ม</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>boy with white fluffy hair, pastel blue bunny-ear hoodie, cute carrot pin</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>B12</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>ผู้ชาย</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>🌙 ลูกแมวดำ</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>boy with black hair and black cat ears, oversized lavender sweater with moon print</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>B13</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>ผู้ชาย</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>🎓 นักเรียนเรียบร้อย</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>boy with neat brown hair and round glasses, pastel school blazer with bow tie</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>B14</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>ผู้ชาย</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>💃 แดนเซอร์</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>boy with pink-dyed messy hair, pastel street dance outfit, bucket hat and baggy pants</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>B15</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>ผู้ชาย</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>🐼 แพนด้า</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>boy with black-and-white hair, panda-ear hoodie, bamboo-print shorts</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>B16</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>ผู้ชาย</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>🍰 คาเฟ่บอย</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>boy with soft caramel hair, barista apron over cream shirt, latte-art badge</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>B17</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>ผู้ชาย</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>🏴‍☠️ โจรสลัดน้อย</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>boy with teal hair, cute pirate hat and pastel striped shirt, tiny eyepatch on forehead</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>B18</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>ผู้ชาย</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>🦖 ไดโนน้อย</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>boy with green spiky hair, mint dinosaur hoodie with little spikes on the hood</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>B19</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>ผู้ชาย</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>🎀 เคป๊อปพาสเทล</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>boy with lilac middle-part hair, pastel K-pop stage outfit with pearl chains</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>B20</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>ผู้ชาย</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>🧸 เด็กตุ๊กตาหมี</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>boy with honey blond curly hair, overalls with a teddy bear patch, cream shirt</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>เพิ่มตัวใหม่: ส่งรูป 17 ท่าให้ทีมเว็บ → ผูกกับบัญชีลูกค้าที่ packages/server/src/mascots/custom.ts (ไม่เก็บอีเมลลูกค้าในไฟล์นี้)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2075,17 +1423,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H511"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="110" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" style="12" min="1" max="1"/>
+    <col width="10" customWidth="1" style="12" min="2" max="2"/>
+    <col width="22" customWidth="1" style="12" min="3" max="3"/>
+    <col width="90" customWidth="1" style="12" min="4" max="4"/>
+    <col width="30" customWidth="1" style="12" min="5" max="5"/>
+    <col width="14" customWidth="1" style="12" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2096,37 +1442,27 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>เพศ</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
           <t>ธีม</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>ลำดับ</t>
-        </is>
-      </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>ท่า</t>
+          <t>[CHARACTER] (คำที่ใส่ในคำสั่ง 1)</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>ใช้ตอน</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>ชื่อไฟล์</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>คำสั่ง (คัดลอกไปวางได้เลย)</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>เสร็จ ✓</t>
+          <t>เสร็จแล้ว ✓</t>
+        </is>
+      </c>
+      <c r="F1" s="17" t="inlineStr">
+        <is>
+          <t>อยู่บนเว็บ</t>
         </is>
       </c>
     </row>
@@ -2138,6 +1474,873 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
+          <t>ผู้หญิง</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>🐰 กระต่ายหวาน</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>girl with long pink twin-tails, white bunny-ear hoodie with pink bows, pastel pink skirt</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>✓ 17/17 ครบ</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>✓ ใช้ได้แล้ว</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>ผู้หญิง</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>⭐ ไอดอลดาว</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>girl with lavender bob hair and star hairclips, sparkly idol stage dress with stars</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>✓ 17/17 ครบ</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>✓ ใช้ได้แล้ว</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>G3</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>ผู้หญิง</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>🐱 แมวนักเรียน</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>girl with brown wavy hair, cat-ear headband, cute sailor school uniform with pink ribbon</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>✓ 16/17 (ขาดท่า 14)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>รอท่า 14</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>G4</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>ผู้หญิง</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>🔮 แม่มดไพ่ทาโร่</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>girl with mint short hair, small purple witch hat with moon charm, starry cape, tarot theme</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>✓ 17/17 ครบ</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>✓ ใช้ได้แล้ว</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>ผู้หญิง</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>🧁 เชฟขนม</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>girl with orange hair buns, white chef hat and frilly pastel apron with strawberry print</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>G6</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>ผู้หญิง</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>🎮 เกมเมอร์สาว</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>girl with blue ponytail, oversized gamer hoodie with pixel hearts, cat-ear headphones</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>✓ 17/17 ครบ</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>✓ ใช้ได้แล้ว</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>G7</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>ผู้หญิง</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>🎤 นักร้อง</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>girl with long golden wavy hair, sparkly pink singer dress, tiny microphone hair clip</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>G8</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>ผู้หญิง</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>🌸 ชุดไทยประยุกต์</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>girl with black hair in a neat bun with jasmine flowers, cute pastel modern Thai traditional dress</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>✓ 17/17 ครบ</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>✓ ใช้ได้แล้ว</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>G9</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>ผู้หญิง</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>🦄 ยูนิคอร์น</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>girl with rainbow pastel hair, unicorn horn headband, fluffy cloud-like pastel dress</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n"/>
+      <c r="F10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>G10</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>ผู้หญิง</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>🍓 สตรอว์เบอร์รี</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>girl with red bob hair, strawberry beret, red-and-white polka dot dress</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>ผู้ชาย</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>🐻 หมีอบอุ่น</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>boy with fluffy brown hair, brown bear-ear hoodie, cream shorts</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>ผู้ชาย</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>🎧 ไอดอลหนุ่ม</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>boy with silver hair, cool pastel idol jacket and lavender headphones</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>ผู้ชาย</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>🎮 เกมเมอร์</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>boy with black messy hair, gamer hoodie with controller print, gaming headset</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>ผู้ชาย</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>👑 เจ้าชาย</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>boy with blond hair, pastel prince outfit with tiny golden crown and short cape</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>✓ 17/17 ครบ</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>✓ ใช้ได้แล้ว</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>B5</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>ผู้ชาย</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>⚽ นักกีฬา</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>boy with red spiky hair, sporty pastel jersey with number 7, sneakers</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>ผู้ชาย</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>🦊 จิ้งจอก</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>boy with orange hair, fox-ear hoodie with fluffy tail, cute mittens</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>B7</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>ผู้ชาย</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>🧙 นักเวทย์</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>boy with blue hair, small wizard hat with stars, mint robe</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>✓ 17/17 ครบ</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>✓ ใช้ได้แล้ว</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>B8</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>ผู้ชาย</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>🎸 ร็อกเกอร์น่ารัก</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>boy with purple undercut hair, pastel leather jacket with heart pins, star sunglasses on head</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>✓ 17/17 ครบ</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>✓ ใช้ได้แล้ว</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>B9</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>ผู้ชาย</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>🐶 หมาน้อย</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>boy with light brown curly hair, puppy-ear hoodie with paw print, red collar scarf</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>B10</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>ผู้ชาย</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>🍜 เชฟหนุ่ม</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>boy with dark green hair, white chef jacket and tall chef hat, pastel apron</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>✓ 17/17 ครบ</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>✓ ใช้ได้แล้ว</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>B11</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>ผู้ชาย</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>🐰 กระต่ายหนุ่ม</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>boy with white fluffy hair, pastel blue bunny-ear hoodie, cute carrot pin</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>B12</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>ผู้ชาย</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>🌙 ลูกแมวดำ</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>boy with black hair and black cat ears, oversized lavender sweater with moon print</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>B13</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>ผู้ชาย</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>🎓 นักเรียนเรียบร้อย</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>boy with neat brown hair and round glasses, pastel school blazer with bow tie</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>B14</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>ผู้ชาย</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>💃 แดนเซอร์</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>boy with pink-dyed messy hair, pastel street dance outfit, bucket hat and baggy pants</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>B15</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>ผู้ชาย</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>🐼 แพนด้า</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>boy with black-and-white hair, panda-ear hoodie, bamboo-print shorts</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>B16</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>ผู้ชาย</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>🍰 คาเฟ่บอย</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>boy with soft caramel hair, barista apron over cream shirt, latte-art badge</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>B17</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>ผู้ชาย</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>🏴‍☠️ โจรสลัดน้อย</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>boy with teal hair, cute pirate hat and pastel striped shirt, tiny eyepatch on forehead</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>B18</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>ผู้ชาย</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>🦖 ไดโนน้อย</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>boy with green spiky hair, mint dinosaur hoodie with little spikes on the hood</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="n"/>
+      <c r="F29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>B19</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>ผู้ชาย</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>🎀 เคป๊อปพาสเทล</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>boy with lilac middle-part hair, pastel K-pop stage outfit with pearl chains</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="n"/>
+      <c r="F30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>B20</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>ผู้ชาย</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>🧸 เด็กตุ๊กตาหมี</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>boy with honey blond curly hair, overalls with a teddy bear patch, cream shirt</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E31"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H511"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" style="12" min="1" max="1"/>
+    <col width="20" customWidth="1" style="12" min="2" max="2"/>
+    <col width="7" customWidth="1" style="12" min="3" max="3"/>
+    <col width="18" customWidth="1" style="12" min="4" max="4"/>
+    <col width="24" customWidth="1" style="12" min="5" max="5"/>
+    <col width="12" customWidth="1" style="12" min="6" max="6"/>
+    <col width="110" customWidth="1" style="12" min="7" max="7"/>
+    <col width="8" customWidth="1" style="12" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>รหัส</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>ธีม</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>ลำดับ</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>ท่า</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>ใช้ตอน</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>ชื่อไฟล์</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>คำสั่ง (คัดลอกไปวางได้เลย)</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>เสร็จ ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="75" customHeight="1" s="12">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
           <t>🐰 กระต่ายหวาน</t>
         </is>
       </c>
@@ -2170,7 +2373,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="45" customHeight="1" s="12">
       <c r="A3" s="5" t="inlineStr">
         <is>
           <t>G1</t>
@@ -2210,7 +2413,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="45" customHeight="1" s="12">
       <c r="A4" s="5" t="inlineStr">
         <is>
           <t>G1</t>
@@ -2250,7 +2453,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="60" customHeight="1" s="12">
       <c r="A5" s="5" t="inlineStr">
         <is>
           <t>G1</t>
@@ -2290,7 +2493,7 @@
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="60" customHeight="1" s="12">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>G1</t>
@@ -2330,7 +2533,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="60" customHeight="1" s="12">
       <c r="A7" s="5" t="inlineStr">
         <is>
           <t>G1</t>
@@ -2370,7 +2573,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="45" customHeight="1" s="12">
       <c r="A8" s="5" t="inlineStr">
         <is>
           <t>G1</t>
@@ -2410,7 +2613,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="45" customHeight="1" s="12">
       <c r="A9" s="5" t="inlineStr">
         <is>
           <t>G1</t>
@@ -2450,7 +2653,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="60" customHeight="1" s="12">
       <c r="A10" s="5" t="inlineStr">
         <is>
           <t>G1</t>
@@ -2490,7 +2693,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="60" customHeight="1" s="12">
       <c r="A11" s="5" t="inlineStr">
         <is>
           <t>G1</t>
@@ -2530,7 +2733,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="45" customHeight="1" s="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
           <t>G1</t>
@@ -2570,7 +2773,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="45" customHeight="1" s="12">
       <c r="A13" s="5" t="inlineStr">
         <is>
           <t>G1</t>
@@ -2610,7 +2813,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="45" customHeight="1" s="12">
       <c r="A14" s="5" t="inlineStr">
         <is>
           <t>G1</t>
@@ -2650,7 +2853,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="45" customHeight="1" s="12">
       <c r="A15" s="5" t="inlineStr">
         <is>
           <t>G1</t>
@@ -2690,7 +2893,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="60" customHeight="1" s="12">
       <c r="A16" s="5" t="inlineStr">
         <is>
           <t>G1</t>
@@ -2730,7 +2933,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="45" customHeight="1" s="12">
       <c r="A17" s="5" t="inlineStr">
         <is>
           <t>G1</t>
@@ -2770,7 +2973,7 @@
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="45" customHeight="1" s="12">
       <c r="A18" s="5" t="inlineStr">
         <is>
           <t>G1</t>
@@ -2810,7 +3013,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="75" customHeight="1" s="12">
       <c r="A19" s="5" t="inlineStr">
         <is>
           <t>G2</t>
@@ -2850,7 +3053,7 @@
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="45" customHeight="1" s="12">
       <c r="A20" s="5" t="inlineStr">
         <is>
           <t>G2</t>
@@ -2890,7 +3093,7 @@
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="45" customHeight="1" s="12">
       <c r="A21" s="5" t="inlineStr">
         <is>
           <t>G2</t>
@@ -2930,7 +3133,7 @@
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="60" customHeight="1" s="12">
       <c r="A22" s="5" t="inlineStr">
         <is>
           <t>G2</t>
@@ -2970,7 +3173,7 @@
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="60" customHeight="1" s="12">
       <c r="A23" s="5" t="inlineStr">
         <is>
           <t>G2</t>
@@ -3010,7 +3213,7 @@
         </is>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="60" customHeight="1" s="12">
       <c r="A24" s="5" t="inlineStr">
         <is>
           <t>G2</t>
@@ -3050,7 +3253,7 @@
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="45" customHeight="1" s="12">
       <c r="A25" s="5" t="inlineStr">
         <is>
           <t>G2</t>
@@ -3090,7 +3293,7 @@
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="45" customHeight="1" s="12">
       <c r="A26" s="5" t="inlineStr">
         <is>
           <t>G2</t>
@@ -3130,7 +3333,7 @@
         </is>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="60" customHeight="1" s="12">
       <c r="A27" s="5" t="inlineStr">
         <is>
           <t>G2</t>
@@ -3170,7 +3373,7 @@
         </is>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="60" customHeight="1" s="12">
       <c r="A28" s="5" t="inlineStr">
         <is>
           <t>G2</t>
@@ -3210,7 +3413,7 @@
         </is>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="45" customHeight="1" s="12">
       <c r="A29" s="5" t="inlineStr">
         <is>
           <t>G2</t>
@@ -3250,7 +3453,7 @@
         </is>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="45" customHeight="1" s="12">
       <c r="A30" s="5" t="inlineStr">
         <is>
           <t>G2</t>
@@ -3290,7 +3493,7 @@
         </is>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="45" customHeight="1" s="12">
       <c r="A31" s="5" t="inlineStr">
         <is>
           <t>G2</t>
@@ -3330,7 +3533,7 @@
         </is>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="45" customHeight="1" s="12">
       <c r="A32" s="5" t="inlineStr">
         <is>
           <t>G2</t>
@@ -3370,7 +3573,7 @@
         </is>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="60" customHeight="1" s="12">
       <c r="A33" s="5" t="inlineStr">
         <is>
           <t>G2</t>
@@ -3410,7 +3613,7 @@
         </is>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="45" customHeight="1" s="12">
       <c r="A34" s="5" t="inlineStr">
         <is>
           <t>G2</t>
@@ -3450,7 +3653,7 @@
         </is>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="45" customHeight="1" s="12">
       <c r="A35" s="5" t="inlineStr">
         <is>
           <t>G2</t>
@@ -3490,7 +3693,7 @@
         </is>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="75" customHeight="1" s="12">
       <c r="A36" s="5" t="inlineStr">
         <is>
           <t>G3</t>
@@ -3530,7 +3733,7 @@
         </is>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="45" customHeight="1" s="12">
       <c r="A37" s="5" t="inlineStr">
         <is>
           <t>G3</t>
@@ -3570,7 +3773,7 @@
         </is>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="45" customHeight="1" s="12">
       <c r="A38" s="5" t="inlineStr">
         <is>
           <t>G3</t>
@@ -3610,7 +3813,7 @@
         </is>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="60" customHeight="1" s="12">
       <c r="A39" s="5" t="inlineStr">
         <is>
           <t>G3</t>
@@ -3650,7 +3853,7 @@
         </is>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="60" customHeight="1" s="12">
       <c r="A40" s="5" t="inlineStr">
         <is>
           <t>G3</t>
@@ -3690,7 +3893,7 @@
         </is>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="60" customHeight="1" s="12">
       <c r="A41" s="5" t="inlineStr">
         <is>
           <t>G3</t>
@@ -3730,7 +3933,7 @@
         </is>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="45" customHeight="1" s="12">
       <c r="A42" s="5" t="inlineStr">
         <is>
           <t>G3</t>
@@ -3770,7 +3973,7 @@
         </is>
       </c>
     </row>
-    <row r="43">
+    <row r="43" ht="45" customHeight="1" s="12">
       <c r="A43" s="5" t="inlineStr">
         <is>
           <t>G3</t>
@@ -3810,7 +4013,7 @@
         </is>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="60" customHeight="1" s="12">
       <c r="A44" s="5" t="inlineStr">
         <is>
           <t>G3</t>
@@ -3850,7 +4053,7 @@
         </is>
       </c>
     </row>
-    <row r="45">
+    <row r="45" ht="60" customHeight="1" s="12">
       <c r="A45" s="5" t="inlineStr">
         <is>
           <t>G3</t>
@@ -3890,7 +4093,7 @@
         </is>
       </c>
     </row>
-    <row r="46">
+    <row r="46" ht="45" customHeight="1" s="12">
       <c r="A46" s="5" t="inlineStr">
         <is>
           <t>G3</t>
@@ -3930,7 +4133,7 @@
         </is>
       </c>
     </row>
-    <row r="47">
+    <row r="47" ht="45" customHeight="1" s="12">
       <c r="A47" s="5" t="inlineStr">
         <is>
           <t>G3</t>
@@ -3970,7 +4173,7 @@
         </is>
       </c>
     </row>
-    <row r="48">
+    <row r="48" ht="45" customHeight="1" s="12">
       <c r="A48" s="5" t="inlineStr">
         <is>
           <t>G3</t>
@@ -4010,7 +4213,7 @@
         </is>
       </c>
     </row>
-    <row r="49">
+    <row r="49" ht="45" customHeight="1" s="12">
       <c r="A49" s="7" t="inlineStr">
         <is>
           <t>G3</t>
@@ -4050,7 +4253,7 @@
         </is>
       </c>
     </row>
-    <row r="50">
+    <row r="50" ht="60" customHeight="1" s="12">
       <c r="A50" s="5" t="inlineStr">
         <is>
           <t>G3</t>
@@ -4090,7 +4293,7 @@
         </is>
       </c>
     </row>
-    <row r="51">
+    <row r="51" ht="45" customHeight="1" s="12">
       <c r="A51" s="5" t="inlineStr">
         <is>
           <t>G3</t>
@@ -4130,7 +4333,7 @@
         </is>
       </c>
     </row>
-    <row r="52">
+    <row r="52" ht="45" customHeight="1" s="12">
       <c r="A52" s="5" t="inlineStr">
         <is>
           <t>G3</t>
@@ -4170,7 +4373,7 @@
         </is>
       </c>
     </row>
-    <row r="53">
+    <row r="53" ht="75" customHeight="1" s="12">
       <c r="A53" s="5" t="inlineStr">
         <is>
           <t>G4</t>
@@ -4210,7 +4413,7 @@
         </is>
       </c>
     </row>
-    <row r="54">
+    <row r="54" ht="45" customHeight="1" s="12">
       <c r="A54" s="5" t="inlineStr">
         <is>
           <t>G4</t>
@@ -4250,7 +4453,7 @@
         </is>
       </c>
     </row>
-    <row r="55">
+    <row r="55" ht="45" customHeight="1" s="12">
       <c r="A55" s="5" t="inlineStr">
         <is>
           <t>G4</t>
@@ -4290,7 +4493,7 @@
         </is>
       </c>
     </row>
-    <row r="56">
+    <row r="56" ht="60" customHeight="1" s="12">
       <c r="A56" s="5" t="inlineStr">
         <is>
           <t>G4</t>
@@ -4330,7 +4533,7 @@
         </is>
       </c>
     </row>
-    <row r="57">
+    <row r="57" ht="60" customHeight="1" s="12">
       <c r="A57" s="5" t="inlineStr">
         <is>
           <t>G4</t>
@@ -4370,7 +4573,7 @@
         </is>
       </c>
     </row>
-    <row r="58">
+    <row r="58" ht="60" customHeight="1" s="12">
       <c r="A58" s="5" t="inlineStr">
         <is>
           <t>G4</t>
@@ -4410,7 +4613,7 @@
         </is>
       </c>
     </row>
-    <row r="59">
+    <row r="59" ht="45" customHeight="1" s="12">
       <c r="A59" s="5" t="inlineStr">
         <is>
           <t>G4</t>
@@ -4450,7 +4653,7 @@
         </is>
       </c>
     </row>
-    <row r="60">
+    <row r="60" ht="45" customHeight="1" s="12">
       <c r="A60" s="5" t="inlineStr">
         <is>
           <t>G4</t>
@@ -4490,7 +4693,7 @@
         </is>
       </c>
     </row>
-    <row r="61">
+    <row r="61" ht="60" customHeight="1" s="12">
       <c r="A61" s="5" t="inlineStr">
         <is>
           <t>G4</t>
@@ -4530,7 +4733,7 @@
         </is>
       </c>
     </row>
-    <row r="62">
+    <row r="62" ht="60" customHeight="1" s="12">
       <c r="A62" s="5" t="inlineStr">
         <is>
           <t>G4</t>
@@ -4570,7 +4773,7 @@
         </is>
       </c>
     </row>
-    <row r="63">
+    <row r="63" ht="45" customHeight="1" s="12">
       <c r="A63" s="5" t="inlineStr">
         <is>
           <t>G4</t>
@@ -4610,7 +4813,7 @@
         </is>
       </c>
     </row>
-    <row r="64">
+    <row r="64" ht="45" customHeight="1" s="12">
       <c r="A64" s="5" t="inlineStr">
         <is>
           <t>G4</t>
@@ -4650,7 +4853,7 @@
         </is>
       </c>
     </row>
-    <row r="65">
+    <row r="65" ht="45" customHeight="1" s="12">
       <c r="A65" s="5" t="inlineStr">
         <is>
           <t>G4</t>
@@ -4690,7 +4893,7 @@
         </is>
       </c>
     </row>
-    <row r="66">
+    <row r="66" ht="45" customHeight="1" s="12">
       <c r="A66" s="5" t="inlineStr">
         <is>
           <t>G4</t>
@@ -4730,7 +4933,7 @@
         </is>
       </c>
     </row>
-    <row r="67">
+    <row r="67" ht="60" customHeight="1" s="12">
       <c r="A67" s="5" t="inlineStr">
         <is>
           <t>G4</t>
@@ -4770,7 +4973,7 @@
         </is>
       </c>
     </row>
-    <row r="68">
+    <row r="68" ht="45" customHeight="1" s="12">
       <c r="A68" s="5" t="inlineStr">
         <is>
           <t>G4</t>
@@ -4810,7 +5013,7 @@
         </is>
       </c>
     </row>
-    <row r="69">
+    <row r="69" ht="45" customHeight="1" s="12">
       <c r="A69" s="5" t="inlineStr">
         <is>
           <t>G4</t>
@@ -4850,7 +5053,7 @@
         </is>
       </c>
     </row>
-    <row r="70">
+    <row r="70" ht="75" customHeight="1" s="12">
       <c r="A70" s="3" t="inlineStr">
         <is>
           <t>G5</t>
@@ -4884,9 +5087,9 @@
           <t>Cute chibi mascot character for a TikTok live streamer, girl with orange hair buns, white chef hat and frilly pastel apron with strawberry print. Full body, front view, standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Centered, 2.5 heads tall, big sparkly eyes open, soft blush cheeks, gentle smile with mouth closed. Soft 3D pastel style like a vinyl toy, smooth shading, clean outline, pink-lavender-mint palette, kawaii. Transparent background, no shadow on ground, no text, single character only, 1024x1024.</t>
         </is>
       </c>
-      <c r="H70" s="3" t="inlineStr"/>
-    </row>
-    <row r="71">
+      <c r="H70" s="3" t="n"/>
+    </row>
+    <row r="71" ht="45" customHeight="1" s="12">
       <c r="A71" s="3" t="inlineStr">
         <is>
           <t>G5</t>
@@ -4920,9 +5123,9 @@
           <t>Same character, same outfit, exact same pose, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: eyes gently closed as if blinking. Gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H71" s="3" t="inlineStr"/>
-    </row>
-    <row r="72">
+      <c r="H71" s="3" t="n"/>
+    </row>
+    <row r="72" ht="45" customHeight="1" s="12">
       <c r="A72" s="3" t="inlineStr">
         <is>
           <t>G5</t>
@@ -4956,9 +5159,9 @@
           <t>Same character, same outfit, exact same pose, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: mouth open happily as if talking "ah". Eyes open. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H72" s="3" t="inlineStr"/>
-    </row>
-    <row r="73">
+      <c r="H72" s="3" t="n"/>
+    </row>
+    <row r="73" ht="60" customHeight="1" s="12">
       <c r="A73" s="3" t="inlineStr">
         <is>
           <t>G5</t>
@@ -4992,9 +5195,9 @@
           <t>Same character, same outfit, exact same pose, body, face, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: hair and hair accessories gently swaying to the LEFT as if blown by a soft breeze (only hair tips, strands and ribbons shift slightly left). Eyes open, gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H73" s="3" t="inlineStr"/>
-    </row>
-    <row r="74">
+      <c r="H73" s="3" t="n"/>
+    </row>
+    <row r="74" ht="60" customHeight="1" s="12">
       <c r="A74" s="3" t="inlineStr">
         <is>
           <t>G5</t>
@@ -5028,9 +5231,9 @@
           <t>Same character, same outfit, exact same pose, body, face, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: hair and hair accessories gently swaying to the RIGHT as if blown by a soft breeze (only hair tips, strands and ribbons shift slightly right). Eyes open, gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H74" s="3" t="inlineStr"/>
-    </row>
-    <row r="75">
+      <c r="H74" s="3" t="n"/>
+    </row>
+    <row r="75" ht="60" customHeight="1" s="12">
       <c r="A75" s="3" t="inlineStr">
         <is>
           <t>G5</t>
@@ -5064,9 +5267,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: happily ready to catch a gift, both hands cupped together in front of the chest with palms facing up, empty hands, not holding anything (no gift box, no props), clear empty space above the palms, eyes sparkling looking at the hands, big happy smile with mouth open, slight lean forward. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H75" s="3" t="inlineStr"/>
-    </row>
-    <row r="76">
+      <c r="H75" s="3" t="n"/>
+    </row>
+    <row r="76" ht="45" customHeight="1" s="12">
       <c r="A76" s="3" t="inlineStr">
         <is>
           <t>G5</t>
@@ -5100,9 +5303,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: super excited jumping pose, both arms raised high in celebration, empty hands, not holding anything (no gift box, no props), eyes closed happily (^ ^), wide open smile, tiny hearts and sparkles around the head. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H76" s="3" t="inlineStr"/>
-    </row>
-    <row r="77">
+      <c r="H76" s="3" t="n"/>
+    </row>
+    <row r="77" ht="45" customHeight="1" s="12">
       <c r="A77" s="3" t="inlineStr">
         <is>
           <t>G5</t>
@@ -5136,9 +5339,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: making a finger heart toward the viewer with one hand near the cheek, other arm relaxed, not holding anything else (no gift box, no props), winking, cute blush, small smile. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H77" s="3" t="inlineStr"/>
-    </row>
-    <row r="78">
+      <c r="H77" s="3" t="n"/>
+    </row>
+    <row r="78" ht="60" customHeight="1" s="12">
       <c r="A78" s="3" t="inlineStr">
         <is>
           <t>G5</t>
@@ -5172,9 +5375,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance move — body leaning to the LEFT, left arm raised up with index finger pointing to the sky, right hand on hip, right knee slightly bent, empty hands, not holding anything (no gift box, no props), cheerful open smile, small music notes around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H78" s="3" t="inlineStr"/>
-    </row>
-    <row r="79">
+      <c r="H78" s="3" t="n"/>
+    </row>
+    <row r="79" ht="60" customHeight="1" s="12">
       <c r="A79" s="3" t="inlineStr">
         <is>
           <t>G5</t>
@@ -5208,9 +5411,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance move — body leaning to the RIGHT, right arm raised up with index finger pointing to the sky, left hand on hip, left knee slightly bent, empty hands, not holding anything (no gift box, no props), cheerful open smile, small music notes around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H79" s="3" t="inlineStr"/>
-    </row>
-    <row r="80">
+      <c r="H79" s="3" t="n"/>
+    </row>
+    <row r="80" ht="45" customHeight="1" s="12">
       <c r="A80" s="3" t="inlineStr">
         <is>
           <t>G5</t>
@@ -5244,9 +5447,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance finishing pose — both hands making peace signs (V) next to the face, one foot kicked up behind, empty hands, not holding anything (no gift box, no props), winking with a big smile, sparkles around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H80" s="3" t="inlineStr"/>
-    </row>
-    <row r="81">
+      <c r="H80" s="3" t="n"/>
+    </row>
+    <row r="81" ht="45" customHeight="1" s="12">
       <c r="A81" s="3" t="inlineStr">
         <is>
           <t>G5</t>
@@ -5280,9 +5483,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: walking toward the viewer, front view, LEFT foot stepping forward, right arm swinging forward and left arm back, empty hands, not holding anything (no gift box, no props), happy smile, slight bounce. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H81" s="3" t="inlineStr"/>
-    </row>
-    <row r="82">
+      <c r="H81" s="3" t="n"/>
+    </row>
+    <row r="82" ht="45" customHeight="1" s="12">
       <c r="A82" s="3" t="inlineStr">
         <is>
           <t>G5</t>
@@ -5316,9 +5519,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: walking toward the viewer, front view, RIGHT foot stepping forward, left arm swinging forward and right arm back, empty hands, not holding anything (no gift box, no props), happy smile, slight bounce. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H82" s="3" t="inlineStr"/>
-    </row>
-    <row r="83">
+      <c r="H82" s="3" t="n"/>
+    </row>
+    <row r="83" ht="45" customHeight="1" s="12">
       <c r="A83" s="3" t="inlineStr">
         <is>
           <t>G5</t>
@@ -5352,9 +5555,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: close to the viewer, front view, one hand touching the lips about to blow a kiss, eyes gently closed, cute blush, other arm relaxed, not holding anything else (no gift box, no props). Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H83" s="3" t="inlineStr"/>
-    </row>
-    <row r="84">
+      <c r="H83" s="3" t="n"/>
+    </row>
+    <row r="84" ht="60" customHeight="1" s="12">
       <c r="A84" s="3" t="inlineStr">
         <is>
           <t>G5</t>
@@ -5388,9 +5591,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: blowing a kiss toward the viewer, arm stretched forward with open palm from the lips, lips puckered, winking, cute blush, a small pink heart floating out from the hand, not holding anything else (no gift box, no props). Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H84" s="3" t="inlineStr"/>
-    </row>
-    <row r="85">
+      <c r="H84" s="3" t="n"/>
+    </row>
+    <row r="85" ht="45" customHeight="1" s="12">
       <c r="A85" s="3" t="inlineStr">
         <is>
           <t>G5</t>
@@ -5424,9 +5627,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: back view, walking away from the viewer, LEFT foot stepping forward, arms swinging naturally, empty hands, not holding anything (no gift box, no props), showing the back of the outfit and hair. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H85" s="3" t="inlineStr"/>
-    </row>
-    <row r="86">
+      <c r="H85" s="3" t="n"/>
+    </row>
+    <row r="86" ht="45" customHeight="1" s="12">
       <c r="A86" s="3" t="inlineStr">
         <is>
           <t>G5</t>
@@ -5460,9 +5663,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: back view, walking away from the viewer, RIGHT foot stepping forward, arms swinging naturally, empty hands, not holding anything (no gift box, no props), showing the back of the outfit and hair. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H86" s="3" t="inlineStr"/>
-    </row>
-    <row r="87">
+      <c r="H86" s="3" t="n"/>
+    </row>
+    <row r="87" ht="75" customHeight="1" s="12">
       <c r="A87" s="5" t="inlineStr">
         <is>
           <t>G6</t>
@@ -5502,7 +5705,7 @@
         </is>
       </c>
     </row>
-    <row r="88">
+    <row r="88" ht="45" customHeight="1" s="12">
       <c r="A88" s="5" t="inlineStr">
         <is>
           <t>G6</t>
@@ -5542,7 +5745,7 @@
         </is>
       </c>
     </row>
-    <row r="89">
+    <row r="89" ht="45" customHeight="1" s="12">
       <c r="A89" s="5" t="inlineStr">
         <is>
           <t>G6</t>
@@ -5582,7 +5785,7 @@
         </is>
       </c>
     </row>
-    <row r="90">
+    <row r="90" ht="60" customHeight="1" s="12">
       <c r="A90" s="5" t="inlineStr">
         <is>
           <t>G6</t>
@@ -5622,7 +5825,7 @@
         </is>
       </c>
     </row>
-    <row r="91">
+    <row r="91" ht="60" customHeight="1" s="12">
       <c r="A91" s="5" t="inlineStr">
         <is>
           <t>G6</t>
@@ -5662,7 +5865,7 @@
         </is>
       </c>
     </row>
-    <row r="92">
+    <row r="92" ht="60" customHeight="1" s="12">
       <c r="A92" s="5" t="inlineStr">
         <is>
           <t>G6</t>
@@ -5702,7 +5905,7 @@
         </is>
       </c>
     </row>
-    <row r="93">
+    <row r="93" ht="45" customHeight="1" s="12">
       <c r="A93" s="5" t="inlineStr">
         <is>
           <t>G6</t>
@@ -5742,7 +5945,7 @@
         </is>
       </c>
     </row>
-    <row r="94">
+    <row r="94" ht="45" customHeight="1" s="12">
       <c r="A94" s="5" t="inlineStr">
         <is>
           <t>G6</t>
@@ -5782,7 +5985,7 @@
         </is>
       </c>
     </row>
-    <row r="95">
+    <row r="95" ht="60" customHeight="1" s="12">
       <c r="A95" s="5" t="inlineStr">
         <is>
           <t>G6</t>
@@ -5822,7 +6025,7 @@
         </is>
       </c>
     </row>
-    <row r="96">
+    <row r="96" ht="60" customHeight="1" s="12">
       <c r="A96" s="5" t="inlineStr">
         <is>
           <t>G6</t>
@@ -5862,7 +6065,7 @@
         </is>
       </c>
     </row>
-    <row r="97">
+    <row r="97" ht="45" customHeight="1" s="12">
       <c r="A97" s="5" t="inlineStr">
         <is>
           <t>G6</t>
@@ -5902,7 +6105,7 @@
         </is>
       </c>
     </row>
-    <row r="98">
+    <row r="98" ht="45" customHeight="1" s="12">
       <c r="A98" s="5" t="inlineStr">
         <is>
           <t>G6</t>
@@ -5942,7 +6145,7 @@
         </is>
       </c>
     </row>
-    <row r="99">
+    <row r="99" ht="45" customHeight="1" s="12">
       <c r="A99" s="5" t="inlineStr">
         <is>
           <t>G6</t>
@@ -5982,7 +6185,7 @@
         </is>
       </c>
     </row>
-    <row r="100">
+    <row r="100" ht="45" customHeight="1" s="12">
       <c r="A100" s="5" t="inlineStr">
         <is>
           <t>G6</t>
@@ -6022,7 +6225,7 @@
         </is>
       </c>
     </row>
-    <row r="101">
+    <row r="101" ht="60" customHeight="1" s="12">
       <c r="A101" s="5" t="inlineStr">
         <is>
           <t>G6</t>
@@ -6062,7 +6265,7 @@
         </is>
       </c>
     </row>
-    <row r="102">
+    <row r="102" ht="45" customHeight="1" s="12">
       <c r="A102" s="5" t="inlineStr">
         <is>
           <t>G6</t>
@@ -6102,7 +6305,7 @@
         </is>
       </c>
     </row>
-    <row r="103">
+    <row r="103" ht="45" customHeight="1" s="12">
       <c r="A103" s="5" t="inlineStr">
         <is>
           <t>G6</t>
@@ -6142,7 +6345,7 @@
         </is>
       </c>
     </row>
-    <row r="104">
+    <row r="104" ht="75" customHeight="1" s="12">
       <c r="A104" s="3" t="inlineStr">
         <is>
           <t>G7</t>
@@ -6176,9 +6379,9 @@
           <t>Cute chibi mascot character for a TikTok live streamer, girl with long golden wavy hair, sparkly pink singer dress, tiny microphone hair clip. Full body, front view, standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Centered, 2.5 heads tall, big sparkly eyes open, soft blush cheeks, gentle smile with mouth closed. Soft 3D pastel style like a vinyl toy, smooth shading, clean outline, pink-lavender-mint palette, kawaii. Transparent background, no shadow on ground, no text, single character only, 1024x1024.</t>
         </is>
       </c>
-      <c r="H104" s="3" t="inlineStr"/>
-    </row>
-    <row r="105">
+      <c r="H104" s="3" t="n"/>
+    </row>
+    <row r="105" ht="45" customHeight="1" s="12">
       <c r="A105" s="3" t="inlineStr">
         <is>
           <t>G7</t>
@@ -6212,9 +6415,9 @@
           <t>Same character, same outfit, exact same pose, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: eyes gently closed as if blinking. Gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H105" s="3" t="inlineStr"/>
-    </row>
-    <row r="106">
+      <c r="H105" s="3" t="n"/>
+    </row>
+    <row r="106" ht="45" customHeight="1" s="12">
       <c r="A106" s="3" t="inlineStr">
         <is>
           <t>G7</t>
@@ -6248,9 +6451,9 @@
           <t>Same character, same outfit, exact same pose, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: mouth open happily as if talking "ah". Eyes open. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H106" s="3" t="inlineStr"/>
-    </row>
-    <row r="107">
+      <c r="H106" s="3" t="n"/>
+    </row>
+    <row r="107" ht="60" customHeight="1" s="12">
       <c r="A107" s="3" t="inlineStr">
         <is>
           <t>G7</t>
@@ -6284,9 +6487,9 @@
           <t>Same character, same outfit, exact same pose, body, face, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: hair and hair accessories gently swaying to the LEFT as if blown by a soft breeze (only hair tips, strands and ribbons shift slightly left). Eyes open, gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H107" s="3" t="inlineStr"/>
-    </row>
-    <row r="108">
+      <c r="H107" s="3" t="n"/>
+    </row>
+    <row r="108" ht="60" customHeight="1" s="12">
       <c r="A108" s="3" t="inlineStr">
         <is>
           <t>G7</t>
@@ -6320,9 +6523,9 @@
           <t>Same character, same outfit, exact same pose, body, face, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: hair and hair accessories gently swaying to the RIGHT as if blown by a soft breeze (only hair tips, strands and ribbons shift slightly right). Eyes open, gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H108" s="3" t="inlineStr"/>
-    </row>
-    <row r="109">
+      <c r="H108" s="3" t="n"/>
+    </row>
+    <row r="109" ht="60" customHeight="1" s="12">
       <c r="A109" s="3" t="inlineStr">
         <is>
           <t>G7</t>
@@ -6356,9 +6559,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: happily ready to catch a gift, both hands cupped together in front of the chest with palms facing up, empty hands, not holding anything (no gift box, no props), clear empty space above the palms, eyes sparkling looking at the hands, big happy smile with mouth open, slight lean forward. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H109" s="3" t="inlineStr"/>
-    </row>
-    <row r="110">
+      <c r="H109" s="3" t="n"/>
+    </row>
+    <row r="110" ht="45" customHeight="1" s="12">
       <c r="A110" s="3" t="inlineStr">
         <is>
           <t>G7</t>
@@ -6392,9 +6595,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: super excited jumping pose, both arms raised high in celebration, empty hands, not holding anything (no gift box, no props), eyes closed happily (^ ^), wide open smile, tiny hearts and sparkles around the head. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H110" s="3" t="inlineStr"/>
-    </row>
-    <row r="111">
+      <c r="H110" s="3" t="n"/>
+    </row>
+    <row r="111" ht="45" customHeight="1" s="12">
       <c r="A111" s="3" t="inlineStr">
         <is>
           <t>G7</t>
@@ -6428,9 +6631,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: making a finger heart toward the viewer with one hand near the cheek, other arm relaxed, not holding anything else (no gift box, no props), winking, cute blush, small smile. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H111" s="3" t="inlineStr"/>
-    </row>
-    <row r="112">
+      <c r="H111" s="3" t="n"/>
+    </row>
+    <row r="112" ht="60" customHeight="1" s="12">
       <c r="A112" s="3" t="inlineStr">
         <is>
           <t>G7</t>
@@ -6464,9 +6667,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance move — body leaning to the LEFT, left arm raised up with index finger pointing to the sky, right hand on hip, right knee slightly bent, empty hands, not holding anything (no gift box, no props), cheerful open smile, small music notes around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H112" s="3" t="inlineStr"/>
-    </row>
-    <row r="113">
+      <c r="H112" s="3" t="n"/>
+    </row>
+    <row r="113" ht="60" customHeight="1" s="12">
       <c r="A113" s="3" t="inlineStr">
         <is>
           <t>G7</t>
@@ -6500,9 +6703,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance move — body leaning to the RIGHT, right arm raised up with index finger pointing to the sky, left hand on hip, left knee slightly bent, empty hands, not holding anything (no gift box, no props), cheerful open smile, small music notes around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H113" s="3" t="inlineStr"/>
-    </row>
-    <row r="114">
+      <c r="H113" s="3" t="n"/>
+    </row>
+    <row r="114" ht="45" customHeight="1" s="12">
       <c r="A114" s="3" t="inlineStr">
         <is>
           <t>G7</t>
@@ -6536,9 +6739,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance finishing pose — both hands making peace signs (V) next to the face, one foot kicked up behind, empty hands, not holding anything (no gift box, no props), winking with a big smile, sparkles around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H114" s="3" t="inlineStr"/>
-    </row>
-    <row r="115">
+      <c r="H114" s="3" t="n"/>
+    </row>
+    <row r="115" ht="45" customHeight="1" s="12">
       <c r="A115" s="3" t="inlineStr">
         <is>
           <t>G7</t>
@@ -6572,9 +6775,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: walking toward the viewer, front view, LEFT foot stepping forward, right arm swinging forward and left arm back, empty hands, not holding anything (no gift box, no props), happy smile, slight bounce. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H115" s="3" t="inlineStr"/>
-    </row>
-    <row r="116">
+      <c r="H115" s="3" t="n"/>
+    </row>
+    <row r="116" ht="45" customHeight="1" s="12">
       <c r="A116" s="3" t="inlineStr">
         <is>
           <t>G7</t>
@@ -6608,9 +6811,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: walking toward the viewer, front view, RIGHT foot stepping forward, left arm swinging forward and right arm back, empty hands, not holding anything (no gift box, no props), happy smile, slight bounce. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H116" s="3" t="inlineStr"/>
-    </row>
-    <row r="117">
+      <c r="H116" s="3" t="n"/>
+    </row>
+    <row r="117" ht="45" customHeight="1" s="12">
       <c r="A117" s="3" t="inlineStr">
         <is>
           <t>G7</t>
@@ -6644,9 +6847,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: close to the viewer, front view, one hand touching the lips about to blow a kiss, eyes gently closed, cute blush, other arm relaxed, not holding anything else (no gift box, no props). Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H117" s="3" t="inlineStr"/>
-    </row>
-    <row r="118">
+      <c r="H117" s="3" t="n"/>
+    </row>
+    <row r="118" ht="60" customHeight="1" s="12">
       <c r="A118" s="3" t="inlineStr">
         <is>
           <t>G7</t>
@@ -6680,9 +6883,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: blowing a kiss toward the viewer, arm stretched forward with open palm from the lips, lips puckered, winking, cute blush, a small pink heart floating out from the hand, not holding anything else (no gift box, no props). Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H118" s="3" t="inlineStr"/>
-    </row>
-    <row r="119">
+      <c r="H118" s="3" t="n"/>
+    </row>
+    <row r="119" ht="45" customHeight="1" s="12">
       <c r="A119" s="3" t="inlineStr">
         <is>
           <t>G7</t>
@@ -6716,9 +6919,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: back view, walking away from the viewer, LEFT foot stepping forward, arms swinging naturally, empty hands, not holding anything (no gift box, no props), showing the back of the outfit and hair. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H119" s="3" t="inlineStr"/>
-    </row>
-    <row r="120">
+      <c r="H119" s="3" t="n"/>
+    </row>
+    <row r="120" ht="45" customHeight="1" s="12">
       <c r="A120" s="3" t="inlineStr">
         <is>
           <t>G7</t>
@@ -6752,9 +6955,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: back view, walking away from the viewer, RIGHT foot stepping forward, arms swinging naturally, empty hands, not holding anything (no gift box, no props), showing the back of the outfit and hair. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H120" s="3" t="inlineStr"/>
-    </row>
-    <row r="121">
+      <c r="H120" s="3" t="n"/>
+    </row>
+    <row r="121" ht="75" customHeight="1" s="12">
       <c r="A121" s="5" t="inlineStr">
         <is>
           <t>G8</t>
@@ -6794,7 +6997,7 @@
         </is>
       </c>
     </row>
-    <row r="122">
+    <row r="122" ht="45" customHeight="1" s="12">
       <c r="A122" s="5" t="inlineStr">
         <is>
           <t>G8</t>
@@ -6834,7 +7037,7 @@
         </is>
       </c>
     </row>
-    <row r="123">
+    <row r="123" ht="45" customHeight="1" s="12">
       <c r="A123" s="5" t="inlineStr">
         <is>
           <t>G8</t>
@@ -6874,7 +7077,7 @@
         </is>
       </c>
     </row>
-    <row r="124">
+    <row r="124" ht="60" customHeight="1" s="12">
       <c r="A124" s="5" t="inlineStr">
         <is>
           <t>G8</t>
@@ -6914,7 +7117,7 @@
         </is>
       </c>
     </row>
-    <row r="125">
+    <row r="125" ht="60" customHeight="1" s="12">
       <c r="A125" s="5" t="inlineStr">
         <is>
           <t>G8</t>
@@ -6954,7 +7157,7 @@
         </is>
       </c>
     </row>
-    <row r="126">
+    <row r="126" ht="60" customHeight="1" s="12">
       <c r="A126" s="5" t="inlineStr">
         <is>
           <t>G8</t>
@@ -6994,7 +7197,7 @@
         </is>
       </c>
     </row>
-    <row r="127">
+    <row r="127" ht="45" customHeight="1" s="12">
       <c r="A127" s="5" t="inlineStr">
         <is>
           <t>G8</t>
@@ -7034,7 +7237,7 @@
         </is>
       </c>
     </row>
-    <row r="128">
+    <row r="128" ht="45" customHeight="1" s="12">
       <c r="A128" s="5" t="inlineStr">
         <is>
           <t>G8</t>
@@ -7074,7 +7277,7 @@
         </is>
       </c>
     </row>
-    <row r="129">
+    <row r="129" ht="60" customHeight="1" s="12">
       <c r="A129" s="5" t="inlineStr">
         <is>
           <t>G8</t>
@@ -7114,7 +7317,7 @@
         </is>
       </c>
     </row>
-    <row r="130">
+    <row r="130" ht="60" customHeight="1" s="12">
       <c r="A130" s="5" t="inlineStr">
         <is>
           <t>G8</t>
@@ -7154,7 +7357,7 @@
         </is>
       </c>
     </row>
-    <row r="131">
+    <row r="131" ht="45" customHeight="1" s="12">
       <c r="A131" s="5" t="inlineStr">
         <is>
           <t>G8</t>
@@ -7194,7 +7397,7 @@
         </is>
       </c>
     </row>
-    <row r="132">
+    <row r="132" ht="45" customHeight="1" s="12">
       <c r="A132" s="5" t="inlineStr">
         <is>
           <t>G8</t>
@@ -7234,7 +7437,7 @@
         </is>
       </c>
     </row>
-    <row r="133">
+    <row r="133" ht="45" customHeight="1" s="12">
       <c r="A133" s="5" t="inlineStr">
         <is>
           <t>G8</t>
@@ -7274,7 +7477,7 @@
         </is>
       </c>
     </row>
-    <row r="134">
+    <row r="134" ht="45" customHeight="1" s="12">
       <c r="A134" s="5" t="inlineStr">
         <is>
           <t>G8</t>
@@ -7314,7 +7517,7 @@
         </is>
       </c>
     </row>
-    <row r="135">
+    <row r="135" ht="60" customHeight="1" s="12">
       <c r="A135" s="5" t="inlineStr">
         <is>
           <t>G8</t>
@@ -7354,7 +7557,7 @@
         </is>
       </c>
     </row>
-    <row r="136">
+    <row r="136" ht="45" customHeight="1" s="12">
       <c r="A136" s="5" t="inlineStr">
         <is>
           <t>G8</t>
@@ -7394,7 +7597,7 @@
         </is>
       </c>
     </row>
-    <row r="137">
+    <row r="137" ht="45" customHeight="1" s="12">
       <c r="A137" s="5" t="inlineStr">
         <is>
           <t>G8</t>
@@ -7434,7 +7637,7 @@
         </is>
       </c>
     </row>
-    <row r="138">
+    <row r="138" ht="75" customHeight="1" s="12">
       <c r="A138" s="3" t="inlineStr">
         <is>
           <t>G9</t>
@@ -7468,9 +7671,9 @@
           <t>Cute chibi mascot character for a TikTok live streamer, girl with rainbow pastel hair, unicorn horn headband, fluffy cloud-like pastel dress. Full body, front view, standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Centered, 2.5 heads tall, big sparkly eyes open, soft blush cheeks, gentle smile with mouth closed. Soft 3D pastel style like a vinyl toy, smooth shading, clean outline, pink-lavender-mint palette, kawaii. Transparent background, no shadow on ground, no text, single character only, 1024x1024.</t>
         </is>
       </c>
-      <c r="H138" s="3" t="inlineStr"/>
-    </row>
-    <row r="139">
+      <c r="H138" s="3" t="n"/>
+    </row>
+    <row r="139" ht="45" customHeight="1" s="12">
       <c r="A139" s="3" t="inlineStr">
         <is>
           <t>G9</t>
@@ -7504,9 +7707,9 @@
           <t>Same character, same outfit, exact same pose, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: eyes gently closed as if blinking. Gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H139" s="3" t="inlineStr"/>
-    </row>
-    <row r="140">
+      <c r="H139" s="3" t="n"/>
+    </row>
+    <row r="140" ht="45" customHeight="1" s="12">
       <c r="A140" s="3" t="inlineStr">
         <is>
           <t>G9</t>
@@ -7540,9 +7743,9 @@
           <t>Same character, same outfit, exact same pose, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: mouth open happily as if talking "ah". Eyes open. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H140" s="3" t="inlineStr"/>
-    </row>
-    <row r="141">
+      <c r="H140" s="3" t="n"/>
+    </row>
+    <row r="141" ht="60" customHeight="1" s="12">
       <c r="A141" s="3" t="inlineStr">
         <is>
           <t>G9</t>
@@ -7576,9 +7779,9 @@
           <t>Same character, same outfit, exact same pose, body, face, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: hair and hair accessories gently swaying to the LEFT as if blown by a soft breeze (only hair tips, strands and ribbons shift slightly left). Eyes open, gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H141" s="3" t="inlineStr"/>
-    </row>
-    <row r="142">
+      <c r="H141" s="3" t="n"/>
+    </row>
+    <row r="142" ht="60" customHeight="1" s="12">
       <c r="A142" s="3" t="inlineStr">
         <is>
           <t>G9</t>
@@ -7612,9 +7815,9 @@
           <t>Same character, same outfit, exact same pose, body, face, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: hair and hair accessories gently swaying to the RIGHT as if blown by a soft breeze (only hair tips, strands and ribbons shift slightly right). Eyes open, gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H142" s="3" t="inlineStr"/>
-    </row>
-    <row r="143">
+      <c r="H142" s="3" t="n"/>
+    </row>
+    <row r="143" ht="60" customHeight="1" s="12">
       <c r="A143" s="3" t="inlineStr">
         <is>
           <t>G9</t>
@@ -7648,9 +7851,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: happily ready to catch a gift, both hands cupped together in front of the chest with palms facing up, empty hands, not holding anything (no gift box, no props), clear empty space above the palms, eyes sparkling looking at the hands, big happy smile with mouth open, slight lean forward. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H143" s="3" t="inlineStr"/>
-    </row>
-    <row r="144">
+      <c r="H143" s="3" t="n"/>
+    </row>
+    <row r="144" ht="45" customHeight="1" s="12">
       <c r="A144" s="3" t="inlineStr">
         <is>
           <t>G9</t>
@@ -7684,9 +7887,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: super excited jumping pose, both arms raised high in celebration, empty hands, not holding anything (no gift box, no props), eyes closed happily (^ ^), wide open smile, tiny hearts and sparkles around the head. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H144" s="3" t="inlineStr"/>
-    </row>
-    <row r="145">
+      <c r="H144" s="3" t="n"/>
+    </row>
+    <row r="145" ht="45" customHeight="1" s="12">
       <c r="A145" s="3" t="inlineStr">
         <is>
           <t>G9</t>
@@ -7720,9 +7923,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: making a finger heart toward the viewer with one hand near the cheek, other arm relaxed, not holding anything else (no gift box, no props), winking, cute blush, small smile. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H145" s="3" t="inlineStr"/>
-    </row>
-    <row r="146">
+      <c r="H145" s="3" t="n"/>
+    </row>
+    <row r="146" ht="60" customHeight="1" s="12">
       <c r="A146" s="3" t="inlineStr">
         <is>
           <t>G9</t>
@@ -7756,9 +7959,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance move — body leaning to the LEFT, left arm raised up with index finger pointing to the sky, right hand on hip, right knee slightly bent, empty hands, not holding anything (no gift box, no props), cheerful open smile, small music notes around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H146" s="3" t="inlineStr"/>
-    </row>
-    <row r="147">
+      <c r="H146" s="3" t="n"/>
+    </row>
+    <row r="147" ht="60" customHeight="1" s="12">
       <c r="A147" s="3" t="inlineStr">
         <is>
           <t>G9</t>
@@ -7792,9 +7995,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance move — body leaning to the RIGHT, right arm raised up with index finger pointing to the sky, left hand on hip, left knee slightly bent, empty hands, not holding anything (no gift box, no props), cheerful open smile, small music notes around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H147" s="3" t="inlineStr"/>
-    </row>
-    <row r="148">
+      <c r="H147" s="3" t="n"/>
+    </row>
+    <row r="148" ht="45" customHeight="1" s="12">
       <c r="A148" s="3" t="inlineStr">
         <is>
           <t>G9</t>
@@ -7828,9 +8031,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance finishing pose — both hands making peace signs (V) next to the face, one foot kicked up behind, empty hands, not holding anything (no gift box, no props), winking with a big smile, sparkles around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H148" s="3" t="inlineStr"/>
-    </row>
-    <row r="149">
+      <c r="H148" s="3" t="n"/>
+    </row>
+    <row r="149" ht="45" customHeight="1" s="12">
       <c r="A149" s="3" t="inlineStr">
         <is>
           <t>G9</t>
@@ -7864,9 +8067,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: walking toward the viewer, front view, LEFT foot stepping forward, right arm swinging forward and left arm back, empty hands, not holding anything (no gift box, no props), happy smile, slight bounce. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H149" s="3" t="inlineStr"/>
-    </row>
-    <row r="150">
+      <c r="H149" s="3" t="n"/>
+    </row>
+    <row r="150" ht="45" customHeight="1" s="12">
       <c r="A150" s="3" t="inlineStr">
         <is>
           <t>G9</t>
@@ -7900,9 +8103,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: walking toward the viewer, front view, RIGHT foot stepping forward, left arm swinging forward and right arm back, empty hands, not holding anything (no gift box, no props), happy smile, slight bounce. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H150" s="3" t="inlineStr"/>
-    </row>
-    <row r="151">
+      <c r="H150" s="3" t="n"/>
+    </row>
+    <row r="151" ht="45" customHeight="1" s="12">
       <c r="A151" s="3" t="inlineStr">
         <is>
           <t>G9</t>
@@ -7936,9 +8139,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: close to the viewer, front view, one hand touching the lips about to blow a kiss, eyes gently closed, cute blush, other arm relaxed, not holding anything else (no gift box, no props). Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H151" s="3" t="inlineStr"/>
-    </row>
-    <row r="152">
+      <c r="H151" s="3" t="n"/>
+    </row>
+    <row r="152" ht="60" customHeight="1" s="12">
       <c r="A152" s="3" t="inlineStr">
         <is>
           <t>G9</t>
@@ -7972,9 +8175,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: blowing a kiss toward the viewer, arm stretched forward with open palm from the lips, lips puckered, winking, cute blush, a small pink heart floating out from the hand, not holding anything else (no gift box, no props). Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H152" s="3" t="inlineStr"/>
-    </row>
-    <row r="153">
+      <c r="H152" s="3" t="n"/>
+    </row>
+    <row r="153" ht="45" customHeight="1" s="12">
       <c r="A153" s="3" t="inlineStr">
         <is>
           <t>G9</t>
@@ -8008,9 +8211,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: back view, walking away from the viewer, LEFT foot stepping forward, arms swinging naturally, empty hands, not holding anything (no gift box, no props), showing the back of the outfit and hair. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H153" s="3" t="inlineStr"/>
-    </row>
-    <row r="154">
+      <c r="H153" s="3" t="n"/>
+    </row>
+    <row r="154" ht="45" customHeight="1" s="12">
       <c r="A154" s="3" t="inlineStr">
         <is>
           <t>G9</t>
@@ -8044,9 +8247,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: back view, walking away from the viewer, RIGHT foot stepping forward, arms swinging naturally, empty hands, not holding anything (no gift box, no props), showing the back of the outfit and hair. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H154" s="3" t="inlineStr"/>
-    </row>
-    <row r="155">
+      <c r="H154" s="3" t="n"/>
+    </row>
+    <row r="155" ht="75" customHeight="1" s="12">
       <c r="A155" s="3" t="inlineStr">
         <is>
           <t>G10</t>
@@ -8080,9 +8283,9 @@
           <t>Cute chibi mascot character for a TikTok live streamer, girl with red bob hair, strawberry beret, red-and-white polka dot dress. Full body, front view, standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Centered, 2.5 heads tall, big sparkly eyes open, soft blush cheeks, gentle smile with mouth closed. Soft 3D pastel style like a vinyl toy, smooth shading, clean outline, pink-lavender-mint palette, kawaii. Transparent background, no shadow on ground, no text, single character only, 1024x1024.</t>
         </is>
       </c>
-      <c r="H155" s="3" t="inlineStr"/>
-    </row>
-    <row r="156">
+      <c r="H155" s="3" t="n"/>
+    </row>
+    <row r="156" ht="45" customHeight="1" s="12">
       <c r="A156" s="3" t="inlineStr">
         <is>
           <t>G10</t>
@@ -8116,9 +8319,9 @@
           <t>Same character, same outfit, exact same pose, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: eyes gently closed as if blinking. Gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H156" s="3" t="inlineStr"/>
-    </row>
-    <row r="157">
+      <c r="H156" s="3" t="n"/>
+    </row>
+    <row r="157" ht="45" customHeight="1" s="12">
       <c r="A157" s="3" t="inlineStr">
         <is>
           <t>G10</t>
@@ -8152,9 +8355,9 @@
           <t>Same character, same outfit, exact same pose, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: mouth open happily as if talking "ah". Eyes open. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H157" s="3" t="inlineStr"/>
-    </row>
-    <row r="158">
+      <c r="H157" s="3" t="n"/>
+    </row>
+    <row r="158" ht="60" customHeight="1" s="12">
       <c r="A158" s="3" t="inlineStr">
         <is>
           <t>G10</t>
@@ -8188,9 +8391,9 @@
           <t>Same character, same outfit, exact same pose, body, face, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: hair and hair accessories gently swaying to the LEFT as if blown by a soft breeze (only hair tips, strands and ribbons shift slightly left). Eyes open, gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H158" s="3" t="inlineStr"/>
-    </row>
-    <row r="159">
+      <c r="H158" s="3" t="n"/>
+    </row>
+    <row r="159" ht="60" customHeight="1" s="12">
       <c r="A159" s="3" t="inlineStr">
         <is>
           <t>G10</t>
@@ -8224,9 +8427,9 @@
           <t>Same character, same outfit, exact same pose, body, face, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: hair and hair accessories gently swaying to the RIGHT as if blown by a soft breeze (only hair tips, strands and ribbons shift slightly right). Eyes open, gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H159" s="3" t="inlineStr"/>
-    </row>
-    <row r="160">
+      <c r="H159" s="3" t="n"/>
+    </row>
+    <row r="160" ht="60" customHeight="1" s="12">
       <c r="A160" s="3" t="inlineStr">
         <is>
           <t>G10</t>
@@ -8260,9 +8463,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: happily ready to catch a gift, both hands cupped together in front of the chest with palms facing up, empty hands, not holding anything (no gift box, no props), clear empty space above the palms, eyes sparkling looking at the hands, big happy smile with mouth open, slight lean forward. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H160" s="3" t="inlineStr"/>
-    </row>
-    <row r="161">
+      <c r="H160" s="3" t="n"/>
+    </row>
+    <row r="161" ht="45" customHeight="1" s="12">
       <c r="A161" s="3" t="inlineStr">
         <is>
           <t>G10</t>
@@ -8296,9 +8499,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: super excited jumping pose, both arms raised high in celebration, empty hands, not holding anything (no gift box, no props), eyes closed happily (^ ^), wide open smile, tiny hearts and sparkles around the head. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H161" s="3" t="inlineStr"/>
-    </row>
-    <row r="162">
+      <c r="H161" s="3" t="n"/>
+    </row>
+    <row r="162" ht="45" customHeight="1" s="12">
       <c r="A162" s="3" t="inlineStr">
         <is>
           <t>G10</t>
@@ -8332,9 +8535,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: making a finger heart toward the viewer with one hand near the cheek, other arm relaxed, not holding anything else (no gift box, no props), winking, cute blush, small smile. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H162" s="3" t="inlineStr"/>
-    </row>
-    <row r="163">
+      <c r="H162" s="3" t="n"/>
+    </row>
+    <row r="163" ht="60" customHeight="1" s="12">
       <c r="A163" s="3" t="inlineStr">
         <is>
           <t>G10</t>
@@ -8368,9 +8571,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance move — body leaning to the LEFT, left arm raised up with index finger pointing to the sky, right hand on hip, right knee slightly bent, empty hands, not holding anything (no gift box, no props), cheerful open smile, small music notes around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H163" s="3" t="inlineStr"/>
-    </row>
-    <row r="164">
+      <c r="H163" s="3" t="n"/>
+    </row>
+    <row r="164" ht="60" customHeight="1" s="12">
       <c r="A164" s="3" t="inlineStr">
         <is>
           <t>G10</t>
@@ -8404,9 +8607,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance move — body leaning to the RIGHT, right arm raised up with index finger pointing to the sky, left hand on hip, left knee slightly bent, empty hands, not holding anything (no gift box, no props), cheerful open smile, small music notes around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H164" s="3" t="inlineStr"/>
-    </row>
-    <row r="165">
+      <c r="H164" s="3" t="n"/>
+    </row>
+    <row r="165" ht="45" customHeight="1" s="12">
       <c r="A165" s="3" t="inlineStr">
         <is>
           <t>G10</t>
@@ -8440,9 +8643,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance finishing pose — both hands making peace signs (V) next to the face, one foot kicked up behind, empty hands, not holding anything (no gift box, no props), winking with a big smile, sparkles around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H165" s="3" t="inlineStr"/>
-    </row>
-    <row r="166">
+      <c r="H165" s="3" t="n"/>
+    </row>
+    <row r="166" ht="45" customHeight="1" s="12">
       <c r="A166" s="3" t="inlineStr">
         <is>
           <t>G10</t>
@@ -8476,9 +8679,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: walking toward the viewer, front view, LEFT foot stepping forward, right arm swinging forward and left arm back, empty hands, not holding anything (no gift box, no props), happy smile, slight bounce. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H166" s="3" t="inlineStr"/>
-    </row>
-    <row r="167">
+      <c r="H166" s="3" t="n"/>
+    </row>
+    <row r="167" ht="45" customHeight="1" s="12">
       <c r="A167" s="3" t="inlineStr">
         <is>
           <t>G10</t>
@@ -8512,9 +8715,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: walking toward the viewer, front view, RIGHT foot stepping forward, left arm swinging forward and right arm back, empty hands, not holding anything (no gift box, no props), happy smile, slight bounce. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H167" s="3" t="inlineStr"/>
-    </row>
-    <row r="168">
+      <c r="H167" s="3" t="n"/>
+    </row>
+    <row r="168" ht="45" customHeight="1" s="12">
       <c r="A168" s="3" t="inlineStr">
         <is>
           <t>G10</t>
@@ -8548,9 +8751,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: close to the viewer, front view, one hand touching the lips about to blow a kiss, eyes gently closed, cute blush, other arm relaxed, not holding anything else (no gift box, no props). Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H168" s="3" t="inlineStr"/>
-    </row>
-    <row r="169">
+      <c r="H168" s="3" t="n"/>
+    </row>
+    <row r="169" ht="60" customHeight="1" s="12">
       <c r="A169" s="3" t="inlineStr">
         <is>
           <t>G10</t>
@@ -8584,9 +8787,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: blowing a kiss toward the viewer, arm stretched forward with open palm from the lips, lips puckered, winking, cute blush, a small pink heart floating out from the hand, not holding anything else (no gift box, no props). Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H169" s="3" t="inlineStr"/>
-    </row>
-    <row r="170">
+      <c r="H169" s="3" t="n"/>
+    </row>
+    <row r="170" ht="45" customHeight="1" s="12">
       <c r="A170" s="3" t="inlineStr">
         <is>
           <t>G10</t>
@@ -8620,9 +8823,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: back view, walking away from the viewer, LEFT foot stepping forward, arms swinging naturally, empty hands, not holding anything (no gift box, no props), showing the back of the outfit and hair. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H170" s="3" t="inlineStr"/>
-    </row>
-    <row r="171">
+      <c r="H170" s="3" t="n"/>
+    </row>
+    <row r="171" ht="45" customHeight="1" s="12">
       <c r="A171" s="3" t="inlineStr">
         <is>
           <t>G10</t>
@@ -8656,9 +8859,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: back view, walking away from the viewer, RIGHT foot stepping forward, arms swinging naturally, empty hands, not holding anything (no gift box, no props), showing the back of the outfit and hair. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H171" s="3" t="inlineStr"/>
-    </row>
-    <row r="172">
+      <c r="H171" s="3" t="n"/>
+    </row>
+    <row r="172" ht="75" customHeight="1" s="12">
       <c r="A172" s="4" t="inlineStr">
         <is>
           <t>B1</t>
@@ -8692,9 +8895,9 @@
           <t>Cute chibi mascot character for a TikTok live streamer, boy with fluffy brown hair, brown bear-ear hoodie, cream shorts. Full body, front view, standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Centered, 2.5 heads tall, big sparkly eyes open, soft blush cheeks, gentle smile with mouth closed. Soft 3D pastel style like a vinyl toy, smooth shading, clean outline, pink-lavender-mint palette, kawaii. Transparent background, no shadow on ground, no text, single character only, 1024x1024.</t>
         </is>
       </c>
-      <c r="H172" s="4" t="inlineStr"/>
-    </row>
-    <row r="173">
+      <c r="H172" s="4" t="n"/>
+    </row>
+    <row r="173" ht="45" customHeight="1" s="12">
       <c r="A173" s="4" t="inlineStr">
         <is>
           <t>B1</t>
@@ -8728,9 +8931,9 @@
           <t>Same character, same outfit, exact same pose, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: eyes gently closed as if blinking. Gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H173" s="4" t="inlineStr"/>
-    </row>
-    <row r="174">
+      <c r="H173" s="4" t="n"/>
+    </row>
+    <row r="174" ht="45" customHeight="1" s="12">
       <c r="A174" s="4" t="inlineStr">
         <is>
           <t>B1</t>
@@ -8764,9 +8967,9 @@
           <t>Same character, same outfit, exact same pose, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: mouth open happily as if talking "ah". Eyes open. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H174" s="4" t="inlineStr"/>
-    </row>
-    <row r="175">
+      <c r="H174" s="4" t="n"/>
+    </row>
+    <row r="175" ht="60" customHeight="1" s="12">
       <c r="A175" s="4" t="inlineStr">
         <is>
           <t>B1</t>
@@ -8800,9 +9003,9 @@
           <t>Same character, same outfit, exact same pose, body, face, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: hair and hair accessories gently swaying to the LEFT as if blown by a soft breeze (only hair tips, strands and ribbons shift slightly left). Eyes open, gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H175" s="4" t="inlineStr"/>
-    </row>
-    <row r="176">
+      <c r="H175" s="4" t="n"/>
+    </row>
+    <row r="176" ht="60" customHeight="1" s="12">
       <c r="A176" s="4" t="inlineStr">
         <is>
           <t>B1</t>
@@ -8836,9 +9039,9 @@
           <t>Same character, same outfit, exact same pose, body, face, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: hair and hair accessories gently swaying to the RIGHT as if blown by a soft breeze (only hair tips, strands and ribbons shift slightly right). Eyes open, gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H176" s="4" t="inlineStr"/>
-    </row>
-    <row r="177">
+      <c r="H176" s="4" t="n"/>
+    </row>
+    <row r="177" ht="60" customHeight="1" s="12">
       <c r="A177" s="4" t="inlineStr">
         <is>
           <t>B1</t>
@@ -8872,9 +9075,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: happily ready to catch a gift, both hands cupped together in front of the chest with palms facing up, empty hands, not holding anything (no gift box, no props), clear empty space above the palms, eyes sparkling looking at the hands, big happy smile with mouth open, slight lean forward. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H177" s="4" t="inlineStr"/>
-    </row>
-    <row r="178">
+      <c r="H177" s="4" t="n"/>
+    </row>
+    <row r="178" ht="45" customHeight="1" s="12">
       <c r="A178" s="4" t="inlineStr">
         <is>
           <t>B1</t>
@@ -8908,9 +9111,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: super excited jumping pose, both arms raised high in celebration, empty hands, not holding anything (no gift box, no props), eyes closed happily (^ ^), wide open smile, tiny hearts and sparkles around the head. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H178" s="4" t="inlineStr"/>
-    </row>
-    <row r="179">
+      <c r="H178" s="4" t="n"/>
+    </row>
+    <row r="179" ht="45" customHeight="1" s="12">
       <c r="A179" s="4" t="inlineStr">
         <is>
           <t>B1</t>
@@ -8944,9 +9147,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: making a finger heart toward the viewer with one hand near the cheek, other arm relaxed, not holding anything else (no gift box, no props), winking, cute blush, small smile. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H179" s="4" t="inlineStr"/>
-    </row>
-    <row r="180">
+      <c r="H179" s="4" t="n"/>
+    </row>
+    <row r="180" ht="60" customHeight="1" s="12">
       <c r="A180" s="4" t="inlineStr">
         <is>
           <t>B1</t>
@@ -8980,9 +9183,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance move — body leaning to the LEFT, left arm raised up with index finger pointing to the sky, right hand on hip, right knee slightly bent, empty hands, not holding anything (no gift box, no props), cheerful open smile, small music notes around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H180" s="4" t="inlineStr"/>
-    </row>
-    <row r="181">
+      <c r="H180" s="4" t="n"/>
+    </row>
+    <row r="181" ht="60" customHeight="1" s="12">
       <c r="A181" s="4" t="inlineStr">
         <is>
           <t>B1</t>
@@ -9016,9 +9219,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance move — body leaning to the RIGHT, right arm raised up with index finger pointing to the sky, left hand on hip, left knee slightly bent, empty hands, not holding anything (no gift box, no props), cheerful open smile, small music notes around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H181" s="4" t="inlineStr"/>
-    </row>
-    <row r="182">
+      <c r="H181" s="4" t="n"/>
+    </row>
+    <row r="182" ht="45" customHeight="1" s="12">
       <c r="A182" s="4" t="inlineStr">
         <is>
           <t>B1</t>
@@ -9052,9 +9255,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance finishing pose — both hands making peace signs (V) next to the face, one foot kicked up behind, empty hands, not holding anything (no gift box, no props), winking with a big smile, sparkles around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H182" s="4" t="inlineStr"/>
-    </row>
-    <row r="183">
+      <c r="H182" s="4" t="n"/>
+    </row>
+    <row r="183" ht="45" customHeight="1" s="12">
       <c r="A183" s="4" t="inlineStr">
         <is>
           <t>B1</t>
@@ -9088,9 +9291,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: walking toward the viewer, front view, LEFT foot stepping forward, right arm swinging forward and left arm back, empty hands, not holding anything (no gift box, no props), happy smile, slight bounce. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H183" s="4" t="inlineStr"/>
-    </row>
-    <row r="184">
+      <c r="H183" s="4" t="n"/>
+    </row>
+    <row r="184" ht="45" customHeight="1" s="12">
       <c r="A184" s="4" t="inlineStr">
         <is>
           <t>B1</t>
@@ -9124,9 +9327,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: walking toward the viewer, front view, RIGHT foot stepping forward, left arm swinging forward and right arm back, empty hands, not holding anything (no gift box, no props), happy smile, slight bounce. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H184" s="4" t="inlineStr"/>
-    </row>
-    <row r="185">
+      <c r="H184" s="4" t="n"/>
+    </row>
+    <row r="185" ht="45" customHeight="1" s="12">
       <c r="A185" s="4" t="inlineStr">
         <is>
           <t>B1</t>
@@ -9160,9 +9363,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: close to the viewer, front view, one hand touching the lips about to blow a kiss, eyes gently closed, cute blush, other arm relaxed, not holding anything else (no gift box, no props). Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H185" s="4" t="inlineStr"/>
-    </row>
-    <row r="186">
+      <c r="H185" s="4" t="n"/>
+    </row>
+    <row r="186" ht="60" customHeight="1" s="12">
       <c r="A186" s="4" t="inlineStr">
         <is>
           <t>B1</t>
@@ -9196,9 +9399,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: blowing a kiss toward the viewer, arm stretched forward with open palm from the lips, lips puckered, winking, cute blush, a small pink heart floating out from the hand, not holding anything else (no gift box, no props). Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H186" s="4" t="inlineStr"/>
-    </row>
-    <row r="187">
+      <c r="H186" s="4" t="n"/>
+    </row>
+    <row r="187" ht="45" customHeight="1" s="12">
       <c r="A187" s="4" t="inlineStr">
         <is>
           <t>B1</t>
@@ -9232,9 +9435,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: back view, walking away from the viewer, LEFT foot stepping forward, arms swinging naturally, empty hands, not holding anything (no gift box, no props), showing the back of the outfit and hair. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H187" s="4" t="inlineStr"/>
-    </row>
-    <row r="188">
+      <c r="H187" s="4" t="n"/>
+    </row>
+    <row r="188" ht="45" customHeight="1" s="12">
       <c r="A188" s="4" t="inlineStr">
         <is>
           <t>B1</t>
@@ -9268,9 +9471,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: back view, walking away from the viewer, RIGHT foot stepping forward, arms swinging naturally, empty hands, not holding anything (no gift box, no props), showing the back of the outfit and hair. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H188" s="4" t="inlineStr"/>
-    </row>
-    <row r="189">
+      <c r="H188" s="4" t="n"/>
+    </row>
+    <row r="189" ht="75" customHeight="1" s="12">
       <c r="A189" s="4" t="inlineStr">
         <is>
           <t>B2</t>
@@ -9304,9 +9507,9 @@
           <t>Cute chibi mascot character for a TikTok live streamer, boy with silver hair, cool pastel idol jacket and lavender headphones. Full body, front view, standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Centered, 2.5 heads tall, big sparkly eyes open, soft blush cheeks, gentle smile with mouth closed. Soft 3D pastel style like a vinyl toy, smooth shading, clean outline, pink-lavender-mint palette, kawaii. Transparent background, no shadow on ground, no text, single character only, 1024x1024.</t>
         </is>
       </c>
-      <c r="H189" s="4" t="inlineStr"/>
-    </row>
-    <row r="190">
+      <c r="H189" s="4" t="n"/>
+    </row>
+    <row r="190" ht="45" customHeight="1" s="12">
       <c r="A190" s="4" t="inlineStr">
         <is>
           <t>B2</t>
@@ -9340,9 +9543,9 @@
           <t>Same character, same outfit, exact same pose, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: eyes gently closed as if blinking. Gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H190" s="4" t="inlineStr"/>
-    </row>
-    <row r="191">
+      <c r="H190" s="4" t="n"/>
+    </row>
+    <row r="191" ht="45" customHeight="1" s="12">
       <c r="A191" s="4" t="inlineStr">
         <is>
           <t>B2</t>
@@ -9376,9 +9579,9 @@
           <t>Same character, same outfit, exact same pose, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: mouth open happily as if talking "ah". Eyes open. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H191" s="4" t="inlineStr"/>
-    </row>
-    <row r="192">
+      <c r="H191" s="4" t="n"/>
+    </row>
+    <row r="192" ht="60" customHeight="1" s="12">
       <c r="A192" s="4" t="inlineStr">
         <is>
           <t>B2</t>
@@ -9412,9 +9615,9 @@
           <t>Same character, same outfit, exact same pose, body, face, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: hair and hair accessories gently swaying to the LEFT as if blown by a soft breeze (only hair tips, strands and ribbons shift slightly left). Eyes open, gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H192" s="4" t="inlineStr"/>
-    </row>
-    <row r="193">
+      <c r="H192" s="4" t="n"/>
+    </row>
+    <row r="193" ht="60" customHeight="1" s="12">
       <c r="A193" s="4" t="inlineStr">
         <is>
           <t>B2</t>
@@ -9448,9 +9651,9 @@
           <t>Same character, same outfit, exact same pose, body, face, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: hair and hair accessories gently swaying to the RIGHT as if blown by a soft breeze (only hair tips, strands and ribbons shift slightly right). Eyes open, gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H193" s="4" t="inlineStr"/>
-    </row>
-    <row r="194">
+      <c r="H193" s="4" t="n"/>
+    </row>
+    <row r="194" ht="60" customHeight="1" s="12">
       <c r="A194" s="4" t="inlineStr">
         <is>
           <t>B2</t>
@@ -9484,9 +9687,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: happily ready to catch a gift, both hands cupped together in front of the chest with palms facing up, empty hands, not holding anything (no gift box, no props), clear empty space above the palms, eyes sparkling looking at the hands, big happy smile with mouth open, slight lean forward. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H194" s="4" t="inlineStr"/>
-    </row>
-    <row r="195">
+      <c r="H194" s="4" t="n"/>
+    </row>
+    <row r="195" ht="45" customHeight="1" s="12">
       <c r="A195" s="4" t="inlineStr">
         <is>
           <t>B2</t>
@@ -9520,9 +9723,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: super excited jumping pose, both arms raised high in celebration, empty hands, not holding anything (no gift box, no props), eyes closed happily (^ ^), wide open smile, tiny hearts and sparkles around the head. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H195" s="4" t="inlineStr"/>
-    </row>
-    <row r="196">
+      <c r="H195" s="4" t="n"/>
+    </row>
+    <row r="196" ht="45" customHeight="1" s="12">
       <c r="A196" s="4" t="inlineStr">
         <is>
           <t>B2</t>
@@ -9556,9 +9759,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: making a finger heart toward the viewer with one hand near the cheek, other arm relaxed, not holding anything else (no gift box, no props), winking, cute blush, small smile. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H196" s="4" t="inlineStr"/>
-    </row>
-    <row r="197">
+      <c r="H196" s="4" t="n"/>
+    </row>
+    <row r="197" ht="60" customHeight="1" s="12">
       <c r="A197" s="4" t="inlineStr">
         <is>
           <t>B2</t>
@@ -9592,9 +9795,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance move — body leaning to the LEFT, left arm raised up with index finger pointing to the sky, right hand on hip, right knee slightly bent, empty hands, not holding anything (no gift box, no props), cheerful open smile, small music notes around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H197" s="4" t="inlineStr"/>
-    </row>
-    <row r="198">
+      <c r="H197" s="4" t="n"/>
+    </row>
+    <row r="198" ht="60" customHeight="1" s="12">
       <c r="A198" s="4" t="inlineStr">
         <is>
           <t>B2</t>
@@ -9628,9 +9831,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance move — body leaning to the RIGHT, right arm raised up with index finger pointing to the sky, left hand on hip, left knee slightly bent, empty hands, not holding anything (no gift box, no props), cheerful open smile, small music notes around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H198" s="4" t="inlineStr"/>
-    </row>
-    <row r="199">
+      <c r="H198" s="4" t="n"/>
+    </row>
+    <row r="199" ht="45" customHeight="1" s="12">
       <c r="A199" s="4" t="inlineStr">
         <is>
           <t>B2</t>
@@ -9664,9 +9867,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance finishing pose — both hands making peace signs (V) next to the face, one foot kicked up behind, empty hands, not holding anything (no gift box, no props), winking with a big smile, sparkles around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H199" s="4" t="inlineStr"/>
-    </row>
-    <row r="200">
+      <c r="H199" s="4" t="n"/>
+    </row>
+    <row r="200" ht="45" customHeight="1" s="12">
       <c r="A200" s="4" t="inlineStr">
         <is>
           <t>B2</t>
@@ -9700,9 +9903,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: walking toward the viewer, front view, LEFT foot stepping forward, right arm swinging forward and left arm back, empty hands, not holding anything (no gift box, no props), happy smile, slight bounce. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H200" s="4" t="inlineStr"/>
-    </row>
-    <row r="201">
+      <c r="H200" s="4" t="n"/>
+    </row>
+    <row r="201" ht="45" customHeight="1" s="12">
       <c r="A201" s="4" t="inlineStr">
         <is>
           <t>B2</t>
@@ -9736,9 +9939,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: walking toward the viewer, front view, RIGHT foot stepping forward, left arm swinging forward and right arm back, empty hands, not holding anything (no gift box, no props), happy smile, slight bounce. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H201" s="4" t="inlineStr"/>
-    </row>
-    <row r="202">
+      <c r="H201" s="4" t="n"/>
+    </row>
+    <row r="202" ht="45" customHeight="1" s="12">
       <c r="A202" s="4" t="inlineStr">
         <is>
           <t>B2</t>
@@ -9772,9 +9975,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: close to the viewer, front view, one hand touching the lips about to blow a kiss, eyes gently closed, cute blush, other arm relaxed, not holding anything else (no gift box, no props). Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H202" s="4" t="inlineStr"/>
-    </row>
-    <row r="203">
+      <c r="H202" s="4" t="n"/>
+    </row>
+    <row r="203" ht="60" customHeight="1" s="12">
       <c r="A203" s="4" t="inlineStr">
         <is>
           <t>B2</t>
@@ -9808,9 +10011,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: blowing a kiss toward the viewer, arm stretched forward with open palm from the lips, lips puckered, winking, cute blush, a small pink heart floating out from the hand, not holding anything else (no gift box, no props). Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H203" s="4" t="inlineStr"/>
-    </row>
-    <row r="204">
+      <c r="H203" s="4" t="n"/>
+    </row>
+    <row r="204" ht="45" customHeight="1" s="12">
       <c r="A204" s="4" t="inlineStr">
         <is>
           <t>B2</t>
@@ -9844,9 +10047,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: back view, walking away from the viewer, LEFT foot stepping forward, arms swinging naturally, empty hands, not holding anything (no gift box, no props), showing the back of the outfit and hair. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H204" s="4" t="inlineStr"/>
-    </row>
-    <row r="205">
+      <c r="H204" s="4" t="n"/>
+    </row>
+    <row r="205" ht="45" customHeight="1" s="12">
       <c r="A205" s="4" t="inlineStr">
         <is>
           <t>B2</t>
@@ -9880,9 +10083,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: back view, walking away from the viewer, RIGHT foot stepping forward, arms swinging naturally, empty hands, not holding anything (no gift box, no props), showing the back of the outfit and hair. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H205" s="4" t="inlineStr"/>
-    </row>
-    <row r="206">
+      <c r="H205" s="4" t="n"/>
+    </row>
+    <row r="206" ht="75" customHeight="1" s="12">
       <c r="A206" s="4" t="inlineStr">
         <is>
           <t>B3</t>
@@ -9916,9 +10119,9 @@
           <t>Cute chibi mascot character for a TikTok live streamer, boy with black messy hair, gamer hoodie with controller print, gaming headset. Full body, front view, standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Centered, 2.5 heads tall, big sparkly eyes open, soft blush cheeks, gentle smile with mouth closed. Soft 3D pastel style like a vinyl toy, smooth shading, clean outline, pink-lavender-mint palette, kawaii. Transparent background, no shadow on ground, no text, single character only, 1024x1024.</t>
         </is>
       </c>
-      <c r="H206" s="4" t="inlineStr"/>
-    </row>
-    <row r="207">
+      <c r="H206" s="4" t="n"/>
+    </row>
+    <row r="207" ht="45" customHeight="1" s="12">
       <c r="A207" s="4" t="inlineStr">
         <is>
           <t>B3</t>
@@ -9952,9 +10155,9 @@
           <t>Same character, same outfit, exact same pose, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: eyes gently closed as if blinking. Gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H207" s="4" t="inlineStr"/>
-    </row>
-    <row r="208">
+      <c r="H207" s="4" t="n"/>
+    </row>
+    <row r="208" ht="45" customHeight="1" s="12">
       <c r="A208" s="4" t="inlineStr">
         <is>
           <t>B3</t>
@@ -9988,9 +10191,9 @@
           <t>Same character, same outfit, exact same pose, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: mouth open happily as if talking "ah". Eyes open. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H208" s="4" t="inlineStr"/>
-    </row>
-    <row r="209">
+      <c r="H208" s="4" t="n"/>
+    </row>
+    <row r="209" ht="60" customHeight="1" s="12">
       <c r="A209" s="4" t="inlineStr">
         <is>
           <t>B3</t>
@@ -10024,9 +10227,9 @@
           <t>Same character, same outfit, exact same pose, body, face, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: hair and hair accessories gently swaying to the LEFT as if blown by a soft breeze (only hair tips, strands and ribbons shift slightly left). Eyes open, gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H209" s="4" t="inlineStr"/>
-    </row>
-    <row r="210">
+      <c r="H209" s="4" t="n"/>
+    </row>
+    <row r="210" ht="60" customHeight="1" s="12">
       <c r="A210" s="4" t="inlineStr">
         <is>
           <t>B3</t>
@@ -10060,9 +10263,9 @@
           <t>Same character, same outfit, exact same pose, body, face, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: hair and hair accessories gently swaying to the RIGHT as if blown by a soft breeze (only hair tips, strands and ribbons shift slightly right). Eyes open, gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H210" s="4" t="inlineStr"/>
-    </row>
-    <row r="211">
+      <c r="H210" s="4" t="n"/>
+    </row>
+    <row r="211" ht="60" customHeight="1" s="12">
       <c r="A211" s="4" t="inlineStr">
         <is>
           <t>B3</t>
@@ -10096,9 +10299,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: happily ready to catch a gift, both hands cupped together in front of the chest with palms facing up, empty hands, not holding anything (no gift box, no props), clear empty space above the palms, eyes sparkling looking at the hands, big happy smile with mouth open, slight lean forward. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H211" s="4" t="inlineStr"/>
-    </row>
-    <row r="212">
+      <c r="H211" s="4" t="n"/>
+    </row>
+    <row r="212" ht="45" customHeight="1" s="12">
       <c r="A212" s="4" t="inlineStr">
         <is>
           <t>B3</t>
@@ -10132,9 +10335,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: super excited jumping pose, both arms raised high in celebration, empty hands, not holding anything (no gift box, no props), eyes closed happily (^ ^), wide open smile, tiny hearts and sparkles around the head. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H212" s="4" t="inlineStr"/>
-    </row>
-    <row r="213">
+      <c r="H212" s="4" t="n"/>
+    </row>
+    <row r="213" ht="45" customHeight="1" s="12">
       <c r="A213" s="4" t="inlineStr">
         <is>
           <t>B3</t>
@@ -10168,9 +10371,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: making a finger heart toward the viewer with one hand near the cheek, other arm relaxed, not holding anything else (no gift box, no props), winking, cute blush, small smile. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H213" s="4" t="inlineStr"/>
-    </row>
-    <row r="214">
+      <c r="H213" s="4" t="n"/>
+    </row>
+    <row r="214" ht="60" customHeight="1" s="12">
       <c r="A214" s="4" t="inlineStr">
         <is>
           <t>B3</t>
@@ -10204,9 +10407,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance move — body leaning to the LEFT, left arm raised up with index finger pointing to the sky, right hand on hip, right knee slightly bent, empty hands, not holding anything (no gift box, no props), cheerful open smile, small music notes around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H214" s="4" t="inlineStr"/>
-    </row>
-    <row r="215">
+      <c r="H214" s="4" t="n"/>
+    </row>
+    <row r="215" ht="60" customHeight="1" s="12">
       <c r="A215" s="4" t="inlineStr">
         <is>
           <t>B3</t>
@@ -10240,9 +10443,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance move — body leaning to the RIGHT, right arm raised up with index finger pointing to the sky, left hand on hip, left knee slightly bent, empty hands, not holding anything (no gift box, no props), cheerful open smile, small music notes around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H215" s="4" t="inlineStr"/>
-    </row>
-    <row r="216">
+      <c r="H215" s="4" t="n"/>
+    </row>
+    <row r="216" ht="45" customHeight="1" s="12">
       <c r="A216" s="4" t="inlineStr">
         <is>
           <t>B3</t>
@@ -10276,9 +10479,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance finishing pose — both hands making peace signs (V) next to the face, one foot kicked up behind, empty hands, not holding anything (no gift box, no props), winking with a big smile, sparkles around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H216" s="4" t="inlineStr"/>
-    </row>
-    <row r="217">
+      <c r="H216" s="4" t="n"/>
+    </row>
+    <row r="217" ht="45" customHeight="1" s="12">
       <c r="A217" s="4" t="inlineStr">
         <is>
           <t>B3</t>
@@ -10312,9 +10515,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: walking toward the viewer, front view, LEFT foot stepping forward, right arm swinging forward and left arm back, empty hands, not holding anything (no gift box, no props), happy smile, slight bounce. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H217" s="4" t="inlineStr"/>
-    </row>
-    <row r="218">
+      <c r="H217" s="4" t="n"/>
+    </row>
+    <row r="218" ht="45" customHeight="1" s="12">
       <c r="A218" s="4" t="inlineStr">
         <is>
           <t>B3</t>
@@ -10348,9 +10551,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: walking toward the viewer, front view, RIGHT foot stepping forward, left arm swinging forward and right arm back, empty hands, not holding anything (no gift box, no props), happy smile, slight bounce. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H218" s="4" t="inlineStr"/>
-    </row>
-    <row r="219">
+      <c r="H218" s="4" t="n"/>
+    </row>
+    <row r="219" ht="45" customHeight="1" s="12">
       <c r="A219" s="4" t="inlineStr">
         <is>
           <t>B3</t>
@@ -10384,9 +10587,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: close to the viewer, front view, one hand touching the lips about to blow a kiss, eyes gently closed, cute blush, other arm relaxed, not holding anything else (no gift box, no props). Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H219" s="4" t="inlineStr"/>
-    </row>
-    <row r="220">
+      <c r="H219" s="4" t="n"/>
+    </row>
+    <row r="220" ht="60" customHeight="1" s="12">
       <c r="A220" s="4" t="inlineStr">
         <is>
           <t>B3</t>
@@ -10420,9 +10623,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: blowing a kiss toward the viewer, arm stretched forward with open palm from the lips, lips puckered, winking, cute blush, a small pink heart floating out from the hand, not holding anything else (no gift box, no props). Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H220" s="4" t="inlineStr"/>
-    </row>
-    <row r="221">
+      <c r="H220" s="4" t="n"/>
+    </row>
+    <row r="221" ht="45" customHeight="1" s="12">
       <c r="A221" s="4" t="inlineStr">
         <is>
           <t>B3</t>
@@ -10456,9 +10659,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: back view, walking away from the viewer, LEFT foot stepping forward, arms swinging naturally, empty hands, not holding anything (no gift box, no props), showing the back of the outfit and hair. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H221" s="4" t="inlineStr"/>
-    </row>
-    <row r="222">
+      <c r="H221" s="4" t="n"/>
+    </row>
+    <row r="222" ht="45" customHeight="1" s="12">
       <c r="A222" s="4" t="inlineStr">
         <is>
           <t>B3</t>
@@ -10492,9 +10695,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: back view, walking away from the viewer, RIGHT foot stepping forward, arms swinging naturally, empty hands, not holding anything (no gift box, no props), showing the back of the outfit and hair. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H222" s="4" t="inlineStr"/>
-    </row>
-    <row r="223">
+      <c r="H222" s="4" t="n"/>
+    </row>
+    <row r="223" ht="75" customHeight="1" s="12">
       <c r="A223" s="5" t="inlineStr">
         <is>
           <t>B4</t>
@@ -10534,7 +10737,7 @@
         </is>
       </c>
     </row>
-    <row r="224">
+    <row r="224" ht="45" customHeight="1" s="12">
       <c r="A224" s="5" t="inlineStr">
         <is>
           <t>B4</t>
@@ -10574,7 +10777,7 @@
         </is>
       </c>
     </row>
-    <row r="225">
+    <row r="225" ht="45" customHeight="1" s="12">
       <c r="A225" s="5" t="inlineStr">
         <is>
           <t>B4</t>
@@ -10614,7 +10817,7 @@
         </is>
       </c>
     </row>
-    <row r="226">
+    <row r="226" ht="60" customHeight="1" s="12">
       <c r="A226" s="5" t="inlineStr">
         <is>
           <t>B4</t>
@@ -10654,7 +10857,7 @@
         </is>
       </c>
     </row>
-    <row r="227">
+    <row r="227" ht="60" customHeight="1" s="12">
       <c r="A227" s="5" t="inlineStr">
         <is>
           <t>B4</t>
@@ -10694,7 +10897,7 @@
         </is>
       </c>
     </row>
-    <row r="228">
+    <row r="228" ht="60" customHeight="1" s="12">
       <c r="A228" s="5" t="inlineStr">
         <is>
           <t>B4</t>
@@ -10734,7 +10937,7 @@
         </is>
       </c>
     </row>
-    <row r="229">
+    <row r="229" ht="45" customHeight="1" s="12">
       <c r="A229" s="5" t="inlineStr">
         <is>
           <t>B4</t>
@@ -10774,7 +10977,7 @@
         </is>
       </c>
     </row>
-    <row r="230">
+    <row r="230" ht="45" customHeight="1" s="12">
       <c r="A230" s="5" t="inlineStr">
         <is>
           <t>B4</t>
@@ -10814,7 +11017,7 @@
         </is>
       </c>
     </row>
-    <row r="231">
+    <row r="231" ht="60" customHeight="1" s="12">
       <c r="A231" s="5" t="inlineStr">
         <is>
           <t>B4</t>
@@ -10854,7 +11057,7 @@
         </is>
       </c>
     </row>
-    <row r="232">
+    <row r="232" ht="60" customHeight="1" s="12">
       <c r="A232" s="5" t="inlineStr">
         <is>
           <t>B4</t>
@@ -10894,7 +11097,7 @@
         </is>
       </c>
     </row>
-    <row r="233">
+    <row r="233" ht="45" customHeight="1" s="12">
       <c r="A233" s="5" t="inlineStr">
         <is>
           <t>B4</t>
@@ -10934,7 +11137,7 @@
         </is>
       </c>
     </row>
-    <row r="234">
+    <row r="234" ht="45" customHeight="1" s="12">
       <c r="A234" s="5" t="inlineStr">
         <is>
           <t>B4</t>
@@ -10974,7 +11177,7 @@
         </is>
       </c>
     </row>
-    <row r="235">
+    <row r="235" ht="45" customHeight="1" s="12">
       <c r="A235" s="5" t="inlineStr">
         <is>
           <t>B4</t>
@@ -11014,7 +11217,7 @@
         </is>
       </c>
     </row>
-    <row r="236">
+    <row r="236" ht="45" customHeight="1" s="12">
       <c r="A236" s="5" t="inlineStr">
         <is>
           <t>B4</t>
@@ -11054,7 +11257,7 @@
         </is>
       </c>
     </row>
-    <row r="237">
+    <row r="237" ht="60" customHeight="1" s="12">
       <c r="A237" s="5" t="inlineStr">
         <is>
           <t>B4</t>
@@ -11094,7 +11297,7 @@
         </is>
       </c>
     </row>
-    <row r="238">
+    <row r="238" ht="45" customHeight="1" s="12">
       <c r="A238" s="5" t="inlineStr">
         <is>
           <t>B4</t>
@@ -11134,7 +11337,7 @@
         </is>
       </c>
     </row>
-    <row r="239">
+    <row r="239" ht="45" customHeight="1" s="12">
       <c r="A239" s="5" t="inlineStr">
         <is>
           <t>B4</t>
@@ -11174,7 +11377,7 @@
         </is>
       </c>
     </row>
-    <row r="240">
+    <row r="240" ht="75" customHeight="1" s="12">
       <c r="A240" s="4" t="inlineStr">
         <is>
           <t>B5</t>
@@ -11208,9 +11411,9 @@
           <t>Cute chibi mascot character for a TikTok live streamer, boy with red spiky hair, sporty pastel jersey with number 7, sneakers. Full body, front view, standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Centered, 2.5 heads tall, big sparkly eyes open, soft blush cheeks, gentle smile with mouth closed. Soft 3D pastel style like a vinyl toy, smooth shading, clean outline, pink-lavender-mint palette, kawaii. Transparent background, no shadow on ground, no text, single character only, 1024x1024.</t>
         </is>
       </c>
-      <c r="H240" s="4" t="inlineStr"/>
-    </row>
-    <row r="241">
+      <c r="H240" s="4" t="n"/>
+    </row>
+    <row r="241" ht="45" customHeight="1" s="12">
       <c r="A241" s="4" t="inlineStr">
         <is>
           <t>B5</t>
@@ -11244,9 +11447,9 @@
           <t>Same character, same outfit, exact same pose, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: eyes gently closed as if blinking. Gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H241" s="4" t="inlineStr"/>
-    </row>
-    <row r="242">
+      <c r="H241" s="4" t="n"/>
+    </row>
+    <row r="242" ht="45" customHeight="1" s="12">
       <c r="A242" s="4" t="inlineStr">
         <is>
           <t>B5</t>
@@ -11280,9 +11483,9 @@
           <t>Same character, same outfit, exact same pose, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: mouth open happily as if talking "ah". Eyes open. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H242" s="4" t="inlineStr"/>
-    </row>
-    <row r="243">
+      <c r="H242" s="4" t="n"/>
+    </row>
+    <row r="243" ht="60" customHeight="1" s="12">
       <c r="A243" s="4" t="inlineStr">
         <is>
           <t>B5</t>
@@ -11316,9 +11519,9 @@
           <t>Same character, same outfit, exact same pose, body, face, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: hair and hair accessories gently swaying to the LEFT as if blown by a soft breeze (only hair tips, strands and ribbons shift slightly left). Eyes open, gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H243" s="4" t="inlineStr"/>
-    </row>
-    <row r="244">
+      <c r="H243" s="4" t="n"/>
+    </row>
+    <row r="244" ht="60" customHeight="1" s="12">
       <c r="A244" s="4" t="inlineStr">
         <is>
           <t>B5</t>
@@ -11352,9 +11555,9 @@
           <t>Same character, same outfit, exact same pose, body, face, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: hair and hair accessories gently swaying to the RIGHT as if blown by a soft breeze (only hair tips, strands and ribbons shift slightly right). Eyes open, gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H244" s="4" t="inlineStr"/>
-    </row>
-    <row r="245">
+      <c r="H244" s="4" t="n"/>
+    </row>
+    <row r="245" ht="60" customHeight="1" s="12">
       <c r="A245" s="4" t="inlineStr">
         <is>
           <t>B5</t>
@@ -11388,9 +11591,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: happily ready to catch a gift, both hands cupped together in front of the chest with palms facing up, empty hands, not holding anything (no gift box, no props), clear empty space above the palms, eyes sparkling looking at the hands, big happy smile with mouth open, slight lean forward. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H245" s="4" t="inlineStr"/>
-    </row>
-    <row r="246">
+      <c r="H245" s="4" t="n"/>
+    </row>
+    <row r="246" ht="45" customHeight="1" s="12">
       <c r="A246" s="4" t="inlineStr">
         <is>
           <t>B5</t>
@@ -11424,9 +11627,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: super excited jumping pose, both arms raised high in celebration, empty hands, not holding anything (no gift box, no props), eyes closed happily (^ ^), wide open smile, tiny hearts and sparkles around the head. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H246" s="4" t="inlineStr"/>
-    </row>
-    <row r="247">
+      <c r="H246" s="4" t="n"/>
+    </row>
+    <row r="247" ht="45" customHeight="1" s="12">
       <c r="A247" s="4" t="inlineStr">
         <is>
           <t>B5</t>
@@ -11460,9 +11663,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: making a finger heart toward the viewer with one hand near the cheek, other arm relaxed, not holding anything else (no gift box, no props), winking, cute blush, small smile. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H247" s="4" t="inlineStr"/>
-    </row>
-    <row r="248">
+      <c r="H247" s="4" t="n"/>
+    </row>
+    <row r="248" ht="60" customHeight="1" s="12">
       <c r="A248" s="4" t="inlineStr">
         <is>
           <t>B5</t>
@@ -11496,9 +11699,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance move — body leaning to the LEFT, left arm raised up with index finger pointing to the sky, right hand on hip, right knee slightly bent, empty hands, not holding anything (no gift box, no props), cheerful open smile, small music notes around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H248" s="4" t="inlineStr"/>
-    </row>
-    <row r="249">
+      <c r="H248" s="4" t="n"/>
+    </row>
+    <row r="249" ht="60" customHeight="1" s="12">
       <c r="A249" s="4" t="inlineStr">
         <is>
           <t>B5</t>
@@ -11532,9 +11735,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance move — body leaning to the RIGHT, right arm raised up with index finger pointing to the sky, left hand on hip, left knee slightly bent, empty hands, not holding anything (no gift box, no props), cheerful open smile, small music notes around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H249" s="4" t="inlineStr"/>
-    </row>
-    <row r="250">
+      <c r="H249" s="4" t="n"/>
+    </row>
+    <row r="250" ht="45" customHeight="1" s="12">
       <c r="A250" s="4" t="inlineStr">
         <is>
           <t>B5</t>
@@ -11568,9 +11771,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance finishing pose — both hands making peace signs (V) next to the face, one foot kicked up behind, empty hands, not holding anything (no gift box, no props), winking with a big smile, sparkles around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H250" s="4" t="inlineStr"/>
-    </row>
-    <row r="251">
+      <c r="H250" s="4" t="n"/>
+    </row>
+    <row r="251" ht="45" customHeight="1" s="12">
       <c r="A251" s="4" t="inlineStr">
         <is>
           <t>B5</t>
@@ -11604,9 +11807,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: walking toward the viewer, front view, LEFT foot stepping forward, right arm swinging forward and left arm back, empty hands, not holding anything (no gift box, no props), happy smile, slight bounce. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H251" s="4" t="inlineStr"/>
-    </row>
-    <row r="252">
+      <c r="H251" s="4" t="n"/>
+    </row>
+    <row r="252" ht="45" customHeight="1" s="12">
       <c r="A252" s="4" t="inlineStr">
         <is>
           <t>B5</t>
@@ -11640,9 +11843,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: walking toward the viewer, front view, RIGHT foot stepping forward, left arm swinging forward and right arm back, empty hands, not holding anything (no gift box, no props), happy smile, slight bounce. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H252" s="4" t="inlineStr"/>
-    </row>
-    <row r="253">
+      <c r="H252" s="4" t="n"/>
+    </row>
+    <row r="253" ht="45" customHeight="1" s="12">
       <c r="A253" s="4" t="inlineStr">
         <is>
           <t>B5</t>
@@ -11676,9 +11879,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: close to the viewer, front view, one hand touching the lips about to blow a kiss, eyes gently closed, cute blush, other arm relaxed, not holding anything else (no gift box, no props). Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H253" s="4" t="inlineStr"/>
-    </row>
-    <row r="254">
+      <c r="H253" s="4" t="n"/>
+    </row>
+    <row r="254" ht="60" customHeight="1" s="12">
       <c r="A254" s="4" t="inlineStr">
         <is>
           <t>B5</t>
@@ -11712,9 +11915,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: blowing a kiss toward the viewer, arm stretched forward with open palm from the lips, lips puckered, winking, cute blush, a small pink heart floating out from the hand, not holding anything else (no gift box, no props). Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H254" s="4" t="inlineStr"/>
-    </row>
-    <row r="255">
+      <c r="H254" s="4" t="n"/>
+    </row>
+    <row r="255" ht="45" customHeight="1" s="12">
       <c r="A255" s="4" t="inlineStr">
         <is>
           <t>B5</t>
@@ -11748,9 +11951,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: back view, walking away from the viewer, LEFT foot stepping forward, arms swinging naturally, empty hands, not holding anything (no gift box, no props), showing the back of the outfit and hair. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H255" s="4" t="inlineStr"/>
-    </row>
-    <row r="256">
+      <c r="H255" s="4" t="n"/>
+    </row>
+    <row r="256" ht="45" customHeight="1" s="12">
       <c r="A256" s="4" t="inlineStr">
         <is>
           <t>B5</t>
@@ -11784,9 +11987,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: back view, walking away from the viewer, RIGHT foot stepping forward, arms swinging naturally, empty hands, not holding anything (no gift box, no props), showing the back of the outfit and hair. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H256" s="4" t="inlineStr"/>
-    </row>
-    <row r="257">
+      <c r="H256" s="4" t="n"/>
+    </row>
+    <row r="257" ht="75" customHeight="1" s="12">
       <c r="A257" s="4" t="inlineStr">
         <is>
           <t>B6</t>
@@ -11820,9 +12023,9 @@
           <t>Cute chibi mascot character for a TikTok live streamer, boy with orange hair, fox-ear hoodie with fluffy tail, cute mittens. Full body, front view, standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Centered, 2.5 heads tall, big sparkly eyes open, soft blush cheeks, gentle smile with mouth closed. Soft 3D pastel style like a vinyl toy, smooth shading, clean outline, pink-lavender-mint palette, kawaii. Transparent background, no shadow on ground, no text, single character only, 1024x1024.</t>
         </is>
       </c>
-      <c r="H257" s="4" t="inlineStr"/>
-    </row>
-    <row r="258">
+      <c r="H257" s="4" t="n"/>
+    </row>
+    <row r="258" ht="45" customHeight="1" s="12">
       <c r="A258" s="4" t="inlineStr">
         <is>
           <t>B6</t>
@@ -11856,9 +12059,9 @@
           <t>Same character, same outfit, exact same pose, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: eyes gently closed as if blinking. Gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H258" s="4" t="inlineStr"/>
-    </row>
-    <row r="259">
+      <c r="H258" s="4" t="n"/>
+    </row>
+    <row r="259" ht="45" customHeight="1" s="12">
       <c r="A259" s="4" t="inlineStr">
         <is>
           <t>B6</t>
@@ -11892,9 +12095,9 @@
           <t>Same character, same outfit, exact same pose, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: mouth open happily as if talking "ah". Eyes open. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H259" s="4" t="inlineStr"/>
-    </row>
-    <row r="260">
+      <c r="H259" s="4" t="n"/>
+    </row>
+    <row r="260" ht="60" customHeight="1" s="12">
       <c r="A260" s="4" t="inlineStr">
         <is>
           <t>B6</t>
@@ -11928,9 +12131,9 @@
           <t>Same character, same outfit, exact same pose, body, face, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: hair and hair accessories gently swaying to the LEFT as if blown by a soft breeze (only hair tips, strands and ribbons shift slightly left). Eyes open, gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H260" s="4" t="inlineStr"/>
-    </row>
-    <row r="261">
+      <c r="H260" s="4" t="n"/>
+    </row>
+    <row r="261" ht="60" customHeight="1" s="12">
       <c r="A261" s="4" t="inlineStr">
         <is>
           <t>B6</t>
@@ -11964,9 +12167,9 @@
           <t>Same character, same outfit, exact same pose, body, face, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: hair and hair accessories gently swaying to the RIGHT as if blown by a soft breeze (only hair tips, strands and ribbons shift slightly right). Eyes open, gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H261" s="4" t="inlineStr"/>
-    </row>
-    <row r="262">
+      <c r="H261" s="4" t="n"/>
+    </row>
+    <row r="262" ht="60" customHeight="1" s="12">
       <c r="A262" s="4" t="inlineStr">
         <is>
           <t>B6</t>
@@ -12000,9 +12203,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: happily ready to catch a gift, both hands cupped together in front of the chest with palms facing up, empty hands, not holding anything (no gift box, no props), clear empty space above the palms, eyes sparkling looking at the hands, big happy smile with mouth open, slight lean forward. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H262" s="4" t="inlineStr"/>
-    </row>
-    <row r="263">
+      <c r="H262" s="4" t="n"/>
+    </row>
+    <row r="263" ht="45" customHeight="1" s="12">
       <c r="A263" s="4" t="inlineStr">
         <is>
           <t>B6</t>
@@ -12036,9 +12239,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: super excited jumping pose, both arms raised high in celebration, empty hands, not holding anything (no gift box, no props), eyes closed happily (^ ^), wide open smile, tiny hearts and sparkles around the head. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H263" s="4" t="inlineStr"/>
-    </row>
-    <row r="264">
+      <c r="H263" s="4" t="n"/>
+    </row>
+    <row r="264" ht="45" customHeight="1" s="12">
       <c r="A264" s="4" t="inlineStr">
         <is>
           <t>B6</t>
@@ -12072,9 +12275,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: making a finger heart toward the viewer with one hand near the cheek, other arm relaxed, not holding anything else (no gift box, no props), winking, cute blush, small smile. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H264" s="4" t="inlineStr"/>
-    </row>
-    <row r="265">
+      <c r="H264" s="4" t="n"/>
+    </row>
+    <row r="265" ht="60" customHeight="1" s="12">
       <c r="A265" s="4" t="inlineStr">
         <is>
           <t>B6</t>
@@ -12108,9 +12311,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance move — body leaning to the LEFT, left arm raised up with index finger pointing to the sky, right hand on hip, right knee slightly bent, empty hands, not holding anything (no gift box, no props), cheerful open smile, small music notes around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H265" s="4" t="inlineStr"/>
-    </row>
-    <row r="266">
+      <c r="H265" s="4" t="n"/>
+    </row>
+    <row r="266" ht="60" customHeight="1" s="12">
       <c r="A266" s="4" t="inlineStr">
         <is>
           <t>B6</t>
@@ -12144,9 +12347,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance move — body leaning to the RIGHT, right arm raised up with index finger pointing to the sky, left hand on hip, left knee slightly bent, empty hands, not holding anything (no gift box, no props), cheerful open smile, small music notes around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H266" s="4" t="inlineStr"/>
-    </row>
-    <row r="267">
+      <c r="H266" s="4" t="n"/>
+    </row>
+    <row r="267" ht="45" customHeight="1" s="12">
       <c r="A267" s="4" t="inlineStr">
         <is>
           <t>B6</t>
@@ -12180,9 +12383,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance finishing pose — both hands making peace signs (V) next to the face, one foot kicked up behind, empty hands, not holding anything (no gift box, no props), winking with a big smile, sparkles around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H267" s="4" t="inlineStr"/>
-    </row>
-    <row r="268">
+      <c r="H267" s="4" t="n"/>
+    </row>
+    <row r="268" ht="45" customHeight="1" s="12">
       <c r="A268" s="4" t="inlineStr">
         <is>
           <t>B6</t>
@@ -12216,9 +12419,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: walking toward the viewer, front view, LEFT foot stepping forward, right arm swinging forward and left arm back, empty hands, not holding anything (no gift box, no props), happy smile, slight bounce. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H268" s="4" t="inlineStr"/>
-    </row>
-    <row r="269">
+      <c r="H268" s="4" t="n"/>
+    </row>
+    <row r="269" ht="45" customHeight="1" s="12">
       <c r="A269" s="4" t="inlineStr">
         <is>
           <t>B6</t>
@@ -12252,9 +12455,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: walking toward the viewer, front view, RIGHT foot stepping forward, left arm swinging forward and right arm back, empty hands, not holding anything (no gift box, no props), happy smile, slight bounce. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H269" s="4" t="inlineStr"/>
-    </row>
-    <row r="270">
+      <c r="H269" s="4" t="n"/>
+    </row>
+    <row r="270" ht="45" customHeight="1" s="12">
       <c r="A270" s="4" t="inlineStr">
         <is>
           <t>B6</t>
@@ -12288,9 +12491,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: close to the viewer, front view, one hand touching the lips about to blow a kiss, eyes gently closed, cute blush, other arm relaxed, not holding anything else (no gift box, no props). Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H270" s="4" t="inlineStr"/>
-    </row>
-    <row r="271">
+      <c r="H270" s="4" t="n"/>
+    </row>
+    <row r="271" ht="60" customHeight="1" s="12">
       <c r="A271" s="4" t="inlineStr">
         <is>
           <t>B6</t>
@@ -12324,9 +12527,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: blowing a kiss toward the viewer, arm stretched forward with open palm from the lips, lips puckered, winking, cute blush, a small pink heart floating out from the hand, not holding anything else (no gift box, no props). Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H271" s="4" t="inlineStr"/>
-    </row>
-    <row r="272">
+      <c r="H271" s="4" t="n"/>
+    </row>
+    <row r="272" ht="45" customHeight="1" s="12">
       <c r="A272" s="4" t="inlineStr">
         <is>
           <t>B6</t>
@@ -12360,9 +12563,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: back view, walking away from the viewer, LEFT foot stepping forward, arms swinging naturally, empty hands, not holding anything (no gift box, no props), showing the back of the outfit and hair. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H272" s="4" t="inlineStr"/>
-    </row>
-    <row r="273">
+      <c r="H272" s="4" t="n"/>
+    </row>
+    <row r="273" ht="45" customHeight="1" s="12">
       <c r="A273" s="4" t="inlineStr">
         <is>
           <t>B6</t>
@@ -12396,9 +12599,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: back view, walking away from the viewer, RIGHT foot stepping forward, arms swinging naturally, empty hands, not holding anything (no gift box, no props), showing the back of the outfit and hair. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H273" s="4" t="inlineStr"/>
-    </row>
-    <row r="274">
+      <c r="H273" s="4" t="n"/>
+    </row>
+    <row r="274" ht="75" customHeight="1" s="12">
       <c r="A274" s="5" t="inlineStr">
         <is>
           <t>B7</t>
@@ -12438,7 +12641,7 @@
         </is>
       </c>
     </row>
-    <row r="275">
+    <row r="275" ht="45" customHeight="1" s="12">
       <c r="A275" s="5" t="inlineStr">
         <is>
           <t>B7</t>
@@ -12478,7 +12681,7 @@
         </is>
       </c>
     </row>
-    <row r="276">
+    <row r="276" ht="45" customHeight="1" s="12">
       <c r="A276" s="5" t="inlineStr">
         <is>
           <t>B7</t>
@@ -12518,7 +12721,7 @@
         </is>
       </c>
     </row>
-    <row r="277">
+    <row r="277" ht="60" customHeight="1" s="12">
       <c r="A277" s="5" t="inlineStr">
         <is>
           <t>B7</t>
@@ -12558,7 +12761,7 @@
         </is>
       </c>
     </row>
-    <row r="278">
+    <row r="278" ht="60" customHeight="1" s="12">
       <c r="A278" s="5" t="inlineStr">
         <is>
           <t>B7</t>
@@ -12598,7 +12801,7 @@
         </is>
       </c>
     </row>
-    <row r="279">
+    <row r="279" ht="60" customHeight="1" s="12">
       <c r="A279" s="5" t="inlineStr">
         <is>
           <t>B7</t>
@@ -12638,7 +12841,7 @@
         </is>
       </c>
     </row>
-    <row r="280">
+    <row r="280" ht="45" customHeight="1" s="12">
       <c r="A280" s="5" t="inlineStr">
         <is>
           <t>B7</t>
@@ -12678,7 +12881,7 @@
         </is>
       </c>
     </row>
-    <row r="281">
+    <row r="281" ht="45" customHeight="1" s="12">
       <c r="A281" s="5" t="inlineStr">
         <is>
           <t>B7</t>
@@ -12718,7 +12921,7 @@
         </is>
       </c>
     </row>
-    <row r="282">
+    <row r="282" ht="60" customHeight="1" s="12">
       <c r="A282" s="5" t="inlineStr">
         <is>
           <t>B7</t>
@@ -12758,7 +12961,7 @@
         </is>
       </c>
     </row>
-    <row r="283">
+    <row r="283" ht="60" customHeight="1" s="12">
       <c r="A283" s="5" t="inlineStr">
         <is>
           <t>B7</t>
@@ -12798,7 +13001,7 @@
         </is>
       </c>
     </row>
-    <row r="284">
+    <row r="284" ht="45" customHeight="1" s="12">
       <c r="A284" s="5" t="inlineStr">
         <is>
           <t>B7</t>
@@ -12838,7 +13041,7 @@
         </is>
       </c>
     </row>
-    <row r="285">
+    <row r="285" ht="45" customHeight="1" s="12">
       <c r="A285" s="5" t="inlineStr">
         <is>
           <t>B7</t>
@@ -12878,7 +13081,7 @@
         </is>
       </c>
     </row>
-    <row r="286">
+    <row r="286" ht="45" customHeight="1" s="12">
       <c r="A286" s="5" t="inlineStr">
         <is>
           <t>B7</t>
@@ -12918,7 +13121,7 @@
         </is>
       </c>
     </row>
-    <row r="287">
+    <row r="287" ht="45" customHeight="1" s="12">
       <c r="A287" s="5" t="inlineStr">
         <is>
           <t>B7</t>
@@ -12958,7 +13161,7 @@
         </is>
       </c>
     </row>
-    <row r="288">
+    <row r="288" ht="60" customHeight="1" s="12">
       <c r="A288" s="5" t="inlineStr">
         <is>
           <t>B7</t>
@@ -12998,7 +13201,7 @@
         </is>
       </c>
     </row>
-    <row r="289">
+    <row r="289" ht="45" customHeight="1" s="12">
       <c r="A289" s="5" t="inlineStr">
         <is>
           <t>B7</t>
@@ -13038,7 +13241,7 @@
         </is>
       </c>
     </row>
-    <row r="290">
+    <row r="290" ht="45" customHeight="1" s="12">
       <c r="A290" s="5" t="inlineStr">
         <is>
           <t>B7</t>
@@ -13078,7 +13281,7 @@
         </is>
       </c>
     </row>
-    <row r="291">
+    <row r="291" ht="75" customHeight="1" s="12">
       <c r="A291" s="5" t="inlineStr">
         <is>
           <t>B8</t>
@@ -13118,7 +13321,7 @@
         </is>
       </c>
     </row>
-    <row r="292">
+    <row r="292" ht="45" customHeight="1" s="12">
       <c r="A292" s="5" t="inlineStr">
         <is>
           <t>B8</t>
@@ -13158,7 +13361,7 @@
         </is>
       </c>
     </row>
-    <row r="293">
+    <row r="293" ht="45" customHeight="1" s="12">
       <c r="A293" s="5" t="inlineStr">
         <is>
           <t>B8</t>
@@ -13198,7 +13401,7 @@
         </is>
       </c>
     </row>
-    <row r="294">
+    <row r="294" ht="60" customHeight="1" s="12">
       <c r="A294" s="5" t="inlineStr">
         <is>
           <t>B8</t>
@@ -13238,7 +13441,7 @@
         </is>
       </c>
     </row>
-    <row r="295">
+    <row r="295" ht="60" customHeight="1" s="12">
       <c r="A295" s="5" t="inlineStr">
         <is>
           <t>B8</t>
@@ -13278,7 +13481,7 @@
         </is>
       </c>
     </row>
-    <row r="296">
+    <row r="296" ht="60" customHeight="1" s="12">
       <c r="A296" s="5" t="inlineStr">
         <is>
           <t>B8</t>
@@ -13318,7 +13521,7 @@
         </is>
       </c>
     </row>
-    <row r="297">
+    <row r="297" ht="45" customHeight="1" s="12">
       <c r="A297" s="5" t="inlineStr">
         <is>
           <t>B8</t>
@@ -13358,7 +13561,7 @@
         </is>
       </c>
     </row>
-    <row r="298">
+    <row r="298" ht="45" customHeight="1" s="12">
       <c r="A298" s="5" t="inlineStr">
         <is>
           <t>B8</t>
@@ -13398,7 +13601,7 @@
         </is>
       </c>
     </row>
-    <row r="299">
+    <row r="299" ht="60" customHeight="1" s="12">
       <c r="A299" s="5" t="inlineStr">
         <is>
           <t>B8</t>
@@ -13438,7 +13641,7 @@
         </is>
       </c>
     </row>
-    <row r="300">
+    <row r="300" ht="60" customHeight="1" s="12">
       <c r="A300" s="5" t="inlineStr">
         <is>
           <t>B8</t>
@@ -13478,7 +13681,7 @@
         </is>
       </c>
     </row>
-    <row r="301">
+    <row r="301" ht="45" customHeight="1" s="12">
       <c r="A301" s="5" t="inlineStr">
         <is>
           <t>B8</t>
@@ -13518,7 +13721,7 @@
         </is>
       </c>
     </row>
-    <row r="302">
+    <row r="302" ht="45" customHeight="1" s="12">
       <c r="A302" s="5" t="inlineStr">
         <is>
           <t>B8</t>
@@ -13558,7 +13761,7 @@
         </is>
       </c>
     </row>
-    <row r="303">
+    <row r="303" ht="45" customHeight="1" s="12">
       <c r="A303" s="5" t="inlineStr">
         <is>
           <t>B8</t>
@@ -13598,7 +13801,7 @@
         </is>
       </c>
     </row>
-    <row r="304">
+    <row r="304" ht="45" customHeight="1" s="12">
       <c r="A304" s="5" t="inlineStr">
         <is>
           <t>B8</t>
@@ -13638,7 +13841,7 @@
         </is>
       </c>
     </row>
-    <row r="305">
+    <row r="305" ht="60" customHeight="1" s="12">
       <c r="A305" s="5" t="inlineStr">
         <is>
           <t>B8</t>
@@ -13678,7 +13881,7 @@
         </is>
       </c>
     </row>
-    <row r="306">
+    <row r="306" ht="45" customHeight="1" s="12">
       <c r="A306" s="5" t="inlineStr">
         <is>
           <t>B8</t>
@@ -13718,7 +13921,7 @@
         </is>
       </c>
     </row>
-    <row r="307">
+    <row r="307" ht="45" customHeight="1" s="12">
       <c r="A307" s="5" t="inlineStr">
         <is>
           <t>B8</t>
@@ -13758,7 +13961,7 @@
         </is>
       </c>
     </row>
-    <row r="308">
+    <row r="308" ht="75" customHeight="1" s="12">
       <c r="A308" s="4" t="inlineStr">
         <is>
           <t>B9</t>
@@ -13792,9 +13995,9 @@
           <t>Cute chibi mascot character for a TikTok live streamer, boy with light brown curly hair, puppy-ear hoodie with paw print, red collar scarf. Full body, front view, standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Centered, 2.5 heads tall, big sparkly eyes open, soft blush cheeks, gentle smile with mouth closed. Soft 3D pastel style like a vinyl toy, smooth shading, clean outline, pink-lavender-mint palette, kawaii. Transparent background, no shadow on ground, no text, single character only, 1024x1024.</t>
         </is>
       </c>
-      <c r="H308" s="4" t="inlineStr"/>
-    </row>
-    <row r="309">
+      <c r="H308" s="4" t="n"/>
+    </row>
+    <row r="309" ht="45" customHeight="1" s="12">
       <c r="A309" s="4" t="inlineStr">
         <is>
           <t>B9</t>
@@ -13828,9 +14031,9 @@
           <t>Same character, same outfit, exact same pose, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: eyes gently closed as if blinking. Gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H309" s="4" t="inlineStr"/>
-    </row>
-    <row r="310">
+      <c r="H309" s="4" t="n"/>
+    </row>
+    <row r="310" ht="45" customHeight="1" s="12">
       <c r="A310" s="4" t="inlineStr">
         <is>
           <t>B9</t>
@@ -13864,9 +14067,9 @@
           <t>Same character, same outfit, exact same pose, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: mouth open happily as if talking "ah". Eyes open. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H310" s="4" t="inlineStr"/>
-    </row>
-    <row r="311">
+      <c r="H310" s="4" t="n"/>
+    </row>
+    <row r="311" ht="60" customHeight="1" s="12">
       <c r="A311" s="4" t="inlineStr">
         <is>
           <t>B9</t>
@@ -13900,9 +14103,9 @@
           <t>Same character, same outfit, exact same pose, body, face, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: hair and hair accessories gently swaying to the LEFT as if blown by a soft breeze (only hair tips, strands and ribbons shift slightly left). Eyes open, gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H311" s="4" t="inlineStr"/>
-    </row>
-    <row r="312">
+      <c r="H311" s="4" t="n"/>
+    </row>
+    <row r="312" ht="60" customHeight="1" s="12">
       <c r="A312" s="4" t="inlineStr">
         <is>
           <t>B9</t>
@@ -13936,9 +14139,9 @@
           <t>Same character, same outfit, exact same pose, body, face, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: hair and hair accessories gently swaying to the RIGHT as if blown by a soft breeze (only hair tips, strands and ribbons shift slightly right). Eyes open, gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H312" s="4" t="inlineStr"/>
-    </row>
-    <row r="313">
+      <c r="H312" s="4" t="n"/>
+    </row>
+    <row r="313" ht="60" customHeight="1" s="12">
       <c r="A313" s="4" t="inlineStr">
         <is>
           <t>B9</t>
@@ -13972,9 +14175,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: happily ready to catch a gift, both hands cupped together in front of the chest with palms facing up, empty hands, not holding anything (no gift box, no props), clear empty space above the palms, eyes sparkling looking at the hands, big happy smile with mouth open, slight lean forward. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H313" s="4" t="inlineStr"/>
-    </row>
-    <row r="314">
+      <c r="H313" s="4" t="n"/>
+    </row>
+    <row r="314" ht="45" customHeight="1" s="12">
       <c r="A314" s="4" t="inlineStr">
         <is>
           <t>B9</t>
@@ -14008,9 +14211,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: super excited jumping pose, both arms raised high in celebration, empty hands, not holding anything (no gift box, no props), eyes closed happily (^ ^), wide open smile, tiny hearts and sparkles around the head. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H314" s="4" t="inlineStr"/>
-    </row>
-    <row r="315">
+      <c r="H314" s="4" t="n"/>
+    </row>
+    <row r="315" ht="45" customHeight="1" s="12">
       <c r="A315" s="4" t="inlineStr">
         <is>
           <t>B9</t>
@@ -14044,9 +14247,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: making a finger heart toward the viewer with one hand near the cheek, other arm relaxed, not holding anything else (no gift box, no props), winking, cute blush, small smile. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H315" s="4" t="inlineStr"/>
-    </row>
-    <row r="316">
+      <c r="H315" s="4" t="n"/>
+    </row>
+    <row r="316" ht="60" customHeight="1" s="12">
       <c r="A316" s="4" t="inlineStr">
         <is>
           <t>B9</t>
@@ -14080,9 +14283,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance move — body leaning to the LEFT, left arm raised up with index finger pointing to the sky, right hand on hip, right knee slightly bent, empty hands, not holding anything (no gift box, no props), cheerful open smile, small music notes around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H316" s="4" t="inlineStr"/>
-    </row>
-    <row r="317">
+      <c r="H316" s="4" t="n"/>
+    </row>
+    <row r="317" ht="60" customHeight="1" s="12">
       <c r="A317" s="4" t="inlineStr">
         <is>
           <t>B9</t>
@@ -14116,9 +14319,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance move — body leaning to the RIGHT, right arm raised up with index finger pointing to the sky, left hand on hip, left knee slightly bent, empty hands, not holding anything (no gift box, no props), cheerful open smile, small music notes around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H317" s="4" t="inlineStr"/>
-    </row>
-    <row r="318">
+      <c r="H317" s="4" t="n"/>
+    </row>
+    <row r="318" ht="45" customHeight="1" s="12">
       <c r="A318" s="4" t="inlineStr">
         <is>
           <t>B9</t>
@@ -14152,9 +14355,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance finishing pose — both hands making peace signs (V) next to the face, one foot kicked up behind, empty hands, not holding anything (no gift box, no props), winking with a big smile, sparkles around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H318" s="4" t="inlineStr"/>
-    </row>
-    <row r="319">
+      <c r="H318" s="4" t="n"/>
+    </row>
+    <row r="319" ht="45" customHeight="1" s="12">
       <c r="A319" s="4" t="inlineStr">
         <is>
           <t>B9</t>
@@ -14188,9 +14391,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: walking toward the viewer, front view, LEFT foot stepping forward, right arm swinging forward and left arm back, empty hands, not holding anything (no gift box, no props), happy smile, slight bounce. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H319" s="4" t="inlineStr"/>
-    </row>
-    <row r="320">
+      <c r="H319" s="4" t="n"/>
+    </row>
+    <row r="320" ht="45" customHeight="1" s="12">
       <c r="A320" s="4" t="inlineStr">
         <is>
           <t>B9</t>
@@ -14224,9 +14427,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: walking toward the viewer, front view, RIGHT foot stepping forward, left arm swinging forward and right arm back, empty hands, not holding anything (no gift box, no props), happy smile, slight bounce. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H320" s="4" t="inlineStr"/>
-    </row>
-    <row r="321">
+      <c r="H320" s="4" t="n"/>
+    </row>
+    <row r="321" ht="45" customHeight="1" s="12">
       <c r="A321" s="4" t="inlineStr">
         <is>
           <t>B9</t>
@@ -14260,9 +14463,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: close to the viewer, front view, one hand touching the lips about to blow a kiss, eyes gently closed, cute blush, other arm relaxed, not holding anything else (no gift box, no props). Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H321" s="4" t="inlineStr"/>
-    </row>
-    <row r="322">
+      <c r="H321" s="4" t="n"/>
+    </row>
+    <row r="322" ht="60" customHeight="1" s="12">
       <c r="A322" s="4" t="inlineStr">
         <is>
           <t>B9</t>
@@ -14296,9 +14499,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: blowing a kiss toward the viewer, arm stretched forward with open palm from the lips, lips puckered, winking, cute blush, a small pink heart floating out from the hand, not holding anything else (no gift box, no props). Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H322" s="4" t="inlineStr"/>
-    </row>
-    <row r="323">
+      <c r="H322" s="4" t="n"/>
+    </row>
+    <row r="323" ht="45" customHeight="1" s="12">
       <c r="A323" s="4" t="inlineStr">
         <is>
           <t>B9</t>
@@ -14332,9 +14535,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: back view, walking away from the viewer, LEFT foot stepping forward, arms swinging naturally, empty hands, not holding anything (no gift box, no props), showing the back of the outfit and hair. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H323" s="4" t="inlineStr"/>
-    </row>
-    <row r="324">
+      <c r="H323" s="4" t="n"/>
+    </row>
+    <row r="324" ht="45" customHeight="1" s="12">
       <c r="A324" s="4" t="inlineStr">
         <is>
           <t>B9</t>
@@ -14368,9 +14571,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: back view, walking away from the viewer, RIGHT foot stepping forward, arms swinging naturally, empty hands, not holding anything (no gift box, no props), showing the back of the outfit and hair. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H324" s="4" t="inlineStr"/>
-    </row>
-    <row r="325">
+      <c r="H324" s="4" t="n"/>
+    </row>
+    <row r="325" ht="75" customHeight="1" s="12">
       <c r="A325" s="5" t="inlineStr">
         <is>
           <t>B10</t>
@@ -14410,7 +14613,7 @@
         </is>
       </c>
     </row>
-    <row r="326">
+    <row r="326" ht="45" customHeight="1" s="12">
       <c r="A326" s="5" t="inlineStr">
         <is>
           <t>B10</t>
@@ -14450,7 +14653,7 @@
         </is>
       </c>
     </row>
-    <row r="327">
+    <row r="327" ht="45" customHeight="1" s="12">
       <c r="A327" s="5" t="inlineStr">
         <is>
           <t>B10</t>
@@ -14490,7 +14693,7 @@
         </is>
       </c>
     </row>
-    <row r="328">
+    <row r="328" ht="60" customHeight="1" s="12">
       <c r="A328" s="5" t="inlineStr">
         <is>
           <t>B10</t>
@@ -14530,7 +14733,7 @@
         </is>
       </c>
     </row>
-    <row r="329">
+    <row r="329" ht="60" customHeight="1" s="12">
       <c r="A329" s="5" t="inlineStr">
         <is>
           <t>B10</t>
@@ -14570,7 +14773,7 @@
         </is>
       </c>
     </row>
-    <row r="330">
+    <row r="330" ht="60" customHeight="1" s="12">
       <c r="A330" s="5" t="inlineStr">
         <is>
           <t>B10</t>
@@ -14610,7 +14813,7 @@
         </is>
       </c>
     </row>
-    <row r="331">
+    <row r="331" ht="45" customHeight="1" s="12">
       <c r="A331" s="5" t="inlineStr">
         <is>
           <t>B10</t>
@@ -14650,7 +14853,7 @@
         </is>
       </c>
     </row>
-    <row r="332">
+    <row r="332" ht="45" customHeight="1" s="12">
       <c r="A332" s="5" t="inlineStr">
         <is>
           <t>B10</t>
@@ -14690,7 +14893,7 @@
         </is>
       </c>
     </row>
-    <row r="333">
+    <row r="333" ht="60" customHeight="1" s="12">
       <c r="A333" s="5" t="inlineStr">
         <is>
           <t>B10</t>
@@ -14730,7 +14933,7 @@
         </is>
       </c>
     </row>
-    <row r="334">
+    <row r="334" ht="60" customHeight="1" s="12">
       <c r="A334" s="5" t="inlineStr">
         <is>
           <t>B10</t>
@@ -14770,7 +14973,7 @@
         </is>
       </c>
     </row>
-    <row r="335">
+    <row r="335" ht="45" customHeight="1" s="12">
       <c r="A335" s="5" t="inlineStr">
         <is>
           <t>B10</t>
@@ -14810,7 +15013,7 @@
         </is>
       </c>
     </row>
-    <row r="336">
+    <row r="336" ht="45" customHeight="1" s="12">
       <c r="A336" s="5" t="inlineStr">
         <is>
           <t>B10</t>
@@ -14850,7 +15053,7 @@
         </is>
       </c>
     </row>
-    <row r="337">
+    <row r="337" ht="45" customHeight="1" s="12">
       <c r="A337" s="5" t="inlineStr">
         <is>
           <t>B10</t>
@@ -14890,7 +15093,7 @@
         </is>
       </c>
     </row>
-    <row r="338">
+    <row r="338" ht="45" customHeight="1" s="12">
       <c r="A338" s="5" t="inlineStr">
         <is>
           <t>B10</t>
@@ -14930,7 +15133,7 @@
         </is>
       </c>
     </row>
-    <row r="339">
+    <row r="339" ht="60" customHeight="1" s="12">
       <c r="A339" s="5" t="inlineStr">
         <is>
           <t>B10</t>
@@ -14970,7 +15173,7 @@
         </is>
       </c>
     </row>
-    <row r="340">
+    <row r="340" ht="45" customHeight="1" s="12">
       <c r="A340" s="5" t="inlineStr">
         <is>
           <t>B10</t>
@@ -15010,7 +15213,7 @@
         </is>
       </c>
     </row>
-    <row r="341">
+    <row r="341" ht="45" customHeight="1" s="12">
       <c r="A341" s="5" t="inlineStr">
         <is>
           <t>B10</t>
@@ -15050,7 +15253,7 @@
         </is>
       </c>
     </row>
-    <row r="342">
+    <row r="342" ht="75" customHeight="1" s="12">
       <c r="A342" s="4" t="inlineStr">
         <is>
           <t>B11</t>
@@ -15084,9 +15287,9 @@
           <t>Cute chibi mascot character for a TikTok live streamer, boy with white fluffy hair, pastel blue bunny-ear hoodie, cute carrot pin. Full body, front view, standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Centered, 2.5 heads tall, big sparkly eyes open, soft blush cheeks, gentle smile with mouth closed. Soft 3D pastel style like a vinyl toy, smooth shading, clean outline, pink-lavender-mint palette, kawaii. Transparent background, no shadow on ground, no text, single character only, 1024x1024.</t>
         </is>
       </c>
-      <c r="H342" s="4" t="inlineStr"/>
-    </row>
-    <row r="343">
+      <c r="H342" s="4" t="n"/>
+    </row>
+    <row r="343" ht="45" customHeight="1" s="12">
       <c r="A343" s="4" t="inlineStr">
         <is>
           <t>B11</t>
@@ -15120,9 +15323,9 @@
           <t>Same character, same outfit, exact same pose, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: eyes gently closed as if blinking. Gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H343" s="4" t="inlineStr"/>
-    </row>
-    <row r="344">
+      <c r="H343" s="4" t="n"/>
+    </row>
+    <row r="344" ht="45" customHeight="1" s="12">
       <c r="A344" s="4" t="inlineStr">
         <is>
           <t>B11</t>
@@ -15156,9 +15359,9 @@
           <t>Same character, same outfit, exact same pose, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: mouth open happily as if talking "ah". Eyes open. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H344" s="4" t="inlineStr"/>
-    </row>
-    <row r="345">
+      <c r="H344" s="4" t="n"/>
+    </row>
+    <row r="345" ht="60" customHeight="1" s="12">
       <c r="A345" s="4" t="inlineStr">
         <is>
           <t>B11</t>
@@ -15192,9 +15395,9 @@
           <t>Same character, same outfit, exact same pose, body, face, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: hair and hair accessories gently swaying to the LEFT as if blown by a soft breeze (only hair tips, strands and ribbons shift slightly left). Eyes open, gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H345" s="4" t="inlineStr"/>
-    </row>
-    <row r="346">
+      <c r="H345" s="4" t="n"/>
+    </row>
+    <row r="346" ht="60" customHeight="1" s="12">
       <c r="A346" s="4" t="inlineStr">
         <is>
           <t>B11</t>
@@ -15228,9 +15431,9 @@
           <t>Same character, same outfit, exact same pose, body, face, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: hair and hair accessories gently swaying to the RIGHT as if blown by a soft breeze (only hair tips, strands and ribbons shift slightly right). Eyes open, gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H346" s="4" t="inlineStr"/>
-    </row>
-    <row r="347">
+      <c r="H346" s="4" t="n"/>
+    </row>
+    <row r="347" ht="60" customHeight="1" s="12">
       <c r="A347" s="4" t="inlineStr">
         <is>
           <t>B11</t>
@@ -15264,9 +15467,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: happily ready to catch a gift, both hands cupped together in front of the chest with palms facing up, empty hands, not holding anything (no gift box, no props), clear empty space above the palms, eyes sparkling looking at the hands, big happy smile with mouth open, slight lean forward. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H347" s="4" t="inlineStr"/>
-    </row>
-    <row r="348">
+      <c r="H347" s="4" t="n"/>
+    </row>
+    <row r="348" ht="45" customHeight="1" s="12">
       <c r="A348" s="4" t="inlineStr">
         <is>
           <t>B11</t>
@@ -15300,9 +15503,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: super excited jumping pose, both arms raised high in celebration, empty hands, not holding anything (no gift box, no props), eyes closed happily (^ ^), wide open smile, tiny hearts and sparkles around the head. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H348" s="4" t="inlineStr"/>
-    </row>
-    <row r="349">
+      <c r="H348" s="4" t="n"/>
+    </row>
+    <row r="349" ht="45" customHeight="1" s="12">
       <c r="A349" s="4" t="inlineStr">
         <is>
           <t>B11</t>
@@ -15336,9 +15539,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: making a finger heart toward the viewer with one hand near the cheek, other arm relaxed, not holding anything else (no gift box, no props), winking, cute blush, small smile. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H349" s="4" t="inlineStr"/>
-    </row>
-    <row r="350">
+      <c r="H349" s="4" t="n"/>
+    </row>
+    <row r="350" ht="60" customHeight="1" s="12">
       <c r="A350" s="4" t="inlineStr">
         <is>
           <t>B11</t>
@@ -15372,9 +15575,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance move — body leaning to the LEFT, left arm raised up with index finger pointing to the sky, right hand on hip, right knee slightly bent, empty hands, not holding anything (no gift box, no props), cheerful open smile, small music notes around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H350" s="4" t="inlineStr"/>
-    </row>
-    <row r="351">
+      <c r="H350" s="4" t="n"/>
+    </row>
+    <row r="351" ht="60" customHeight="1" s="12">
       <c r="A351" s="4" t="inlineStr">
         <is>
           <t>B11</t>
@@ -15408,9 +15611,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance move — body leaning to the RIGHT, right arm raised up with index finger pointing to the sky, left hand on hip, left knee slightly bent, empty hands, not holding anything (no gift box, no props), cheerful open smile, small music notes around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H351" s="4" t="inlineStr"/>
-    </row>
-    <row r="352">
+      <c r="H351" s="4" t="n"/>
+    </row>
+    <row r="352" ht="45" customHeight="1" s="12">
       <c r="A352" s="4" t="inlineStr">
         <is>
           <t>B11</t>
@@ -15444,9 +15647,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance finishing pose — both hands making peace signs (V) next to the face, one foot kicked up behind, empty hands, not holding anything (no gift box, no props), winking with a big smile, sparkles around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H352" s="4" t="inlineStr"/>
-    </row>
-    <row r="353">
+      <c r="H352" s="4" t="n"/>
+    </row>
+    <row r="353" ht="45" customHeight="1" s="12">
       <c r="A353" s="4" t="inlineStr">
         <is>
           <t>B11</t>
@@ -15480,9 +15683,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: walking toward the viewer, front view, LEFT foot stepping forward, right arm swinging forward and left arm back, empty hands, not holding anything (no gift box, no props), happy smile, slight bounce. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H353" s="4" t="inlineStr"/>
-    </row>
-    <row r="354">
+      <c r="H353" s="4" t="n"/>
+    </row>
+    <row r="354" ht="45" customHeight="1" s="12">
       <c r="A354" s="4" t="inlineStr">
         <is>
           <t>B11</t>
@@ -15516,9 +15719,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: walking toward the viewer, front view, RIGHT foot stepping forward, left arm swinging forward and right arm back, empty hands, not holding anything (no gift box, no props), happy smile, slight bounce. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H354" s="4" t="inlineStr"/>
-    </row>
-    <row r="355">
+      <c r="H354" s="4" t="n"/>
+    </row>
+    <row r="355" ht="45" customHeight="1" s="12">
       <c r="A355" s="4" t="inlineStr">
         <is>
           <t>B11</t>
@@ -15552,9 +15755,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: close to the viewer, front view, one hand touching the lips about to blow a kiss, eyes gently closed, cute blush, other arm relaxed, not holding anything else (no gift box, no props). Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H355" s="4" t="inlineStr"/>
-    </row>
-    <row r="356">
+      <c r="H355" s="4" t="n"/>
+    </row>
+    <row r="356" ht="60" customHeight="1" s="12">
       <c r="A356" s="4" t="inlineStr">
         <is>
           <t>B11</t>
@@ -15588,9 +15791,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: blowing a kiss toward the viewer, arm stretched forward with open palm from the lips, lips puckered, winking, cute blush, a small pink heart floating out from the hand, not holding anything else (no gift box, no props). Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H356" s="4" t="inlineStr"/>
-    </row>
-    <row r="357">
+      <c r="H356" s="4" t="n"/>
+    </row>
+    <row r="357" ht="45" customHeight="1" s="12">
       <c r="A357" s="4" t="inlineStr">
         <is>
           <t>B11</t>
@@ -15624,9 +15827,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: back view, walking away from the viewer, LEFT foot stepping forward, arms swinging naturally, empty hands, not holding anything (no gift box, no props), showing the back of the outfit and hair. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H357" s="4" t="inlineStr"/>
-    </row>
-    <row r="358">
+      <c r="H357" s="4" t="n"/>
+    </row>
+    <row r="358" ht="45" customHeight="1" s="12">
       <c r="A358" s="4" t="inlineStr">
         <is>
           <t>B11</t>
@@ -15660,9 +15863,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: back view, walking away from the viewer, RIGHT foot stepping forward, arms swinging naturally, empty hands, not holding anything (no gift box, no props), showing the back of the outfit and hair. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H358" s="4" t="inlineStr"/>
-    </row>
-    <row r="359">
+      <c r="H358" s="4" t="n"/>
+    </row>
+    <row r="359" ht="75" customHeight="1" s="12">
       <c r="A359" s="4" t="inlineStr">
         <is>
           <t>B12</t>
@@ -15696,9 +15899,9 @@
           <t>Cute chibi mascot character for a TikTok live streamer, boy with black hair and black cat ears, oversized lavender sweater with moon print. Full body, front view, standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Centered, 2.5 heads tall, big sparkly eyes open, soft blush cheeks, gentle smile with mouth closed. Soft 3D pastel style like a vinyl toy, smooth shading, clean outline, pink-lavender-mint palette, kawaii. Transparent background, no shadow on ground, no text, single character only, 1024x1024.</t>
         </is>
       </c>
-      <c r="H359" s="4" t="inlineStr"/>
-    </row>
-    <row r="360">
+      <c r="H359" s="4" t="n"/>
+    </row>
+    <row r="360" ht="45" customHeight="1" s="12">
       <c r="A360" s="4" t="inlineStr">
         <is>
           <t>B12</t>
@@ -15732,9 +15935,9 @@
           <t>Same character, same outfit, exact same pose, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: eyes gently closed as if blinking. Gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H360" s="4" t="inlineStr"/>
-    </row>
-    <row r="361">
+      <c r="H360" s="4" t="n"/>
+    </row>
+    <row r="361" ht="45" customHeight="1" s="12">
       <c r="A361" s="4" t="inlineStr">
         <is>
           <t>B12</t>
@@ -15768,9 +15971,9 @@
           <t>Same character, same outfit, exact same pose, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: mouth open happily as if talking "ah". Eyes open. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H361" s="4" t="inlineStr"/>
-    </row>
-    <row r="362">
+      <c r="H361" s="4" t="n"/>
+    </row>
+    <row r="362" ht="60" customHeight="1" s="12">
       <c r="A362" s="4" t="inlineStr">
         <is>
           <t>B12</t>
@@ -15804,9 +16007,9 @@
           <t>Same character, same outfit, exact same pose, body, face, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: hair and hair accessories gently swaying to the LEFT as if blown by a soft breeze (only hair tips, strands and ribbons shift slightly left). Eyes open, gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H362" s="4" t="inlineStr"/>
-    </row>
-    <row r="363">
+      <c r="H362" s="4" t="n"/>
+    </row>
+    <row r="363" ht="60" customHeight="1" s="12">
       <c r="A363" s="4" t="inlineStr">
         <is>
           <t>B12</t>
@@ -15840,9 +16043,9 @@
           <t>Same character, same outfit, exact same pose, body, face, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: hair and hair accessories gently swaying to the RIGHT as if blown by a soft breeze (only hair tips, strands and ribbons shift slightly right). Eyes open, gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H363" s="4" t="inlineStr"/>
-    </row>
-    <row r="364">
+      <c r="H363" s="4" t="n"/>
+    </row>
+    <row r="364" ht="60" customHeight="1" s="12">
       <c r="A364" s="4" t="inlineStr">
         <is>
           <t>B12</t>
@@ -15876,9 +16079,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: happily ready to catch a gift, both hands cupped together in front of the chest with palms facing up, empty hands, not holding anything (no gift box, no props), clear empty space above the palms, eyes sparkling looking at the hands, big happy smile with mouth open, slight lean forward. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H364" s="4" t="inlineStr"/>
-    </row>
-    <row r="365">
+      <c r="H364" s="4" t="n"/>
+    </row>
+    <row r="365" ht="45" customHeight="1" s="12">
       <c r="A365" s="4" t="inlineStr">
         <is>
           <t>B12</t>
@@ -15912,9 +16115,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: super excited jumping pose, both arms raised high in celebration, empty hands, not holding anything (no gift box, no props), eyes closed happily (^ ^), wide open smile, tiny hearts and sparkles around the head. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H365" s="4" t="inlineStr"/>
-    </row>
-    <row r="366">
+      <c r="H365" s="4" t="n"/>
+    </row>
+    <row r="366" ht="45" customHeight="1" s="12">
       <c r="A366" s="4" t="inlineStr">
         <is>
           <t>B12</t>
@@ -15948,9 +16151,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: making a finger heart toward the viewer with one hand near the cheek, other arm relaxed, not holding anything else (no gift box, no props), winking, cute blush, small smile. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H366" s="4" t="inlineStr"/>
-    </row>
-    <row r="367">
+      <c r="H366" s="4" t="n"/>
+    </row>
+    <row r="367" ht="60" customHeight="1" s="12">
       <c r="A367" s="4" t="inlineStr">
         <is>
           <t>B12</t>
@@ -15984,9 +16187,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance move — body leaning to the LEFT, left arm raised up with index finger pointing to the sky, right hand on hip, right knee slightly bent, empty hands, not holding anything (no gift box, no props), cheerful open smile, small music notes around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H367" s="4" t="inlineStr"/>
-    </row>
-    <row r="368">
+      <c r="H367" s="4" t="n"/>
+    </row>
+    <row r="368" ht="60" customHeight="1" s="12">
       <c r="A368" s="4" t="inlineStr">
         <is>
           <t>B12</t>
@@ -16020,9 +16223,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance move — body leaning to the RIGHT, right arm raised up with index finger pointing to the sky, left hand on hip, left knee slightly bent, empty hands, not holding anything (no gift box, no props), cheerful open smile, small music notes around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H368" s="4" t="inlineStr"/>
-    </row>
-    <row r="369">
+      <c r="H368" s="4" t="n"/>
+    </row>
+    <row r="369" ht="45" customHeight="1" s="12">
       <c r="A369" s="4" t="inlineStr">
         <is>
           <t>B12</t>
@@ -16056,9 +16259,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance finishing pose — both hands making peace signs (V) next to the face, one foot kicked up behind, empty hands, not holding anything (no gift box, no props), winking with a big smile, sparkles around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H369" s="4" t="inlineStr"/>
-    </row>
-    <row r="370">
+      <c r="H369" s="4" t="n"/>
+    </row>
+    <row r="370" ht="45" customHeight="1" s="12">
       <c r="A370" s="4" t="inlineStr">
         <is>
           <t>B12</t>
@@ -16092,9 +16295,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: walking toward the viewer, front view, LEFT foot stepping forward, right arm swinging forward and left arm back, empty hands, not holding anything (no gift box, no props), happy smile, slight bounce. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H370" s="4" t="inlineStr"/>
-    </row>
-    <row r="371">
+      <c r="H370" s="4" t="n"/>
+    </row>
+    <row r="371" ht="45" customHeight="1" s="12">
       <c r="A371" s="4" t="inlineStr">
         <is>
           <t>B12</t>
@@ -16128,9 +16331,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: walking toward the viewer, front view, RIGHT foot stepping forward, left arm swinging forward and right arm back, empty hands, not holding anything (no gift box, no props), happy smile, slight bounce. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H371" s="4" t="inlineStr"/>
-    </row>
-    <row r="372">
+      <c r="H371" s="4" t="n"/>
+    </row>
+    <row r="372" ht="45" customHeight="1" s="12">
       <c r="A372" s="4" t="inlineStr">
         <is>
           <t>B12</t>
@@ -16164,9 +16367,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: close to the viewer, front view, one hand touching the lips about to blow a kiss, eyes gently closed, cute blush, other arm relaxed, not holding anything else (no gift box, no props). Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H372" s="4" t="inlineStr"/>
-    </row>
-    <row r="373">
+      <c r="H372" s="4" t="n"/>
+    </row>
+    <row r="373" ht="60" customHeight="1" s="12">
       <c r="A373" s="4" t="inlineStr">
         <is>
           <t>B12</t>
@@ -16200,9 +16403,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: blowing a kiss toward the viewer, arm stretched forward with open palm from the lips, lips puckered, winking, cute blush, a small pink heart floating out from the hand, not holding anything else (no gift box, no props). Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H373" s="4" t="inlineStr"/>
-    </row>
-    <row r="374">
+      <c r="H373" s="4" t="n"/>
+    </row>
+    <row r="374" ht="45" customHeight="1" s="12">
       <c r="A374" s="4" t="inlineStr">
         <is>
           <t>B12</t>
@@ -16236,9 +16439,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: back view, walking away from the viewer, LEFT foot stepping forward, arms swinging naturally, empty hands, not holding anything (no gift box, no props), showing the back of the outfit and hair. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H374" s="4" t="inlineStr"/>
-    </row>
-    <row r="375">
+      <c r="H374" s="4" t="n"/>
+    </row>
+    <row r="375" ht="45" customHeight="1" s="12">
       <c r="A375" s="4" t="inlineStr">
         <is>
           <t>B12</t>
@@ -16272,9 +16475,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: back view, walking away from the viewer, RIGHT foot stepping forward, arms swinging naturally, empty hands, not holding anything (no gift box, no props), showing the back of the outfit and hair. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H375" s="4" t="inlineStr"/>
-    </row>
-    <row r="376">
+      <c r="H375" s="4" t="n"/>
+    </row>
+    <row r="376" ht="75" customHeight="1" s="12">
       <c r="A376" s="4" t="inlineStr">
         <is>
           <t>B13</t>
@@ -16308,9 +16511,9 @@
           <t>Cute chibi mascot character for a TikTok live streamer, boy with neat brown hair and round glasses, pastel school blazer with bow tie. Full body, front view, standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Centered, 2.5 heads tall, big sparkly eyes open, soft blush cheeks, gentle smile with mouth closed. Soft 3D pastel style like a vinyl toy, smooth shading, clean outline, pink-lavender-mint palette, kawaii. Transparent background, no shadow on ground, no text, single character only, 1024x1024.</t>
         </is>
       </c>
-      <c r="H376" s="4" t="inlineStr"/>
-    </row>
-    <row r="377">
+      <c r="H376" s="4" t="n"/>
+    </row>
+    <row r="377" ht="45" customHeight="1" s="12">
       <c r="A377" s="4" t="inlineStr">
         <is>
           <t>B13</t>
@@ -16344,9 +16547,9 @@
           <t>Same character, same outfit, exact same pose, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: eyes gently closed as if blinking. Gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H377" s="4" t="inlineStr"/>
-    </row>
-    <row r="378">
+      <c r="H377" s="4" t="n"/>
+    </row>
+    <row r="378" ht="45" customHeight="1" s="12">
       <c r="A378" s="4" t="inlineStr">
         <is>
           <t>B13</t>
@@ -16380,9 +16583,9 @@
           <t>Same character, same outfit, exact same pose, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: mouth open happily as if talking "ah". Eyes open. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H378" s="4" t="inlineStr"/>
-    </row>
-    <row r="379">
+      <c r="H378" s="4" t="n"/>
+    </row>
+    <row r="379" ht="60" customHeight="1" s="12">
       <c r="A379" s="4" t="inlineStr">
         <is>
           <t>B13</t>
@@ -16416,9 +16619,9 @@
           <t>Same character, same outfit, exact same pose, body, face, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: hair and hair accessories gently swaying to the LEFT as if blown by a soft breeze (only hair tips, strands and ribbons shift slightly left). Eyes open, gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H379" s="4" t="inlineStr"/>
-    </row>
-    <row r="380">
+      <c r="H379" s="4" t="n"/>
+    </row>
+    <row r="380" ht="60" customHeight="1" s="12">
       <c r="A380" s="4" t="inlineStr">
         <is>
           <t>B13</t>
@@ -16452,9 +16655,9 @@
           <t>Same character, same outfit, exact same pose, body, face, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: hair and hair accessories gently swaying to the RIGHT as if blown by a soft breeze (only hair tips, strands and ribbons shift slightly right). Eyes open, gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H380" s="4" t="inlineStr"/>
-    </row>
-    <row r="381">
+      <c r="H380" s="4" t="n"/>
+    </row>
+    <row r="381" ht="60" customHeight="1" s="12">
       <c r="A381" s="4" t="inlineStr">
         <is>
           <t>B13</t>
@@ -16488,9 +16691,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: happily ready to catch a gift, both hands cupped together in front of the chest with palms facing up, empty hands, not holding anything (no gift box, no props), clear empty space above the palms, eyes sparkling looking at the hands, big happy smile with mouth open, slight lean forward. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H381" s="4" t="inlineStr"/>
-    </row>
-    <row r="382">
+      <c r="H381" s="4" t="n"/>
+    </row>
+    <row r="382" ht="45" customHeight="1" s="12">
       <c r="A382" s="4" t="inlineStr">
         <is>
           <t>B13</t>
@@ -16524,9 +16727,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: super excited jumping pose, both arms raised high in celebration, empty hands, not holding anything (no gift box, no props), eyes closed happily (^ ^), wide open smile, tiny hearts and sparkles around the head. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H382" s="4" t="inlineStr"/>
-    </row>
-    <row r="383">
+      <c r="H382" s="4" t="n"/>
+    </row>
+    <row r="383" ht="45" customHeight="1" s="12">
       <c r="A383" s="4" t="inlineStr">
         <is>
           <t>B13</t>
@@ -16560,9 +16763,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: making a finger heart toward the viewer with one hand near the cheek, other arm relaxed, not holding anything else (no gift box, no props), winking, cute blush, small smile. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H383" s="4" t="inlineStr"/>
-    </row>
-    <row r="384">
+      <c r="H383" s="4" t="n"/>
+    </row>
+    <row r="384" ht="60" customHeight="1" s="12">
       <c r="A384" s="4" t="inlineStr">
         <is>
           <t>B13</t>
@@ -16596,9 +16799,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance move — body leaning to the LEFT, left arm raised up with index finger pointing to the sky, right hand on hip, right knee slightly bent, empty hands, not holding anything (no gift box, no props), cheerful open smile, small music notes around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H384" s="4" t="inlineStr"/>
-    </row>
-    <row r="385">
+      <c r="H384" s="4" t="n"/>
+    </row>
+    <row r="385" ht="60" customHeight="1" s="12">
       <c r="A385" s="4" t="inlineStr">
         <is>
           <t>B13</t>
@@ -16632,9 +16835,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance move — body leaning to the RIGHT, right arm raised up with index finger pointing to the sky, left hand on hip, left knee slightly bent, empty hands, not holding anything (no gift box, no props), cheerful open smile, small music notes around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H385" s="4" t="inlineStr"/>
-    </row>
-    <row r="386">
+      <c r="H385" s="4" t="n"/>
+    </row>
+    <row r="386" ht="45" customHeight="1" s="12">
       <c r="A386" s="4" t="inlineStr">
         <is>
           <t>B13</t>
@@ -16668,9 +16871,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance finishing pose — both hands making peace signs (V) next to the face, one foot kicked up behind, empty hands, not holding anything (no gift box, no props), winking with a big smile, sparkles around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H386" s="4" t="inlineStr"/>
-    </row>
-    <row r="387">
+      <c r="H386" s="4" t="n"/>
+    </row>
+    <row r="387" ht="45" customHeight="1" s="12">
       <c r="A387" s="4" t="inlineStr">
         <is>
           <t>B13</t>
@@ -16704,9 +16907,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: walking toward the viewer, front view, LEFT foot stepping forward, right arm swinging forward and left arm back, empty hands, not holding anything (no gift box, no props), happy smile, slight bounce. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H387" s="4" t="inlineStr"/>
-    </row>
-    <row r="388">
+      <c r="H387" s="4" t="n"/>
+    </row>
+    <row r="388" ht="45" customHeight="1" s="12">
       <c r="A388" s="4" t="inlineStr">
         <is>
           <t>B13</t>
@@ -16740,9 +16943,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: walking toward the viewer, front view, RIGHT foot stepping forward, left arm swinging forward and right arm back, empty hands, not holding anything (no gift box, no props), happy smile, slight bounce. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H388" s="4" t="inlineStr"/>
-    </row>
-    <row r="389">
+      <c r="H388" s="4" t="n"/>
+    </row>
+    <row r="389" ht="45" customHeight="1" s="12">
       <c r="A389" s="4" t="inlineStr">
         <is>
           <t>B13</t>
@@ -16776,9 +16979,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: close to the viewer, front view, one hand touching the lips about to blow a kiss, eyes gently closed, cute blush, other arm relaxed, not holding anything else (no gift box, no props). Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H389" s="4" t="inlineStr"/>
-    </row>
-    <row r="390">
+      <c r="H389" s="4" t="n"/>
+    </row>
+    <row r="390" ht="60" customHeight="1" s="12">
       <c r="A390" s="4" t="inlineStr">
         <is>
           <t>B13</t>
@@ -16812,9 +17015,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: blowing a kiss toward the viewer, arm stretched forward with open palm from the lips, lips puckered, winking, cute blush, a small pink heart floating out from the hand, not holding anything else (no gift box, no props). Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H390" s="4" t="inlineStr"/>
-    </row>
-    <row r="391">
+      <c r="H390" s="4" t="n"/>
+    </row>
+    <row r="391" ht="45" customHeight="1" s="12">
       <c r="A391" s="4" t="inlineStr">
         <is>
           <t>B13</t>
@@ -16848,9 +17051,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: back view, walking away from the viewer, LEFT foot stepping forward, arms swinging naturally, empty hands, not holding anything (no gift box, no props), showing the back of the outfit and hair. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H391" s="4" t="inlineStr"/>
-    </row>
-    <row r="392">
+      <c r="H391" s="4" t="n"/>
+    </row>
+    <row r="392" ht="45" customHeight="1" s="12">
       <c r="A392" s="4" t="inlineStr">
         <is>
           <t>B13</t>
@@ -16884,9 +17087,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: back view, walking away from the viewer, RIGHT foot stepping forward, arms swinging naturally, empty hands, not holding anything (no gift box, no props), showing the back of the outfit and hair. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H392" s="4" t="inlineStr"/>
-    </row>
-    <row r="393">
+      <c r="H392" s="4" t="n"/>
+    </row>
+    <row r="393" ht="75" customHeight="1" s="12">
       <c r="A393" s="4" t="inlineStr">
         <is>
           <t>B14</t>
@@ -16920,9 +17123,9 @@
           <t>Cute chibi mascot character for a TikTok live streamer, boy with pink-dyed messy hair, pastel street dance outfit, bucket hat and baggy pants. Full body, front view, standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Centered, 2.5 heads tall, big sparkly eyes open, soft blush cheeks, gentle smile with mouth closed. Soft 3D pastel style like a vinyl toy, smooth shading, clean outline, pink-lavender-mint palette, kawaii. Transparent background, no shadow on ground, no text, single character only, 1024x1024.</t>
         </is>
       </c>
-      <c r="H393" s="4" t="inlineStr"/>
-    </row>
-    <row r="394">
+      <c r="H393" s="4" t="n"/>
+    </row>
+    <row r="394" ht="45" customHeight="1" s="12">
       <c r="A394" s="4" t="inlineStr">
         <is>
           <t>B14</t>
@@ -16956,9 +17159,9 @@
           <t>Same character, same outfit, exact same pose, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: eyes gently closed as if blinking. Gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H394" s="4" t="inlineStr"/>
-    </row>
-    <row r="395">
+      <c r="H394" s="4" t="n"/>
+    </row>
+    <row r="395" ht="45" customHeight="1" s="12">
       <c r="A395" s="4" t="inlineStr">
         <is>
           <t>B14</t>
@@ -16992,9 +17195,9 @@
           <t>Same character, same outfit, exact same pose, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: mouth open happily as if talking "ah". Eyes open. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H395" s="4" t="inlineStr"/>
-    </row>
-    <row r="396">
+      <c r="H395" s="4" t="n"/>
+    </row>
+    <row r="396" ht="60" customHeight="1" s="12">
       <c r="A396" s="4" t="inlineStr">
         <is>
           <t>B14</t>
@@ -17028,9 +17231,9 @@
           <t>Same character, same outfit, exact same pose, body, face, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: hair and hair accessories gently swaying to the LEFT as if blown by a soft breeze (only hair tips, strands and ribbons shift slightly left). Eyes open, gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H396" s="4" t="inlineStr"/>
-    </row>
-    <row r="397">
+      <c r="H396" s="4" t="n"/>
+    </row>
+    <row r="397" ht="60" customHeight="1" s="12">
       <c r="A397" s="4" t="inlineStr">
         <is>
           <t>B14</t>
@@ -17064,9 +17267,9 @@
           <t>Same character, same outfit, exact same pose, body, face, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: hair and hair accessories gently swaying to the RIGHT as if blown by a soft breeze (only hair tips, strands and ribbons shift slightly right). Eyes open, gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H397" s="4" t="inlineStr"/>
-    </row>
-    <row r="398">
+      <c r="H397" s="4" t="n"/>
+    </row>
+    <row r="398" ht="60" customHeight="1" s="12">
       <c r="A398" s="4" t="inlineStr">
         <is>
           <t>B14</t>
@@ -17100,9 +17303,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: happily ready to catch a gift, both hands cupped together in front of the chest with palms facing up, empty hands, not holding anything (no gift box, no props), clear empty space above the palms, eyes sparkling looking at the hands, big happy smile with mouth open, slight lean forward. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H398" s="4" t="inlineStr"/>
-    </row>
-    <row r="399">
+      <c r="H398" s="4" t="n"/>
+    </row>
+    <row r="399" ht="45" customHeight="1" s="12">
       <c r="A399" s="4" t="inlineStr">
         <is>
           <t>B14</t>
@@ -17136,9 +17339,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: super excited jumping pose, both arms raised high in celebration, empty hands, not holding anything (no gift box, no props), eyes closed happily (^ ^), wide open smile, tiny hearts and sparkles around the head. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H399" s="4" t="inlineStr"/>
-    </row>
-    <row r="400">
+      <c r="H399" s="4" t="n"/>
+    </row>
+    <row r="400" ht="45" customHeight="1" s="12">
       <c r="A400" s="4" t="inlineStr">
         <is>
           <t>B14</t>
@@ -17172,9 +17375,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: making a finger heart toward the viewer with one hand near the cheek, other arm relaxed, not holding anything else (no gift box, no props), winking, cute blush, small smile. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H400" s="4" t="inlineStr"/>
-    </row>
-    <row r="401">
+      <c r="H400" s="4" t="n"/>
+    </row>
+    <row r="401" ht="60" customHeight="1" s="12">
       <c r="A401" s="4" t="inlineStr">
         <is>
           <t>B14</t>
@@ -17208,9 +17411,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance move — body leaning to the LEFT, left arm raised up with index finger pointing to the sky, right hand on hip, right knee slightly bent, empty hands, not holding anything (no gift box, no props), cheerful open smile, small music notes around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H401" s="4" t="inlineStr"/>
-    </row>
-    <row r="402">
+      <c r="H401" s="4" t="n"/>
+    </row>
+    <row r="402" ht="60" customHeight="1" s="12">
       <c r="A402" s="4" t="inlineStr">
         <is>
           <t>B14</t>
@@ -17244,9 +17447,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance move — body leaning to the RIGHT, right arm raised up with index finger pointing to the sky, left hand on hip, left knee slightly bent, empty hands, not holding anything (no gift box, no props), cheerful open smile, small music notes around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H402" s="4" t="inlineStr"/>
-    </row>
-    <row r="403">
+      <c r="H402" s="4" t="n"/>
+    </row>
+    <row r="403" ht="45" customHeight="1" s="12">
       <c r="A403" s="4" t="inlineStr">
         <is>
           <t>B14</t>
@@ -17280,9 +17483,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance finishing pose — both hands making peace signs (V) next to the face, one foot kicked up behind, empty hands, not holding anything (no gift box, no props), winking with a big smile, sparkles around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H403" s="4" t="inlineStr"/>
-    </row>
-    <row r="404">
+      <c r="H403" s="4" t="n"/>
+    </row>
+    <row r="404" ht="45" customHeight="1" s="12">
       <c r="A404" s="4" t="inlineStr">
         <is>
           <t>B14</t>
@@ -17316,9 +17519,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: walking toward the viewer, front view, LEFT foot stepping forward, right arm swinging forward and left arm back, empty hands, not holding anything (no gift box, no props), happy smile, slight bounce. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H404" s="4" t="inlineStr"/>
-    </row>
-    <row r="405">
+      <c r="H404" s="4" t="n"/>
+    </row>
+    <row r="405" ht="45" customHeight="1" s="12">
       <c r="A405" s="4" t="inlineStr">
         <is>
           <t>B14</t>
@@ -17352,9 +17555,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: walking toward the viewer, front view, RIGHT foot stepping forward, left arm swinging forward and right arm back, empty hands, not holding anything (no gift box, no props), happy smile, slight bounce. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H405" s="4" t="inlineStr"/>
-    </row>
-    <row r="406">
+      <c r="H405" s="4" t="n"/>
+    </row>
+    <row r="406" ht="45" customHeight="1" s="12">
       <c r="A406" s="4" t="inlineStr">
         <is>
           <t>B14</t>
@@ -17388,9 +17591,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: close to the viewer, front view, one hand touching the lips about to blow a kiss, eyes gently closed, cute blush, other arm relaxed, not holding anything else (no gift box, no props). Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H406" s="4" t="inlineStr"/>
-    </row>
-    <row r="407">
+      <c r="H406" s="4" t="n"/>
+    </row>
+    <row r="407" ht="60" customHeight="1" s="12">
       <c r="A407" s="4" t="inlineStr">
         <is>
           <t>B14</t>
@@ -17424,9 +17627,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: blowing a kiss toward the viewer, arm stretched forward with open palm from the lips, lips puckered, winking, cute blush, a small pink heart floating out from the hand, not holding anything else (no gift box, no props). Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H407" s="4" t="inlineStr"/>
-    </row>
-    <row r="408">
+      <c r="H407" s="4" t="n"/>
+    </row>
+    <row r="408" ht="45" customHeight="1" s="12">
       <c r="A408" s="4" t="inlineStr">
         <is>
           <t>B14</t>
@@ -17460,9 +17663,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: back view, walking away from the viewer, LEFT foot stepping forward, arms swinging naturally, empty hands, not holding anything (no gift box, no props), showing the back of the outfit and hair. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H408" s="4" t="inlineStr"/>
-    </row>
-    <row r="409">
+      <c r="H408" s="4" t="n"/>
+    </row>
+    <row r="409" ht="45" customHeight="1" s="12">
       <c r="A409" s="4" t="inlineStr">
         <is>
           <t>B14</t>
@@ -17496,9 +17699,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: back view, walking away from the viewer, RIGHT foot stepping forward, arms swinging naturally, empty hands, not holding anything (no gift box, no props), showing the back of the outfit and hair. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H409" s="4" t="inlineStr"/>
-    </row>
-    <row r="410">
+      <c r="H409" s="4" t="n"/>
+    </row>
+    <row r="410" ht="75" customHeight="1" s="12">
       <c r="A410" s="4" t="inlineStr">
         <is>
           <t>B15</t>
@@ -17532,9 +17735,9 @@
           <t>Cute chibi mascot character for a TikTok live streamer, boy with black-and-white hair, panda-ear hoodie, bamboo-print shorts. Full body, front view, standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Centered, 2.5 heads tall, big sparkly eyes open, soft blush cheeks, gentle smile with mouth closed. Soft 3D pastel style like a vinyl toy, smooth shading, clean outline, pink-lavender-mint palette, kawaii. Transparent background, no shadow on ground, no text, single character only, 1024x1024.</t>
         </is>
       </c>
-      <c r="H410" s="4" t="inlineStr"/>
-    </row>
-    <row r="411">
+      <c r="H410" s="4" t="n"/>
+    </row>
+    <row r="411" ht="45" customHeight="1" s="12">
       <c r="A411" s="4" t="inlineStr">
         <is>
           <t>B15</t>
@@ -17568,9 +17771,9 @@
           <t>Same character, same outfit, exact same pose, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: eyes gently closed as if blinking. Gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H411" s="4" t="inlineStr"/>
-    </row>
-    <row r="412">
+      <c r="H411" s="4" t="n"/>
+    </row>
+    <row r="412" ht="45" customHeight="1" s="12">
       <c r="A412" s="4" t="inlineStr">
         <is>
           <t>B15</t>
@@ -17604,9 +17807,9 @@
           <t>Same character, same outfit, exact same pose, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: mouth open happily as if talking "ah". Eyes open. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H412" s="4" t="inlineStr"/>
-    </row>
-    <row r="413">
+      <c r="H412" s="4" t="n"/>
+    </row>
+    <row r="413" ht="60" customHeight="1" s="12">
       <c r="A413" s="4" t="inlineStr">
         <is>
           <t>B15</t>
@@ -17640,9 +17843,9 @@
           <t>Same character, same outfit, exact same pose, body, face, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: hair and hair accessories gently swaying to the LEFT as if blown by a soft breeze (only hair tips, strands and ribbons shift slightly left). Eyes open, gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H413" s="4" t="inlineStr"/>
-    </row>
-    <row r="414">
+      <c r="H413" s="4" t="n"/>
+    </row>
+    <row r="414" ht="60" customHeight="1" s="12">
       <c r="A414" s="4" t="inlineStr">
         <is>
           <t>B15</t>
@@ -17676,9 +17879,9 @@
           <t>Same character, same outfit, exact same pose, body, face, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: hair and hair accessories gently swaying to the RIGHT as if blown by a soft breeze (only hair tips, strands and ribbons shift slightly right). Eyes open, gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H414" s="4" t="inlineStr"/>
-    </row>
-    <row r="415">
+      <c r="H414" s="4" t="n"/>
+    </row>
+    <row r="415" ht="60" customHeight="1" s="12">
       <c r="A415" s="4" t="inlineStr">
         <is>
           <t>B15</t>
@@ -17712,9 +17915,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: happily ready to catch a gift, both hands cupped together in front of the chest with palms facing up, empty hands, not holding anything (no gift box, no props), clear empty space above the palms, eyes sparkling looking at the hands, big happy smile with mouth open, slight lean forward. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H415" s="4" t="inlineStr"/>
-    </row>
-    <row r="416">
+      <c r="H415" s="4" t="n"/>
+    </row>
+    <row r="416" ht="45" customHeight="1" s="12">
       <c r="A416" s="4" t="inlineStr">
         <is>
           <t>B15</t>
@@ -17748,9 +17951,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: super excited jumping pose, both arms raised high in celebration, empty hands, not holding anything (no gift box, no props), eyes closed happily (^ ^), wide open smile, tiny hearts and sparkles around the head. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H416" s="4" t="inlineStr"/>
-    </row>
-    <row r="417">
+      <c r="H416" s="4" t="n"/>
+    </row>
+    <row r="417" ht="45" customHeight="1" s="12">
       <c r="A417" s="4" t="inlineStr">
         <is>
           <t>B15</t>
@@ -17784,9 +17987,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: making a finger heart toward the viewer with one hand near the cheek, other arm relaxed, not holding anything else (no gift box, no props), winking, cute blush, small smile. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H417" s="4" t="inlineStr"/>
-    </row>
-    <row r="418">
+      <c r="H417" s="4" t="n"/>
+    </row>
+    <row r="418" ht="60" customHeight="1" s="12">
       <c r="A418" s="4" t="inlineStr">
         <is>
           <t>B15</t>
@@ -17820,9 +18023,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance move — body leaning to the LEFT, left arm raised up with index finger pointing to the sky, right hand on hip, right knee slightly bent, empty hands, not holding anything (no gift box, no props), cheerful open smile, small music notes around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H418" s="4" t="inlineStr"/>
-    </row>
-    <row r="419">
+      <c r="H418" s="4" t="n"/>
+    </row>
+    <row r="419" ht="60" customHeight="1" s="12">
       <c r="A419" s="4" t="inlineStr">
         <is>
           <t>B15</t>
@@ -17856,9 +18059,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance move — body leaning to the RIGHT, right arm raised up with index finger pointing to the sky, left hand on hip, left knee slightly bent, empty hands, not holding anything (no gift box, no props), cheerful open smile, small music notes around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H419" s="4" t="inlineStr"/>
-    </row>
-    <row r="420">
+      <c r="H419" s="4" t="n"/>
+    </row>
+    <row r="420" ht="45" customHeight="1" s="12">
       <c r="A420" s="4" t="inlineStr">
         <is>
           <t>B15</t>
@@ -17892,9 +18095,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance finishing pose — both hands making peace signs (V) next to the face, one foot kicked up behind, empty hands, not holding anything (no gift box, no props), winking with a big smile, sparkles around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H420" s="4" t="inlineStr"/>
-    </row>
-    <row r="421">
+      <c r="H420" s="4" t="n"/>
+    </row>
+    <row r="421" ht="45" customHeight="1" s="12">
       <c r="A421" s="4" t="inlineStr">
         <is>
           <t>B15</t>
@@ -17928,9 +18131,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: walking toward the viewer, front view, LEFT foot stepping forward, right arm swinging forward and left arm back, empty hands, not holding anything (no gift box, no props), happy smile, slight bounce. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H421" s="4" t="inlineStr"/>
-    </row>
-    <row r="422">
+      <c r="H421" s="4" t="n"/>
+    </row>
+    <row r="422" ht="45" customHeight="1" s="12">
       <c r="A422" s="4" t="inlineStr">
         <is>
           <t>B15</t>
@@ -17964,9 +18167,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: walking toward the viewer, front view, RIGHT foot stepping forward, left arm swinging forward and right arm back, empty hands, not holding anything (no gift box, no props), happy smile, slight bounce. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H422" s="4" t="inlineStr"/>
-    </row>
-    <row r="423">
+      <c r="H422" s="4" t="n"/>
+    </row>
+    <row r="423" ht="45" customHeight="1" s="12">
       <c r="A423" s="4" t="inlineStr">
         <is>
           <t>B15</t>
@@ -18000,9 +18203,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: close to the viewer, front view, one hand touching the lips about to blow a kiss, eyes gently closed, cute blush, other arm relaxed, not holding anything else (no gift box, no props). Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H423" s="4" t="inlineStr"/>
-    </row>
-    <row r="424">
+      <c r="H423" s="4" t="n"/>
+    </row>
+    <row r="424" ht="60" customHeight="1" s="12">
       <c r="A424" s="4" t="inlineStr">
         <is>
           <t>B15</t>
@@ -18036,9 +18239,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: blowing a kiss toward the viewer, arm stretched forward with open palm from the lips, lips puckered, winking, cute blush, a small pink heart floating out from the hand, not holding anything else (no gift box, no props). Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H424" s="4" t="inlineStr"/>
-    </row>
-    <row r="425">
+      <c r="H424" s="4" t="n"/>
+    </row>
+    <row r="425" ht="45" customHeight="1" s="12">
       <c r="A425" s="4" t="inlineStr">
         <is>
           <t>B15</t>
@@ -18072,9 +18275,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: back view, walking away from the viewer, LEFT foot stepping forward, arms swinging naturally, empty hands, not holding anything (no gift box, no props), showing the back of the outfit and hair. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H425" s="4" t="inlineStr"/>
-    </row>
-    <row r="426">
+      <c r="H425" s="4" t="n"/>
+    </row>
+    <row r="426" ht="45" customHeight="1" s="12">
       <c r="A426" s="4" t="inlineStr">
         <is>
           <t>B15</t>
@@ -18108,9 +18311,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: back view, walking away from the viewer, RIGHT foot stepping forward, arms swinging naturally, empty hands, not holding anything (no gift box, no props), showing the back of the outfit and hair. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H426" s="4" t="inlineStr"/>
-    </row>
-    <row r="427">
+      <c r="H426" s="4" t="n"/>
+    </row>
+    <row r="427" ht="75" customHeight="1" s="12">
       <c r="A427" s="4" t="inlineStr">
         <is>
           <t>B16</t>
@@ -18144,9 +18347,9 @@
           <t>Cute chibi mascot character for a TikTok live streamer, boy with soft caramel hair, barista apron over cream shirt, latte-art badge. Full body, front view, standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Centered, 2.5 heads tall, big sparkly eyes open, soft blush cheeks, gentle smile with mouth closed. Soft 3D pastel style like a vinyl toy, smooth shading, clean outline, pink-lavender-mint palette, kawaii. Transparent background, no shadow on ground, no text, single character only, 1024x1024.</t>
         </is>
       </c>
-      <c r="H427" s="4" t="inlineStr"/>
-    </row>
-    <row r="428">
+      <c r="H427" s="4" t="n"/>
+    </row>
+    <row r="428" ht="45" customHeight="1" s="12">
       <c r="A428" s="4" t="inlineStr">
         <is>
           <t>B16</t>
@@ -18180,9 +18383,9 @@
           <t>Same character, same outfit, exact same pose, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: eyes gently closed as if blinking. Gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H428" s="4" t="inlineStr"/>
-    </row>
-    <row r="429">
+      <c r="H428" s="4" t="n"/>
+    </row>
+    <row r="429" ht="45" customHeight="1" s="12">
       <c r="A429" s="4" t="inlineStr">
         <is>
           <t>B16</t>
@@ -18216,9 +18419,9 @@
           <t>Same character, same outfit, exact same pose, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: mouth open happily as if talking "ah". Eyes open. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H429" s="4" t="inlineStr"/>
-    </row>
-    <row r="430">
+      <c r="H429" s="4" t="n"/>
+    </row>
+    <row r="430" ht="60" customHeight="1" s="12">
       <c r="A430" s="4" t="inlineStr">
         <is>
           <t>B16</t>
@@ -18252,9 +18455,9 @@
           <t>Same character, same outfit, exact same pose, body, face, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: hair and hair accessories gently swaying to the LEFT as if blown by a soft breeze (only hair tips, strands and ribbons shift slightly left). Eyes open, gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H430" s="4" t="inlineStr"/>
-    </row>
-    <row r="431">
+      <c r="H430" s="4" t="n"/>
+    </row>
+    <row r="431" ht="60" customHeight="1" s="12">
       <c r="A431" s="4" t="inlineStr">
         <is>
           <t>B16</t>
@@ -18288,9 +18491,9 @@
           <t>Same character, same outfit, exact same pose, body, face, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: hair and hair accessories gently swaying to the RIGHT as if blown by a soft breeze (only hair tips, strands and ribbons shift slightly right). Eyes open, gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H431" s="4" t="inlineStr"/>
-    </row>
-    <row r="432">
+      <c r="H431" s="4" t="n"/>
+    </row>
+    <row r="432" ht="60" customHeight="1" s="12">
       <c r="A432" s="4" t="inlineStr">
         <is>
           <t>B16</t>
@@ -18324,9 +18527,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: happily ready to catch a gift, both hands cupped together in front of the chest with palms facing up, empty hands, not holding anything (no gift box, no props), clear empty space above the palms, eyes sparkling looking at the hands, big happy smile with mouth open, slight lean forward. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H432" s="4" t="inlineStr"/>
-    </row>
-    <row r="433">
+      <c r="H432" s="4" t="n"/>
+    </row>
+    <row r="433" ht="45" customHeight="1" s="12">
       <c r="A433" s="4" t="inlineStr">
         <is>
           <t>B16</t>
@@ -18360,9 +18563,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: super excited jumping pose, both arms raised high in celebration, empty hands, not holding anything (no gift box, no props), eyes closed happily (^ ^), wide open smile, tiny hearts and sparkles around the head. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H433" s="4" t="inlineStr"/>
-    </row>
-    <row r="434">
+      <c r="H433" s="4" t="n"/>
+    </row>
+    <row r="434" ht="45" customHeight="1" s="12">
       <c r="A434" s="4" t="inlineStr">
         <is>
           <t>B16</t>
@@ -18396,9 +18599,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: making a finger heart toward the viewer with one hand near the cheek, other arm relaxed, not holding anything else (no gift box, no props), winking, cute blush, small smile. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H434" s="4" t="inlineStr"/>
-    </row>
-    <row r="435">
+      <c r="H434" s="4" t="n"/>
+    </row>
+    <row r="435" ht="60" customHeight="1" s="12">
       <c r="A435" s="4" t="inlineStr">
         <is>
           <t>B16</t>
@@ -18432,9 +18635,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance move — body leaning to the LEFT, left arm raised up with index finger pointing to the sky, right hand on hip, right knee slightly bent, empty hands, not holding anything (no gift box, no props), cheerful open smile, small music notes around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H435" s="4" t="inlineStr"/>
-    </row>
-    <row r="436">
+      <c r="H435" s="4" t="n"/>
+    </row>
+    <row r="436" ht="60" customHeight="1" s="12">
       <c r="A436" s="4" t="inlineStr">
         <is>
           <t>B16</t>
@@ -18468,9 +18671,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance move — body leaning to the RIGHT, right arm raised up with index finger pointing to the sky, left hand on hip, left knee slightly bent, empty hands, not holding anything (no gift box, no props), cheerful open smile, small music notes around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H436" s="4" t="inlineStr"/>
-    </row>
-    <row r="437">
+      <c r="H436" s="4" t="n"/>
+    </row>
+    <row r="437" ht="45" customHeight="1" s="12">
       <c r="A437" s="4" t="inlineStr">
         <is>
           <t>B16</t>
@@ -18504,9 +18707,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance finishing pose — both hands making peace signs (V) next to the face, one foot kicked up behind, empty hands, not holding anything (no gift box, no props), winking with a big smile, sparkles around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H437" s="4" t="inlineStr"/>
-    </row>
-    <row r="438">
+      <c r="H437" s="4" t="n"/>
+    </row>
+    <row r="438" ht="45" customHeight="1" s="12">
       <c r="A438" s="4" t="inlineStr">
         <is>
           <t>B16</t>
@@ -18540,9 +18743,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: walking toward the viewer, front view, LEFT foot stepping forward, right arm swinging forward and left arm back, empty hands, not holding anything (no gift box, no props), happy smile, slight bounce. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H438" s="4" t="inlineStr"/>
-    </row>
-    <row r="439">
+      <c r="H438" s="4" t="n"/>
+    </row>
+    <row r="439" ht="45" customHeight="1" s="12">
       <c r="A439" s="4" t="inlineStr">
         <is>
           <t>B16</t>
@@ -18576,9 +18779,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: walking toward the viewer, front view, RIGHT foot stepping forward, left arm swinging forward and right arm back, empty hands, not holding anything (no gift box, no props), happy smile, slight bounce. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H439" s="4" t="inlineStr"/>
-    </row>
-    <row r="440">
+      <c r="H439" s="4" t="n"/>
+    </row>
+    <row r="440" ht="45" customHeight="1" s="12">
       <c r="A440" s="4" t="inlineStr">
         <is>
           <t>B16</t>
@@ -18612,9 +18815,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: close to the viewer, front view, one hand touching the lips about to blow a kiss, eyes gently closed, cute blush, other arm relaxed, not holding anything else (no gift box, no props). Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H440" s="4" t="inlineStr"/>
-    </row>
-    <row r="441">
+      <c r="H440" s="4" t="n"/>
+    </row>
+    <row r="441" ht="60" customHeight="1" s="12">
       <c r="A441" s="4" t="inlineStr">
         <is>
           <t>B16</t>
@@ -18648,9 +18851,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: blowing a kiss toward the viewer, arm stretched forward with open palm from the lips, lips puckered, winking, cute blush, a small pink heart floating out from the hand, not holding anything else (no gift box, no props). Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H441" s="4" t="inlineStr"/>
-    </row>
-    <row r="442">
+      <c r="H441" s="4" t="n"/>
+    </row>
+    <row r="442" ht="45" customHeight="1" s="12">
       <c r="A442" s="4" t="inlineStr">
         <is>
           <t>B16</t>
@@ -18684,9 +18887,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: back view, walking away from the viewer, LEFT foot stepping forward, arms swinging naturally, empty hands, not holding anything (no gift box, no props), showing the back of the outfit and hair. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H442" s="4" t="inlineStr"/>
-    </row>
-    <row r="443">
+      <c r="H442" s="4" t="n"/>
+    </row>
+    <row r="443" ht="45" customHeight="1" s="12">
       <c r="A443" s="4" t="inlineStr">
         <is>
           <t>B16</t>
@@ -18720,9 +18923,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: back view, walking away from the viewer, RIGHT foot stepping forward, arms swinging naturally, empty hands, not holding anything (no gift box, no props), showing the back of the outfit and hair. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H443" s="4" t="inlineStr"/>
-    </row>
-    <row r="444">
+      <c r="H443" s="4" t="n"/>
+    </row>
+    <row r="444" ht="75" customHeight="1" s="12">
       <c r="A444" s="4" t="inlineStr">
         <is>
           <t>B17</t>
@@ -18756,9 +18959,9 @@
           <t>Cute chibi mascot character for a TikTok live streamer, boy with teal hair, cute pirate hat and pastel striped shirt, tiny eyepatch on forehead. Full body, front view, standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Centered, 2.5 heads tall, big sparkly eyes open, soft blush cheeks, gentle smile with mouth closed. Soft 3D pastel style like a vinyl toy, smooth shading, clean outline, pink-lavender-mint palette, kawaii. Transparent background, no shadow on ground, no text, single character only, 1024x1024.</t>
         </is>
       </c>
-      <c r="H444" s="4" t="inlineStr"/>
-    </row>
-    <row r="445">
+      <c r="H444" s="4" t="n"/>
+    </row>
+    <row r="445" ht="45" customHeight="1" s="12">
       <c r="A445" s="4" t="inlineStr">
         <is>
           <t>B17</t>
@@ -18792,9 +18995,9 @@
           <t>Same character, same outfit, exact same pose, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: eyes gently closed as if blinking. Gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H445" s="4" t="inlineStr"/>
-    </row>
-    <row r="446">
+      <c r="H445" s="4" t="n"/>
+    </row>
+    <row r="446" ht="45" customHeight="1" s="12">
       <c r="A446" s="4" t="inlineStr">
         <is>
           <t>B17</t>
@@ -18828,9 +19031,9 @@
           <t>Same character, same outfit, exact same pose, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: mouth open happily as if talking "ah". Eyes open. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H446" s="4" t="inlineStr"/>
-    </row>
-    <row r="447">
+      <c r="H446" s="4" t="n"/>
+    </row>
+    <row r="447" ht="60" customHeight="1" s="12">
       <c r="A447" s="4" t="inlineStr">
         <is>
           <t>B17</t>
@@ -18864,9 +19067,9 @@
           <t>Same character, same outfit, exact same pose, body, face, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: hair and hair accessories gently swaying to the LEFT as if blown by a soft breeze (only hair tips, strands and ribbons shift slightly left). Eyes open, gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H447" s="4" t="inlineStr"/>
-    </row>
-    <row r="448">
+      <c r="H447" s="4" t="n"/>
+    </row>
+    <row r="448" ht="60" customHeight="1" s="12">
       <c r="A448" s="4" t="inlineStr">
         <is>
           <t>B17</t>
@@ -18900,9 +19103,9 @@
           <t>Same character, same outfit, exact same pose, body, face, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: hair and hair accessories gently swaying to the RIGHT as if blown by a soft breeze (only hair tips, strands and ribbons shift slightly right). Eyes open, gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H448" s="4" t="inlineStr"/>
-    </row>
-    <row r="449">
+      <c r="H448" s="4" t="n"/>
+    </row>
+    <row r="449" ht="60" customHeight="1" s="12">
       <c r="A449" s="4" t="inlineStr">
         <is>
           <t>B17</t>
@@ -18936,9 +19139,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: happily ready to catch a gift, both hands cupped together in front of the chest with palms facing up, empty hands, not holding anything (no gift box, no props), clear empty space above the palms, eyes sparkling looking at the hands, big happy smile with mouth open, slight lean forward. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H449" s="4" t="inlineStr"/>
-    </row>
-    <row r="450">
+      <c r="H449" s="4" t="n"/>
+    </row>
+    <row r="450" ht="45" customHeight="1" s="12">
       <c r="A450" s="4" t="inlineStr">
         <is>
           <t>B17</t>
@@ -18972,9 +19175,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: super excited jumping pose, both arms raised high in celebration, empty hands, not holding anything (no gift box, no props), eyes closed happily (^ ^), wide open smile, tiny hearts and sparkles around the head. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H450" s="4" t="inlineStr"/>
-    </row>
-    <row r="451">
+      <c r="H450" s="4" t="n"/>
+    </row>
+    <row r="451" ht="45" customHeight="1" s="12">
       <c r="A451" s="4" t="inlineStr">
         <is>
           <t>B17</t>
@@ -19008,9 +19211,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: making a finger heart toward the viewer with one hand near the cheek, other arm relaxed, not holding anything else (no gift box, no props), winking, cute blush, small smile. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H451" s="4" t="inlineStr"/>
-    </row>
-    <row r="452">
+      <c r="H451" s="4" t="n"/>
+    </row>
+    <row r="452" ht="60" customHeight="1" s="12">
       <c r="A452" s="4" t="inlineStr">
         <is>
           <t>B17</t>
@@ -19044,9 +19247,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance move — body leaning to the LEFT, left arm raised up with index finger pointing to the sky, right hand on hip, right knee slightly bent, empty hands, not holding anything (no gift box, no props), cheerful open smile, small music notes around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H452" s="4" t="inlineStr"/>
-    </row>
-    <row r="453">
+      <c r="H452" s="4" t="n"/>
+    </row>
+    <row r="453" ht="60" customHeight="1" s="12">
       <c r="A453" s="4" t="inlineStr">
         <is>
           <t>B17</t>
@@ -19080,9 +19283,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance move — body leaning to the RIGHT, right arm raised up with index finger pointing to the sky, left hand on hip, left knee slightly bent, empty hands, not holding anything (no gift box, no props), cheerful open smile, small music notes around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H453" s="4" t="inlineStr"/>
-    </row>
-    <row r="454">
+      <c r="H453" s="4" t="n"/>
+    </row>
+    <row r="454" ht="45" customHeight="1" s="12">
       <c r="A454" s="4" t="inlineStr">
         <is>
           <t>B17</t>
@@ -19116,9 +19319,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance finishing pose — both hands making peace signs (V) next to the face, one foot kicked up behind, empty hands, not holding anything (no gift box, no props), winking with a big smile, sparkles around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H454" s="4" t="inlineStr"/>
-    </row>
-    <row r="455">
+      <c r="H454" s="4" t="n"/>
+    </row>
+    <row r="455" ht="45" customHeight="1" s="12">
       <c r="A455" s="4" t="inlineStr">
         <is>
           <t>B17</t>
@@ -19152,9 +19355,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: walking toward the viewer, front view, LEFT foot stepping forward, right arm swinging forward and left arm back, empty hands, not holding anything (no gift box, no props), happy smile, slight bounce. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H455" s="4" t="inlineStr"/>
-    </row>
-    <row r="456">
+      <c r="H455" s="4" t="n"/>
+    </row>
+    <row r="456" ht="45" customHeight="1" s="12">
       <c r="A456" s="4" t="inlineStr">
         <is>
           <t>B17</t>
@@ -19188,9 +19391,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: walking toward the viewer, front view, RIGHT foot stepping forward, left arm swinging forward and right arm back, empty hands, not holding anything (no gift box, no props), happy smile, slight bounce. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H456" s="4" t="inlineStr"/>
-    </row>
-    <row r="457">
+      <c r="H456" s="4" t="n"/>
+    </row>
+    <row r="457" ht="45" customHeight="1" s="12">
       <c r="A457" s="4" t="inlineStr">
         <is>
           <t>B17</t>
@@ -19224,9 +19427,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: close to the viewer, front view, one hand touching the lips about to blow a kiss, eyes gently closed, cute blush, other arm relaxed, not holding anything else (no gift box, no props). Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H457" s="4" t="inlineStr"/>
-    </row>
-    <row r="458">
+      <c r="H457" s="4" t="n"/>
+    </row>
+    <row r="458" ht="60" customHeight="1" s="12">
       <c r="A458" s="4" t="inlineStr">
         <is>
           <t>B17</t>
@@ -19260,9 +19463,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: blowing a kiss toward the viewer, arm stretched forward with open palm from the lips, lips puckered, winking, cute blush, a small pink heart floating out from the hand, not holding anything else (no gift box, no props). Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H458" s="4" t="inlineStr"/>
-    </row>
-    <row r="459">
+      <c r="H458" s="4" t="n"/>
+    </row>
+    <row r="459" ht="45" customHeight="1" s="12">
       <c r="A459" s="4" t="inlineStr">
         <is>
           <t>B17</t>
@@ -19296,9 +19499,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: back view, walking away from the viewer, LEFT foot stepping forward, arms swinging naturally, empty hands, not holding anything (no gift box, no props), showing the back of the outfit and hair. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H459" s="4" t="inlineStr"/>
-    </row>
-    <row r="460">
+      <c r="H459" s="4" t="n"/>
+    </row>
+    <row r="460" ht="45" customHeight="1" s="12">
       <c r="A460" s="4" t="inlineStr">
         <is>
           <t>B17</t>
@@ -19332,9 +19535,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: back view, walking away from the viewer, RIGHT foot stepping forward, arms swinging naturally, empty hands, not holding anything (no gift box, no props), showing the back of the outfit and hair. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H460" s="4" t="inlineStr"/>
-    </row>
-    <row r="461">
+      <c r="H460" s="4" t="n"/>
+    </row>
+    <row r="461" ht="75" customHeight="1" s="12">
       <c r="A461" s="4" t="inlineStr">
         <is>
           <t>B18</t>
@@ -19368,9 +19571,9 @@
           <t>Cute chibi mascot character for a TikTok live streamer, boy with green spiky hair, mint dinosaur hoodie with little spikes on the hood. Full body, front view, standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Centered, 2.5 heads tall, big sparkly eyes open, soft blush cheeks, gentle smile with mouth closed. Soft 3D pastel style like a vinyl toy, smooth shading, clean outline, pink-lavender-mint palette, kawaii. Transparent background, no shadow on ground, no text, single character only, 1024x1024.</t>
         </is>
       </c>
-      <c r="H461" s="4" t="inlineStr"/>
-    </row>
-    <row r="462">
+      <c r="H461" s="4" t="n"/>
+    </row>
+    <row r="462" ht="45" customHeight="1" s="12">
       <c r="A462" s="4" t="inlineStr">
         <is>
           <t>B18</t>
@@ -19404,9 +19607,9 @@
           <t>Same character, same outfit, exact same pose, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: eyes gently closed as if blinking. Gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H462" s="4" t="inlineStr"/>
-    </row>
-    <row r="463">
+      <c r="H462" s="4" t="n"/>
+    </row>
+    <row r="463" ht="45" customHeight="1" s="12">
       <c r="A463" s="4" t="inlineStr">
         <is>
           <t>B18</t>
@@ -19440,9 +19643,9 @@
           <t>Same character, same outfit, exact same pose, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: mouth open happily as if talking "ah". Eyes open. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H463" s="4" t="inlineStr"/>
-    </row>
-    <row r="464">
+      <c r="H463" s="4" t="n"/>
+    </row>
+    <row r="464" ht="60" customHeight="1" s="12">
       <c r="A464" s="4" t="inlineStr">
         <is>
           <t>B18</t>
@@ -19476,9 +19679,9 @@
           <t>Same character, same outfit, exact same pose, body, face, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: hair and hair accessories gently swaying to the LEFT as if blown by a soft breeze (only hair tips, strands and ribbons shift slightly left). Eyes open, gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H464" s="4" t="inlineStr"/>
-    </row>
-    <row r="465">
+      <c r="H464" s="4" t="n"/>
+    </row>
+    <row r="465" ht="60" customHeight="1" s="12">
       <c r="A465" s="4" t="inlineStr">
         <is>
           <t>B18</t>
@@ -19512,9 +19715,9 @@
           <t>Same character, same outfit, exact same pose, body, face, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: hair and hair accessories gently swaying to the RIGHT as if blown by a soft breeze (only hair tips, strands and ribbons shift slightly right). Eyes open, gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H465" s="4" t="inlineStr"/>
-    </row>
-    <row r="466">
+      <c r="H465" s="4" t="n"/>
+    </row>
+    <row r="466" ht="60" customHeight="1" s="12">
       <c r="A466" s="4" t="inlineStr">
         <is>
           <t>B18</t>
@@ -19548,9 +19751,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: happily ready to catch a gift, both hands cupped together in front of the chest with palms facing up, empty hands, not holding anything (no gift box, no props), clear empty space above the palms, eyes sparkling looking at the hands, big happy smile with mouth open, slight lean forward. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H466" s="4" t="inlineStr"/>
-    </row>
-    <row r="467">
+      <c r="H466" s="4" t="n"/>
+    </row>
+    <row r="467" ht="45" customHeight="1" s="12">
       <c r="A467" s="4" t="inlineStr">
         <is>
           <t>B18</t>
@@ -19584,9 +19787,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: super excited jumping pose, both arms raised high in celebration, empty hands, not holding anything (no gift box, no props), eyes closed happily (^ ^), wide open smile, tiny hearts and sparkles around the head. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H467" s="4" t="inlineStr"/>
-    </row>
-    <row r="468">
+      <c r="H467" s="4" t="n"/>
+    </row>
+    <row r="468" ht="45" customHeight="1" s="12">
       <c r="A468" s="4" t="inlineStr">
         <is>
           <t>B18</t>
@@ -19620,9 +19823,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: making a finger heart toward the viewer with one hand near the cheek, other arm relaxed, not holding anything else (no gift box, no props), winking, cute blush, small smile. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H468" s="4" t="inlineStr"/>
-    </row>
-    <row r="469">
+      <c r="H468" s="4" t="n"/>
+    </row>
+    <row r="469" ht="60" customHeight="1" s="12">
       <c r="A469" s="4" t="inlineStr">
         <is>
           <t>B18</t>
@@ -19656,9 +19859,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance move — body leaning to the LEFT, left arm raised up with index finger pointing to the sky, right hand on hip, right knee slightly bent, empty hands, not holding anything (no gift box, no props), cheerful open smile, small music notes around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H469" s="4" t="inlineStr"/>
-    </row>
-    <row r="470">
+      <c r="H469" s="4" t="n"/>
+    </row>
+    <row r="470" ht="60" customHeight="1" s="12">
       <c r="A470" s="4" t="inlineStr">
         <is>
           <t>B18</t>
@@ -19692,9 +19895,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance move — body leaning to the RIGHT, right arm raised up with index finger pointing to the sky, left hand on hip, left knee slightly bent, empty hands, not holding anything (no gift box, no props), cheerful open smile, small music notes around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H470" s="4" t="inlineStr"/>
-    </row>
-    <row r="471">
+      <c r="H470" s="4" t="n"/>
+    </row>
+    <row r="471" ht="45" customHeight="1" s="12">
       <c r="A471" s="4" t="inlineStr">
         <is>
           <t>B18</t>
@@ -19728,9 +19931,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance finishing pose — both hands making peace signs (V) next to the face, one foot kicked up behind, empty hands, not holding anything (no gift box, no props), winking with a big smile, sparkles around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H471" s="4" t="inlineStr"/>
-    </row>
-    <row r="472">
+      <c r="H471" s="4" t="n"/>
+    </row>
+    <row r="472" ht="45" customHeight="1" s="12">
       <c r="A472" s="4" t="inlineStr">
         <is>
           <t>B18</t>
@@ -19764,9 +19967,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: walking toward the viewer, front view, LEFT foot stepping forward, right arm swinging forward and left arm back, empty hands, not holding anything (no gift box, no props), happy smile, slight bounce. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H472" s="4" t="inlineStr"/>
-    </row>
-    <row r="473">
+      <c r="H472" s="4" t="n"/>
+    </row>
+    <row r="473" ht="45" customHeight="1" s="12">
       <c r="A473" s="4" t="inlineStr">
         <is>
           <t>B18</t>
@@ -19800,9 +20003,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: walking toward the viewer, front view, RIGHT foot stepping forward, left arm swinging forward and right arm back, empty hands, not holding anything (no gift box, no props), happy smile, slight bounce. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H473" s="4" t="inlineStr"/>
-    </row>
-    <row r="474">
+      <c r="H473" s="4" t="n"/>
+    </row>
+    <row r="474" ht="45" customHeight="1" s="12">
       <c r="A474" s="4" t="inlineStr">
         <is>
           <t>B18</t>
@@ -19836,9 +20039,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: close to the viewer, front view, one hand touching the lips about to blow a kiss, eyes gently closed, cute blush, other arm relaxed, not holding anything else (no gift box, no props). Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H474" s="4" t="inlineStr"/>
-    </row>
-    <row r="475">
+      <c r="H474" s="4" t="n"/>
+    </row>
+    <row r="475" ht="60" customHeight="1" s="12">
       <c r="A475" s="4" t="inlineStr">
         <is>
           <t>B18</t>
@@ -19872,9 +20075,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: blowing a kiss toward the viewer, arm stretched forward with open palm from the lips, lips puckered, winking, cute blush, a small pink heart floating out from the hand, not holding anything else (no gift box, no props). Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H475" s="4" t="inlineStr"/>
-    </row>
-    <row r="476">
+      <c r="H475" s="4" t="n"/>
+    </row>
+    <row r="476" ht="45" customHeight="1" s="12">
       <c r="A476" s="4" t="inlineStr">
         <is>
           <t>B18</t>
@@ -19908,9 +20111,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: back view, walking away from the viewer, LEFT foot stepping forward, arms swinging naturally, empty hands, not holding anything (no gift box, no props), showing the back of the outfit and hair. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H476" s="4" t="inlineStr"/>
-    </row>
-    <row r="477">
+      <c r="H476" s="4" t="n"/>
+    </row>
+    <row r="477" ht="45" customHeight="1" s="12">
       <c r="A477" s="4" t="inlineStr">
         <is>
           <t>B18</t>
@@ -19944,9 +20147,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: back view, walking away from the viewer, RIGHT foot stepping forward, arms swinging naturally, empty hands, not holding anything (no gift box, no props), showing the back of the outfit and hair. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H477" s="4" t="inlineStr"/>
-    </row>
-    <row r="478">
+      <c r="H477" s="4" t="n"/>
+    </row>
+    <row r="478" ht="75" customHeight="1" s="12">
       <c r="A478" s="4" t="inlineStr">
         <is>
           <t>B19</t>
@@ -19980,9 +20183,9 @@
           <t>Cute chibi mascot character for a TikTok live streamer, boy with lilac middle-part hair, pastel K-pop stage outfit with pearl chains. Full body, front view, standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Centered, 2.5 heads tall, big sparkly eyes open, soft blush cheeks, gentle smile with mouth closed. Soft 3D pastel style like a vinyl toy, smooth shading, clean outline, pink-lavender-mint palette, kawaii. Transparent background, no shadow on ground, no text, single character only, 1024x1024.</t>
         </is>
       </c>
-      <c r="H478" s="4" t="inlineStr"/>
-    </row>
-    <row r="479">
+      <c r="H478" s="4" t="n"/>
+    </row>
+    <row r="479" ht="45" customHeight="1" s="12">
       <c r="A479" s="4" t="inlineStr">
         <is>
           <t>B19</t>
@@ -20016,9 +20219,9 @@
           <t>Same character, same outfit, exact same pose, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: eyes gently closed as if blinking. Gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H479" s="4" t="inlineStr"/>
-    </row>
-    <row r="480">
+      <c r="H479" s="4" t="n"/>
+    </row>
+    <row r="480" ht="45" customHeight="1" s="12">
       <c r="A480" s="4" t="inlineStr">
         <is>
           <t>B19</t>
@@ -20052,9 +20255,9 @@
           <t>Same character, same outfit, exact same pose, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: mouth open happily as if talking "ah". Eyes open. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H480" s="4" t="inlineStr"/>
-    </row>
-    <row r="481">
+      <c r="H480" s="4" t="n"/>
+    </row>
+    <row r="481" ht="60" customHeight="1" s="12">
       <c r="A481" s="4" t="inlineStr">
         <is>
           <t>B19</t>
@@ -20088,9 +20291,9 @@
           <t>Same character, same outfit, exact same pose, body, face, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: hair and hair accessories gently swaying to the LEFT as if blown by a soft breeze (only hair tips, strands and ribbons shift slightly left). Eyes open, gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H481" s="4" t="inlineStr"/>
-    </row>
-    <row r="482">
+      <c r="H481" s="4" t="n"/>
+    </row>
+    <row r="482" ht="60" customHeight="1" s="12">
       <c r="A482" s="4" t="inlineStr">
         <is>
           <t>B19</t>
@@ -20124,9 +20327,9 @@
           <t>Same character, same outfit, exact same pose, body, face, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: hair and hair accessories gently swaying to the RIGHT as if blown by a soft breeze (only hair tips, strands and ribbons shift slightly right). Eyes open, gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H482" s="4" t="inlineStr"/>
-    </row>
-    <row r="483">
+      <c r="H482" s="4" t="n"/>
+    </row>
+    <row r="483" ht="60" customHeight="1" s="12">
       <c r="A483" s="4" t="inlineStr">
         <is>
           <t>B19</t>
@@ -20160,9 +20363,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: happily ready to catch a gift, both hands cupped together in front of the chest with palms facing up, empty hands, not holding anything (no gift box, no props), clear empty space above the palms, eyes sparkling looking at the hands, big happy smile with mouth open, slight lean forward. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H483" s="4" t="inlineStr"/>
-    </row>
-    <row r="484">
+      <c r="H483" s="4" t="n"/>
+    </row>
+    <row r="484" ht="45" customHeight="1" s="12">
       <c r="A484" s="4" t="inlineStr">
         <is>
           <t>B19</t>
@@ -20196,9 +20399,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: super excited jumping pose, both arms raised high in celebration, empty hands, not holding anything (no gift box, no props), eyes closed happily (^ ^), wide open smile, tiny hearts and sparkles around the head. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H484" s="4" t="inlineStr"/>
-    </row>
-    <row r="485">
+      <c r="H484" s="4" t="n"/>
+    </row>
+    <row r="485" ht="45" customHeight="1" s="12">
       <c r="A485" s="4" t="inlineStr">
         <is>
           <t>B19</t>
@@ -20232,9 +20435,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: making a finger heart toward the viewer with one hand near the cheek, other arm relaxed, not holding anything else (no gift box, no props), winking, cute blush, small smile. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H485" s="4" t="inlineStr"/>
-    </row>
-    <row r="486">
+      <c r="H485" s="4" t="n"/>
+    </row>
+    <row r="486" ht="60" customHeight="1" s="12">
       <c r="A486" s="4" t="inlineStr">
         <is>
           <t>B19</t>
@@ -20268,9 +20471,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance move — body leaning to the LEFT, left arm raised up with index finger pointing to the sky, right hand on hip, right knee slightly bent, empty hands, not holding anything (no gift box, no props), cheerful open smile, small music notes around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H486" s="4" t="inlineStr"/>
-    </row>
-    <row r="487">
+      <c r="H486" s="4" t="n"/>
+    </row>
+    <row r="487" ht="60" customHeight="1" s="12">
       <c r="A487" s="4" t="inlineStr">
         <is>
           <t>B19</t>
@@ -20304,9 +20507,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance move — body leaning to the RIGHT, right arm raised up with index finger pointing to the sky, left hand on hip, left knee slightly bent, empty hands, not holding anything (no gift box, no props), cheerful open smile, small music notes around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H487" s="4" t="inlineStr"/>
-    </row>
-    <row r="488">
+      <c r="H487" s="4" t="n"/>
+    </row>
+    <row r="488" ht="45" customHeight="1" s="12">
       <c r="A488" s="4" t="inlineStr">
         <is>
           <t>B19</t>
@@ -20340,9 +20543,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance finishing pose — both hands making peace signs (V) next to the face, one foot kicked up behind, empty hands, not holding anything (no gift box, no props), winking with a big smile, sparkles around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H488" s="4" t="inlineStr"/>
-    </row>
-    <row r="489">
+      <c r="H488" s="4" t="n"/>
+    </row>
+    <row r="489" ht="45" customHeight="1" s="12">
       <c r="A489" s="4" t="inlineStr">
         <is>
           <t>B19</t>
@@ -20376,9 +20579,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: walking toward the viewer, front view, LEFT foot stepping forward, right arm swinging forward and left arm back, empty hands, not holding anything (no gift box, no props), happy smile, slight bounce. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H489" s="4" t="inlineStr"/>
-    </row>
-    <row r="490">
+      <c r="H489" s="4" t="n"/>
+    </row>
+    <row r="490" ht="45" customHeight="1" s="12">
       <c r="A490" s="4" t="inlineStr">
         <is>
           <t>B19</t>
@@ -20412,9 +20615,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: walking toward the viewer, front view, RIGHT foot stepping forward, left arm swinging forward and right arm back, empty hands, not holding anything (no gift box, no props), happy smile, slight bounce. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H490" s="4" t="inlineStr"/>
-    </row>
-    <row r="491">
+      <c r="H490" s="4" t="n"/>
+    </row>
+    <row r="491" ht="45" customHeight="1" s="12">
       <c r="A491" s="4" t="inlineStr">
         <is>
           <t>B19</t>
@@ -20448,9 +20651,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: close to the viewer, front view, one hand touching the lips about to blow a kiss, eyes gently closed, cute blush, other arm relaxed, not holding anything else (no gift box, no props). Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H491" s="4" t="inlineStr"/>
-    </row>
-    <row r="492">
+      <c r="H491" s="4" t="n"/>
+    </row>
+    <row r="492" ht="60" customHeight="1" s="12">
       <c r="A492" s="4" t="inlineStr">
         <is>
           <t>B19</t>
@@ -20484,9 +20687,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: blowing a kiss toward the viewer, arm stretched forward with open palm from the lips, lips puckered, winking, cute blush, a small pink heart floating out from the hand, not holding anything else (no gift box, no props). Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H492" s="4" t="inlineStr"/>
-    </row>
-    <row r="493">
+      <c r="H492" s="4" t="n"/>
+    </row>
+    <row r="493" ht="45" customHeight="1" s="12">
       <c r="A493" s="4" t="inlineStr">
         <is>
           <t>B19</t>
@@ -20520,9 +20723,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: back view, walking away from the viewer, LEFT foot stepping forward, arms swinging naturally, empty hands, not holding anything (no gift box, no props), showing the back of the outfit and hair. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H493" s="4" t="inlineStr"/>
-    </row>
-    <row r="494">
+      <c r="H493" s="4" t="n"/>
+    </row>
+    <row r="494" ht="45" customHeight="1" s="12">
       <c r="A494" s="4" t="inlineStr">
         <is>
           <t>B19</t>
@@ -20556,9 +20759,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: back view, walking away from the viewer, RIGHT foot stepping forward, arms swinging naturally, empty hands, not holding anything (no gift box, no props), showing the back of the outfit and hair. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H494" s="4" t="inlineStr"/>
-    </row>
-    <row r="495">
+      <c r="H494" s="4" t="n"/>
+    </row>
+    <row r="495" ht="75" customHeight="1" s="12">
       <c r="A495" s="4" t="inlineStr">
         <is>
           <t>B20</t>
@@ -20592,9 +20795,9 @@
           <t>Cute chibi mascot character for a TikTok live streamer, boy with honey blond curly hair, overalls with a teddy bear patch, cream shirt. Full body, front view, standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Centered, 2.5 heads tall, big sparkly eyes open, soft blush cheeks, gentle smile with mouth closed. Soft 3D pastel style like a vinyl toy, smooth shading, clean outline, pink-lavender-mint palette, kawaii. Transparent background, no shadow on ground, no text, single character only, 1024x1024.</t>
         </is>
       </c>
-      <c r="H495" s="4" t="inlineStr"/>
-    </row>
-    <row r="496">
+      <c r="H495" s="4" t="n"/>
+    </row>
+    <row r="496" ht="45" customHeight="1" s="12">
       <c r="A496" s="4" t="inlineStr">
         <is>
           <t>B20</t>
@@ -20628,9 +20831,9 @@
           <t>Same character, same outfit, exact same pose, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: eyes gently closed as if blinking. Gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H496" s="4" t="inlineStr"/>
-    </row>
-    <row r="497">
+      <c r="H496" s="4" t="n"/>
+    </row>
+    <row r="497" ht="45" customHeight="1" s="12">
       <c r="A497" s="4" t="inlineStr">
         <is>
           <t>B20</t>
@@ -20664,9 +20867,9 @@
           <t>Same character, same outfit, exact same pose, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: mouth open happily as if talking "ah". Eyes open. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H497" s="4" t="inlineStr"/>
-    </row>
-    <row r="498">
+      <c r="H497" s="4" t="n"/>
+    </row>
+    <row r="498" ht="60" customHeight="1" s="12">
       <c r="A498" s="4" t="inlineStr">
         <is>
           <t>B20</t>
@@ -20700,9 +20903,9 @@
           <t>Same character, same outfit, exact same pose, body, face, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: hair and hair accessories gently swaying to the LEFT as if blown by a soft breeze (only hair tips, strands and ribbons shift slightly left). Eyes open, gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H498" s="4" t="inlineStr"/>
-    </row>
-    <row r="499">
+      <c r="H498" s="4" t="n"/>
+    </row>
+    <row r="499" ht="60" customHeight="1" s="12">
       <c r="A499" s="4" t="inlineStr">
         <is>
           <t>B20</t>
@@ -20736,9 +20939,9 @@
           <t>Same character, same outfit, exact same pose, body, face, size, position and framing as the first image — standing straight, arms relaxed at sides, empty hands, not holding anything (no gift box, no props). Only change: hair and hair accessories gently swaying to the RIGHT as if blown by a soft breeze (only hair tips, strands and ribbons shift slightly right). Eyes open, gentle smile with mouth closed. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H499" s="4" t="inlineStr"/>
-    </row>
-    <row r="500">
+      <c r="H499" s="4" t="n"/>
+    </row>
+    <row r="500" ht="60" customHeight="1" s="12">
       <c r="A500" s="4" t="inlineStr">
         <is>
           <t>B20</t>
@@ -20772,9 +20975,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: happily ready to catch a gift, both hands cupped together in front of the chest with palms facing up, empty hands, not holding anything (no gift box, no props), clear empty space above the palms, eyes sparkling looking at the hands, big happy smile with mouth open, slight lean forward. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H500" s="4" t="inlineStr"/>
-    </row>
-    <row r="501">
+      <c r="H500" s="4" t="n"/>
+    </row>
+    <row r="501" ht="45" customHeight="1" s="12">
       <c r="A501" s="4" t="inlineStr">
         <is>
           <t>B20</t>
@@ -20808,9 +21011,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: super excited jumping pose, both arms raised high in celebration, empty hands, not holding anything (no gift box, no props), eyes closed happily (^ ^), wide open smile, tiny hearts and sparkles around the head. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H501" s="4" t="inlineStr"/>
-    </row>
-    <row r="502">
+      <c r="H501" s="4" t="n"/>
+    </row>
+    <row r="502" ht="45" customHeight="1" s="12">
       <c r="A502" s="4" t="inlineStr">
         <is>
           <t>B20</t>
@@ -20844,9 +21047,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: making a finger heart toward the viewer with one hand near the cheek, other arm relaxed, not holding anything else (no gift box, no props), winking, cute blush, small smile. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H502" s="4" t="inlineStr"/>
-    </row>
-    <row r="503">
+      <c r="H502" s="4" t="n"/>
+    </row>
+    <row r="503" ht="60" customHeight="1" s="12">
       <c r="A503" s="4" t="inlineStr">
         <is>
           <t>B20</t>
@@ -20880,9 +21083,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance move — body leaning to the LEFT, left arm raised up with index finger pointing to the sky, right hand on hip, right knee slightly bent, empty hands, not holding anything (no gift box, no props), cheerful open smile, small music notes around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H503" s="4" t="inlineStr"/>
-    </row>
-    <row r="504">
+      <c r="H503" s="4" t="n"/>
+    </row>
+    <row r="504" ht="60" customHeight="1" s="12">
       <c r="A504" s="4" t="inlineStr">
         <is>
           <t>B20</t>
@@ -20916,9 +21119,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance move — body leaning to the RIGHT, right arm raised up with index finger pointing to the sky, left hand on hip, left knee slightly bent, empty hands, not holding anything (no gift box, no props), cheerful open smile, small music notes around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H504" s="4" t="inlineStr"/>
-    </row>
-    <row r="505">
+      <c r="H504" s="4" t="n"/>
+    </row>
+    <row r="505" ht="45" customHeight="1" s="12">
       <c r="A505" s="4" t="inlineStr">
         <is>
           <t>B20</t>
@@ -20952,9 +21155,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: cute dance finishing pose — both hands making peace signs (V) next to the face, one foot kicked up behind, empty hands, not holding anything (no gift box, no props), winking with a big smile, sparkles around. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H505" s="4" t="inlineStr"/>
-    </row>
-    <row r="506">
+      <c r="H505" s="4" t="n"/>
+    </row>
+    <row r="506" ht="45" customHeight="1" s="12">
       <c r="A506" s="4" t="inlineStr">
         <is>
           <t>B20</t>
@@ -20988,9 +21191,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: walking toward the viewer, front view, LEFT foot stepping forward, right arm swinging forward and left arm back, empty hands, not holding anything (no gift box, no props), happy smile, slight bounce. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H506" s="4" t="inlineStr"/>
-    </row>
-    <row r="507">
+      <c r="H506" s="4" t="n"/>
+    </row>
+    <row r="507" ht="45" customHeight="1" s="12">
       <c r="A507" s="4" t="inlineStr">
         <is>
           <t>B20</t>
@@ -21024,9 +21227,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: walking toward the viewer, front view, RIGHT foot stepping forward, left arm swinging forward and right arm back, empty hands, not holding anything (no gift box, no props), happy smile, slight bounce. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H507" s="4" t="inlineStr"/>
-    </row>
-    <row r="508">
+      <c r="H507" s="4" t="n"/>
+    </row>
+    <row r="508" ht="45" customHeight="1" s="12">
       <c r="A508" s="4" t="inlineStr">
         <is>
           <t>B20</t>
@@ -21060,9 +21263,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: close to the viewer, front view, one hand touching the lips about to blow a kiss, eyes gently closed, cute blush, other arm relaxed, not holding anything else (no gift box, no props). Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H508" s="4" t="inlineStr"/>
-    </row>
-    <row r="509">
+      <c r="H508" s="4" t="n"/>
+    </row>
+    <row r="509" ht="60" customHeight="1" s="12">
       <c r="A509" s="4" t="inlineStr">
         <is>
           <t>B20</t>
@@ -21096,9 +21299,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: blowing a kiss toward the viewer, arm stretched forward with open palm from the lips, lips puckered, winking, cute blush, a small pink heart floating out from the hand, not holding anything else (no gift box, no props). Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H509" s="4" t="inlineStr"/>
-    </row>
-    <row r="510">
+      <c r="H509" s="4" t="n"/>
+    </row>
+    <row r="510" ht="45" customHeight="1" s="12">
       <c r="A510" s="4" t="inlineStr">
         <is>
           <t>B20</t>
@@ -21132,9 +21335,9 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: back view, walking away from the viewer, LEFT foot stepping forward, arms swinging naturally, empty hands, not holding anything (no gift box, no props), showing the back of the outfit and hair. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H510" s="4" t="inlineStr"/>
-    </row>
-    <row r="511">
+      <c r="H510" s="4" t="n"/>
+    </row>
+    <row r="511" ht="45" customHeight="1" s="12">
       <c r="A511" s="4" t="inlineStr">
         <is>
           <t>B20</t>
@@ -21168,7 +21371,7 @@
           <t>Same character, same outfit, same size, position and framing as the first image — new pose: back view, walking away from the viewer, RIGHT foot stepping forward, arms swinging naturally, empty hands, not holding anything (no gift box, no props), showing the back of the outfit and hair. Transparent background, no text, 1024x1024.</t>
         </is>
       </c>
-      <c r="H511" s="4" t="inlineStr"/>
+      <c r="H511" s="4" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H511"/>
